--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46081,7 +46081,7 @@
         <v>17577</v>
       </c>
       <c r="C1988" t="n">
-        <v>5.28000020980835</v>
+        <v>5.30000019073486</v>
       </c>
       <c r="D1988" t="n">
         <v>5.15999984741211</v>
@@ -46093,6 +46093,29 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1988" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1989" t="n">
+        <v>2411</v>
+      </c>
+      <c r="C1989" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="E1989" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F1989" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="G1989" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46119,6 +46119,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1990">
+      <c r="A1990" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1990" t="n">
+        <v>3068</v>
+      </c>
+      <c r="C1990" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D1990" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="E1990" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="F1990" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="G1990" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46142,6 +46142,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1991">
+      <c r="A1991" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1991" t="n">
+        <v>12605</v>
+      </c>
+      <c r="C1991" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="D1991" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="E1991" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="F1991" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="G1991" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46165,6 +46165,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1992">
+      <c r="A1992" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1992" t="n">
+        <v>7954</v>
+      </c>
+      <c r="C1992" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="D1992" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="E1992" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G1992" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46006,22 +46006,22 @@
     </row>
     <row r="1985">
       <c r="A1985" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1985" t="n">
-        <v>5786</v>
+        <v>815</v>
       </c>
       <c r="C1985" t="n">
-        <v>5.61999988555908</v>
+        <v>5.65999984741211</v>
       </c>
       <c r="D1985" t="n">
-        <v>5.51999998092651</v>
+        <v>5.59999990463257</v>
       </c>
       <c r="E1985" t="n">
-        <v>5.57999992370605</v>
+        <v>5.65999984741211</v>
       </c>
       <c r="F1985" t="n">
-        <v>5.51999998092651</v>
+        <v>5.6399998664856</v>
       </c>
       <c r="G1985" t="s">
         <v>7</v>
@@ -46029,22 +46029,22 @@
     </row>
     <row r="1986">
       <c r="A1986" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1986" t="n">
-        <v>19127</v>
+        <v>5786</v>
       </c>
       <c r="C1986" t="n">
-        <v>5.53999996185303</v>
+        <v>5.61999988555908</v>
       </c>
       <c r="D1986" t="n">
-        <v>5.34000015258789</v>
+        <v>5.51999998092651</v>
       </c>
       <c r="E1986" t="n">
-        <v>5.48000001907349</v>
+        <v>5.57999992370605</v>
       </c>
       <c r="F1986" t="n">
-        <v>5.3600001335144</v>
+        <v>5.51999998092651</v>
       </c>
       <c r="G1986" t="s">
         <v>7</v>
@@ -46052,22 +46052,22 @@
     </row>
     <row r="1987">
       <c r="A1987" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1987" t="n">
-        <v>14959</v>
+        <v>19127</v>
       </c>
       <c r="C1987" t="n">
-        <v>5.38000011444092</v>
+        <v>5.53999996185303</v>
       </c>
       <c r="D1987" t="n">
-        <v>5.19999980926514</v>
+        <v>5.34000015258789</v>
       </c>
       <c r="E1987" t="n">
-        <v>5.38000011444092</v>
+        <v>5.48000001907349</v>
       </c>
       <c r="F1987" t="n">
-        <v>5.19999980926514</v>
+        <v>5.3600001335144</v>
       </c>
       <c r="G1987" t="s">
         <v>7</v>
@@ -46075,22 +46075,22 @@
     </row>
     <row r="1988">
       <c r="A1988" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1988" t="n">
-        <v>17577</v>
+        <v>14959</v>
       </c>
       <c r="C1988" t="n">
-        <v>5.30000019073486</v>
+        <v>5.38000011444092</v>
       </c>
       <c r="D1988" t="n">
-        <v>5.15999984741211</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="E1988" t="n">
-        <v>5.15999984741211</v>
+        <v>5.38000011444092</v>
       </c>
       <c r="F1988" t="n">
-        <v>5.30000019073486</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="G1988" t="s">
         <v>7</v>
@@ -46098,22 +46098,22 @@
     </row>
     <row r="1989">
       <c r="A1989" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1989" t="n">
-        <v>2411</v>
+        <v>17577</v>
       </c>
       <c r="C1989" t="n">
-        <v>5.32000017166138</v>
+        <v>5.30000019073486</v>
       </c>
       <c r="D1989" t="n">
-        <v>5.26000022888184</v>
+        <v>5.15999984741211</v>
       </c>
       <c r="E1989" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="F1989" t="n">
         <v>5.30000019073486</v>
-      </c>
-      <c r="F1989" t="n">
-        <v>5.32000017166138</v>
       </c>
       <c r="G1989" t="s">
         <v>7</v>
@@ -46121,22 +46121,22 @@
     </row>
     <row r="1990">
       <c r="A1990" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1990" t="n">
-        <v>3068</v>
+        <v>2411</v>
       </c>
       <c r="C1990" t="n">
-        <v>5.30000019073486</v>
+        <v>5.32000017166138</v>
       </c>
       <c r="D1990" t="n">
         <v>5.26000022888184</v>
       </c>
       <c r="E1990" t="n">
-        <v>5.28000020980835</v>
+        <v>5.30000019073486</v>
       </c>
       <c r="F1990" t="n">
-        <v>5.26000022888184</v>
+        <v>5.32000017166138</v>
       </c>
       <c r="G1990" t="s">
         <v>7</v>
@@ -46144,22 +46144,22 @@
     </row>
     <row r="1991">
       <c r="A1991" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1991" t="n">
-        <v>12605</v>
+        <v>3068</v>
       </c>
       <c r="C1991" t="n">
-        <v>5.38000011444092</v>
+        <v>5.30000019073486</v>
       </c>
       <c r="D1991" t="n">
-        <v>5.19999980926514</v>
+        <v>5.26000022888184</v>
       </c>
       <c r="E1991" t="n">
-        <v>5.19999980926514</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="F1991" t="n">
-        <v>5.38000011444092</v>
+        <v>5.26000022888184</v>
       </c>
       <c r="G1991" t="s">
         <v>7</v>
@@ -46167,24 +46167,47 @@
     </row>
     <row r="1992">
       <c r="A1992" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1992" t="n">
-        <v>7954</v>
+        <v>12605</v>
       </c>
       <c r="C1992" t="n">
         <v>5.38000011444092</v>
       </c>
       <c r="D1992" t="n">
-        <v>5.26000022888184</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="E1992" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="F1992" t="n">
         <v>5.38000011444092</v>
       </c>
-      <c r="F1992" t="n">
-        <v>5.3600001335144</v>
-      </c>
       <c r="G1992" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1993" t="n">
+        <v>15091</v>
+      </c>
+      <c r="C1993" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="D1993" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="E1993" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="F1993" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="G1993" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835204124451</v>
+        <v>3.50835180282593</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290766716003</v>
+        <v>3.59290790557861</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555630683899</v>
+        <v>3.54555654525757</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694540023804</v>
+        <v>3.47694516181946</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018098831177</v>
+        <v>3.47018074989319</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710980415344</v>
+        <v>3.58710956573486</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299379348755</v>
+        <v>3.53299355506897</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185546875</v>
+        <v>3.65185570716858</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464311599731</v>
+        <v>3.84464335441589</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869815826416</v>
+        <v>3.82869839668274</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243480682373</v>
+        <v>3.92243504524231</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863742828369</v>
+        <v>3.75863766670227</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364147186279</v>
+        <v>3.64364123344421</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422080993652</v>
+        <v>3.91422057151794</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615319252014</v>
+        <v>3.91615343093872</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331522941589</v>
+        <v>3.98331546783447</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.95287489891052</v>
+        <v>3.9528751373291</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354797363281</v>
+        <v>3.93354773521423</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445379257202</v>
+        <v>3.86445355415344</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.6866443157196</v>
+        <v>3.68664455413818</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251308441162</v>
+        <v>4.09251356124878</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501791000366</v>
+        <v>4.59501838684082</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929832458496</v>
+        <v>4.75929880142212</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727981567383</v>
+        <v>4.81727933883667</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740079879761</v>
+        <v>4.95740127563477</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596115112305</v>
+        <v>5.28596162796021</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134527206421</v>
+        <v>5.13134479522705</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489692687988</v>
+        <v>4.45489645004272</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.62400817871094</v>
+        <v>4.6240086555481</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309289932251</v>
+        <v>4.36309242248535</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645755767822</v>
+        <v>4.26645708084106</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621439933777</v>
+        <v>3.98621416091919</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453254699707</v>
+        <v>4.03453207015991</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193374633789</v>
+        <v>3.82193398475647</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.9668869972229</v>
+        <v>3.96688747406006</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820494651794</v>
+        <v>3.49820470809937</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297143936157</v>
+        <v>4.22297096252441</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605560302734</v>
+        <v>4.99605512619019</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -52242,6 +52242,32 @@
         <v>5.40000009536743</v>
       </c>
       <c r="H1995" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1996" t="n">
+        <v>14166</v>
+      </c>
+      <c r="C1996" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="D1996" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="E1996" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="F1996" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="G1996" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="H1996" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835180282593</v>
+        <v>3.50835204124451</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290790557861</v>
+        <v>3.59290766716003</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555654525757</v>
+        <v>3.54555630683899</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694516181946</v>
+        <v>3.47694540023804</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018074989319</v>
+        <v>3.47018098831177</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887778282166</v>
+        <v>3.47887802124023</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786876678467</v>
+        <v>3.50786852836609</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887778282166</v>
+        <v>3.47887802124023</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786876678467</v>
+        <v>3.50786852836609</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710956573486</v>
+        <v>3.58710980415344</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299355506897</v>
+        <v>3.53299379348755</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5368595123291</v>
+        <v>3.53685927391052</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185570716858</v>
+        <v>3.65185546875</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464335441589</v>
+        <v>3.84464311599731</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869839668274</v>
+        <v>3.82869815826416</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243504524231</v>
+        <v>3.92243480682373</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863766670227</v>
+        <v>3.75863742828369</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364123344421</v>
+        <v>3.64364147186279</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422057151794</v>
+        <v>3.91422080993652</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615343093872</v>
+        <v>3.91615319252014</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331546783447</v>
+        <v>3.98331522941589</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.9528751373291</v>
+        <v>3.95287489891052</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354773521423</v>
+        <v>3.93354797363281</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445355415344</v>
+        <v>3.86445379257202</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890598297119</v>
+        <v>3.90890622138977</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856908798218</v>
+        <v>3.91856932640076</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.68664455413818</v>
+        <v>3.6866443157196</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890598297119</v>
+        <v>3.90890622138977</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.04419565200806</v>
+        <v>4.0441951751709</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431663513184</v>
+        <v>4.18431711196899</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251356124878</v>
+        <v>4.09251308441162</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431663513184</v>
+        <v>4.18431711196899</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501838684082</v>
+        <v>4.59501791000366</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761623382568</v>
+        <v>4.80761575698853</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761623382568</v>
+        <v>4.80761575698853</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929880142212</v>
+        <v>4.75929832458496</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727933883667</v>
+        <v>4.81727981567383</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740127563477</v>
+        <v>4.95740079879761</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596162796021</v>
+        <v>5.28596115112305</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134479522705</v>
+        <v>5.13134527206421</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263502120972</v>
+        <v>4.23263454437256</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489645004272</v>
+        <v>4.45489692687988</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745719909668</v>
+        <v>5.81745672225952</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745719909668</v>
+        <v>5.81745672225952</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725185394287</v>
+        <v>4.38725137710571</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.6240086555481</v>
+        <v>4.62400817871094</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602716445923</v>
+        <v>4.56602764129639</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602716445923</v>
+        <v>4.56602764129639</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309242248535</v>
+        <v>4.36309289932251</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645708084106</v>
+        <v>4.26645755767822</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095245361328</v>
+        <v>4.28095197677612</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.04419565200806</v>
+        <v>4.0441951751709</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621416091919</v>
+        <v>3.98621439933777</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453207015991</v>
+        <v>4.03453254699707</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.8557562828064</v>
+        <v>3.85575652122498</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193398475647</v>
+        <v>3.82193374633789</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327965736389</v>
+        <v>3.78327989578247</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327965736389</v>
+        <v>3.78327989578247</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945759773254</v>
+        <v>3.74945735931396</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.8557562828064</v>
+        <v>3.85575652122498</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945759773254</v>
+        <v>3.74945735931396</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.96688747406006</v>
+        <v>3.9668869972229</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856908798218</v>
+        <v>3.91856932640076</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820470809937</v>
+        <v>3.49820494651794</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135464668274</v>
+        <v>3.55135440826416</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.5368595123291</v>
+        <v>3.53685927391052</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.59967231750488</v>
+        <v>3.5996720790863</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135464668274</v>
+        <v>3.55135440826416</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59967231750488</v>
+        <v>3.5996720790863</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263502120972</v>
+        <v>4.23263454437256</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095245361328</v>
+        <v>4.28095197677612</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297096252441</v>
+        <v>4.22297143936157</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725185394287</v>
+        <v>4.38725137710571</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605512619019</v>
+        <v>4.99605560302734</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -52268,6 +52268,32 @@
         <v>5.38000011444092</v>
       </c>
       <c r="H1996" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1997" t="n">
+        <v>14461</v>
+      </c>
+      <c r="C1997" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="D1997" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="E1997" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="G1997" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="H1997" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -52297,6 +52297,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1998">
+      <c r="A1998" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1998" t="n">
+        <v>55416</v>
+      </c>
+      <c r="C1998" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="E1998" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="F1998" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="G1998" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="H1998" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -52323,6 +52323,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1999">
+      <c r="A1999" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1999" t="n">
+        <v>7902</v>
+      </c>
+      <c r="C1999" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E1999" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="F1999" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="G1999" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="H1999" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835204124451</v>
+        <v>3.50835180282593</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290766716003</v>
+        <v>3.59290790557861</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555630683899</v>
+        <v>3.54555654525757</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694540023804</v>
+        <v>3.47694516181946</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018098831177</v>
+        <v>3.47018074989319</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710980415344</v>
+        <v>3.58710956573486</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299379348755</v>
+        <v>3.53299355506897</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185546875</v>
+        <v>3.65185570716858</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464311599731</v>
+        <v>3.84464335441589</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869815826416</v>
+        <v>3.82869839668274</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243480682373</v>
+        <v>3.92243504524231</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863742828369</v>
+        <v>3.75863766670227</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364147186279</v>
+        <v>3.64364123344421</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422080993652</v>
+        <v>3.91422057151794</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615319252014</v>
+        <v>3.91615343093872</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331522941589</v>
+        <v>3.98331546783447</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.95287489891052</v>
+        <v>3.9528751373291</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354797363281</v>
+        <v>3.93354773521423</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445379257202</v>
+        <v>3.86445355415344</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.6866443157196</v>
+        <v>3.68664455413818</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251308441162</v>
+        <v>4.09251356124878</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501791000366</v>
+        <v>4.59501838684082</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929832458496</v>
+        <v>4.75929880142212</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727981567383</v>
+        <v>4.81727933883667</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740079879761</v>
+        <v>4.95740127563477</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596115112305</v>
+        <v>5.28596162796021</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134527206421</v>
+        <v>5.13134479522705</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489692687988</v>
+        <v>4.45489645004272</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.62400817871094</v>
+        <v>4.6240086555481</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309289932251</v>
+        <v>4.36309242248535</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645755767822</v>
+        <v>4.26645708084106</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621439933777</v>
+        <v>3.98621416091919</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453254699707</v>
+        <v>4.03453207015991</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193374633789</v>
+        <v>3.82193398475647</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.9668869972229</v>
+        <v>3.96688747406006</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820494651794</v>
+        <v>3.49820470809937</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297143936157</v>
+        <v>4.22297096252441</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605560302734</v>
+        <v>4.99605512619019</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -52398,6 +52398,32 @@
         <v>5.40000009536743</v>
       </c>
       <c r="H2001" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2002" t="n">
+        <v>15624</v>
+      </c>
+      <c r="C2002" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="F2002" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="G2002" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="H2002" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46480,8 +46480,31 @@
       <c r="E2005" t="n">
         <v>5.38000011444092</v>
       </c>
-      <c r="F2005"/>
+      <c r="F2005" t="n">
+        <v>5.42000007629395</v>
+      </c>
       <c r="G2005" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2006" t="n">
+        <v>53235</v>
+      </c>
+      <c r="C2006" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E2006" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="F2006"/>
+      <c r="G2006" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46503,8 +46503,31 @@
       <c r="E2006" t="n">
         <v>5.3600001335144</v>
       </c>
-      <c r="F2006"/>
+      <c r="F2006" t="n">
+        <v>5.38000011444092</v>
+      </c>
       <c r="G2006" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2007" t="n">
+        <v>35259</v>
+      </c>
+      <c r="C2007" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D2007" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="F2007"/>
+      <c r="G2007" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46526,8 +46526,31 @@
       <c r="E2007" t="n">
         <v>5.40000009536743</v>
       </c>
-      <c r="F2007"/>
+      <c r="F2007" t="n">
+        <v>5.38000011444092</v>
+      </c>
       <c r="G2007" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2008" t="n">
+        <v>61665</v>
+      </c>
+      <c r="C2008" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="D2008" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>5.42000007629395</v>
+      </c>
+      <c r="F2008"/>
+      <c r="G2008" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46549,8 +46549,31 @@
       <c r="E2008" t="n">
         <v>5.42000007629395</v>
       </c>
-      <c r="F2008"/>
+      <c r="F2008" t="n">
+        <v>5.40000009536743</v>
+      </c>
       <c r="G2008" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2009" t="n">
+        <v>17555</v>
+      </c>
+      <c r="C2009" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="D2009" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="E2009" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="F2009"/>
+      <c r="G2009" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -46579,6 +46579,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2010">
+      <c r="A2010" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2010" t="n">
+        <v>25394</v>
+      </c>
+      <c r="C2010" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="G2010" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -52687,6 +52687,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2013">
+      <c r="A2013" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2013" t="n">
+        <v>120337</v>
+      </c>
+      <c r="C2013" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="D2013" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="G2013" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="H2013" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -499,7 +499,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835204124451</v>
+        <v>3.50835180282593</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290766716003</v>
+        <v>3.59290790557861</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555630683899</v>
+        <v>3.54555654525757</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694540023804</v>
+        <v>3.47694516181946</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018098831177</v>
+        <v>3.47018074989319</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710980415344</v>
+        <v>3.58710956573486</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299379348755</v>
+        <v>3.53299355506897</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185546875</v>
+        <v>3.65185570716858</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464311599731</v>
+        <v>3.84464335441589</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869815826416</v>
+        <v>3.82869839668274</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243480682373</v>
+        <v>3.92243504524231</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863742828369</v>
+        <v>3.75863766670227</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364147186279</v>
+        <v>3.64364123344421</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422080993652</v>
+        <v>3.91422057151794</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615319252014</v>
+        <v>3.91615343093872</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331522941589</v>
+        <v>3.98331546783447</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.95287489891052</v>
+        <v>3.9528751373291</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354797363281</v>
+        <v>3.93354773521423</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445379257202</v>
+        <v>3.86445355415344</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.6866443157196</v>
+        <v>3.68664455413818</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251308441162</v>
+        <v>4.09251356124878</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501791000366</v>
+        <v>4.59501838684082</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929832458496</v>
+        <v>4.75929880142212</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727981567383</v>
+        <v>4.81727933883667</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740079879761</v>
+        <v>4.95740127563477</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596115112305</v>
+        <v>5.28596162796021</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134527206421</v>
+        <v>5.13134479522705</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489692687988</v>
+        <v>4.45489645004272</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.62400817871094</v>
+        <v>4.6240086555481</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309289932251</v>
+        <v>4.36309242248535</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645755767822</v>
+        <v>4.26645708084106</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621439933777</v>
+        <v>3.98621416091919</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453254699707</v>
+        <v>4.03453207015991</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193374633789</v>
+        <v>3.82193398475647</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.9668869972229</v>
+        <v>3.96688747406006</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820494651794</v>
+        <v>3.49820470809937</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297143936157</v>
+        <v>4.22297096252441</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605560302734</v>
+        <v>4.99605512619019</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -52692,7 +52692,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B2013" t="n">
-        <v>120337</v>
+        <v>132525</v>
       </c>
       <c r="C2013" t="n">
         <v>5.44000005722046</v>
@@ -52710,6 +52710,32 @@
         <v>5.17999982833862</v>
       </c>
       <c r="H2013" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2014" t="n">
+        <v>41592</v>
+      </c>
+      <c r="C2014" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="D2014" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="E2014" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="G2014" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="H2014" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835180282593</v>
+        <v>3.50835204124451</v>
       </c>
       <c r="H5" t="n">
         <v>168607</v>
@@ -572,7 +572,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290790557861</v>
+        <v>3.59290766716003</v>
       </c>
       <c r="H7" t="n">
         <v>115707</v>
@@ -630,7 +630,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555654525757</v>
+        <v>3.54555630683899</v>
       </c>
       <c r="H9" t="n">
         <v>18987</v>
@@ -717,7 +717,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694516181946</v>
+        <v>3.47694540023804</v>
       </c>
       <c r="H12" t="n">
         <v>25574</v>
@@ -775,7 +775,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018074989319</v>
+        <v>3.47018098831177</v>
       </c>
       <c r="H14" t="n">
         <v>14046</v>
@@ -804,7 +804,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887778282166</v>
+        <v>3.47887802124023</v>
       </c>
       <c r="H15" t="n">
         <v>25673</v>
@@ -833,7 +833,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786876678467</v>
+        <v>3.50786852836609</v>
       </c>
       <c r="H16" t="n">
         <v>17829</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887778282166</v>
+        <v>3.47887802124023</v>
       </c>
       <c r="H20" t="n">
         <v>24337</v>
@@ -1007,7 +1007,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786876678467</v>
+        <v>3.50786852836609</v>
       </c>
       <c r="H22" t="n">
         <v>15060</v>
@@ -1065,7 +1065,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710956573486</v>
+        <v>3.58710980415344</v>
       </c>
       <c r="H24" t="n">
         <v>31246</v>
@@ -1297,7 +1297,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299355506897</v>
+        <v>3.53299379348755</v>
       </c>
       <c r="H32" t="n">
         <v>12155</v>
@@ -1326,7 +1326,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5368595123291</v>
+        <v>3.53685927391052</v>
       </c>
       <c r="H33" t="n">
         <v>2992</v>
@@ -1384,7 +1384,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185570716858</v>
+        <v>3.65185546875</v>
       </c>
       <c r="H35" t="n">
         <v>9616</v>
@@ -1500,7 +1500,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H39" t="n">
         <v>33223</v>
@@ -1558,7 +1558,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464335441589</v>
+        <v>3.84464311599731</v>
       </c>
       <c r="H41" t="n">
         <v>67310</v>
@@ -1674,7 +1674,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869839668274</v>
+        <v>3.82869815826416</v>
       </c>
       <c r="H45" t="n">
         <v>15050</v>
@@ -1761,7 +1761,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243504524231</v>
+        <v>3.92243480682373</v>
       </c>
       <c r="H48" t="n">
         <v>7064</v>
@@ -1848,7 +1848,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H51" t="n">
         <v>10244</v>
@@ -2138,7 +2138,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863766670227</v>
+        <v>3.75863742828369</v>
       </c>
       <c r="H61" t="n">
         <v>18963</v>
@@ -2167,7 +2167,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H62" t="n">
         <v>25241</v>
@@ -2254,7 +2254,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H65" t="n">
         <v>14098</v>
@@ -2283,7 +2283,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364123344421</v>
+        <v>3.64364147186279</v>
       </c>
       <c r="H66" t="n">
         <v>24444</v>
@@ -2312,7 +2312,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H67" t="n">
         <v>14328</v>
@@ -2457,7 +2457,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422057151794</v>
+        <v>3.91422080993652</v>
       </c>
       <c r="H72" t="n">
         <v>37886</v>
@@ -2544,7 +2544,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H75" t="n">
         <v>61176</v>
@@ -2573,7 +2573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H76" t="n">
         <v>4871</v>
@@ -2631,7 +2631,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615343093872</v>
+        <v>3.91615319252014</v>
       </c>
       <c r="H78" t="n">
         <v>28408</v>
@@ -2660,7 +2660,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331546783447</v>
+        <v>3.98331522941589</v>
       </c>
       <c r="H79" t="n">
         <v>15491</v>
@@ -2689,7 +2689,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H80" t="n">
         <v>8568</v>
@@ -2718,7 +2718,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.9528751373291</v>
+        <v>3.95287489891052</v>
       </c>
       <c r="H81" t="n">
         <v>11304</v>
@@ -2747,7 +2747,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354773521423</v>
+        <v>3.93354797363281</v>
       </c>
       <c r="H82" t="n">
         <v>1333</v>
@@ -2805,7 +2805,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445355415344</v>
+        <v>3.86445379257202</v>
       </c>
       <c r="H84" t="n">
         <v>14743</v>
@@ -2892,7 +2892,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H87" t="n">
         <v>16436</v>
@@ -2921,7 +2921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H88" t="n">
         <v>70067</v>
@@ -2950,7 +2950,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H89" t="n">
         <v>20248</v>
@@ -2979,7 +2979,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H90" t="n">
         <v>9804</v>
@@ -3008,7 +3008,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H91" t="n">
         <v>8029</v>
@@ -3124,7 +3124,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H95" t="n">
         <v>6789</v>
@@ -3153,7 +3153,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H96" t="n">
         <v>16453</v>
@@ -3182,7 +3182,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H97" t="n">
         <v>13893</v>
@@ -3211,7 +3211,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H98" t="n">
         <v>34445</v>
@@ -3269,7 +3269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H100" t="n">
         <v>5569</v>
@@ -3327,7 +3327,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H102" t="n">
         <v>17175</v>
@@ -3385,7 +3385,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H104" t="n">
         <v>4792</v>
@@ -3443,7 +3443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H106" t="n">
         <v>12618</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H107" t="n">
         <v>7801</v>
@@ -3530,7 +3530,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H109" t="n">
         <v>27377</v>
@@ -3559,7 +3559,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H110" t="n">
         <v>9652</v>
@@ -3588,7 +3588,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H111" t="n">
         <v>22427</v>
@@ -3646,7 +3646,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H113" t="n">
         <v>5635</v>
@@ -3675,7 +3675,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H114" t="n">
         <v>12247</v>
@@ -3704,7 +3704,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H115" t="n">
         <v>46534</v>
@@ -3762,7 +3762,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H117" t="n">
         <v>14370</v>
@@ -3791,7 +3791,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H118" t="n">
         <v>20871</v>
@@ -3849,7 +3849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H120" t="n">
         <v>51861</v>
@@ -3907,7 +3907,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890598297119</v>
+        <v>3.90890622138977</v>
       </c>
       <c r="H122" t="n">
         <v>24632</v>
@@ -3965,7 +3965,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856908798218</v>
+        <v>3.91856932640076</v>
       </c>
       <c r="H124" t="n">
         <v>9251</v>
@@ -4023,7 +4023,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H126" t="n">
         <v>23445</v>
@@ -4052,7 +4052,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H127" t="n">
         <v>13288</v>
@@ -4226,7 +4226,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H133" t="n">
         <v>69275</v>
@@ -4255,7 +4255,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.68664455413818</v>
+        <v>3.6866443157196</v>
       </c>
       <c r="H134" t="n">
         <v>83826</v>
@@ -4284,7 +4284,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H135" t="n">
         <v>38411</v>
@@ -4342,7 +4342,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H137" t="n">
         <v>28361</v>
@@ -4371,7 +4371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H138" t="n">
         <v>16251</v>
@@ -4400,7 +4400,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890598297119</v>
+        <v>3.90890622138977</v>
       </c>
       <c r="H139" t="n">
         <v>24663</v>
@@ -4661,7 +4661,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H148" t="n">
         <v>6408</v>
@@ -4690,7 +4690,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H149" t="n">
         <v>17007</v>
@@ -4748,7 +4748,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H151" t="n">
         <v>51508</v>
@@ -4893,7 +4893,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.04419565200806</v>
+        <v>4.0441951751709</v>
       </c>
       <c r="H156" t="n">
         <v>57059</v>
@@ -4951,7 +4951,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431663513184</v>
+        <v>4.18431711196899</v>
       </c>
       <c r="H158" t="n">
         <v>51199</v>
@@ -5821,7 +5821,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251356124878</v>
+        <v>4.09251308441162</v>
       </c>
       <c r="H188" t="n">
         <v>3584</v>
@@ -5995,7 +5995,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431663513184</v>
+        <v>4.18431711196899</v>
       </c>
       <c r="H194" t="n">
         <v>11423</v>
@@ -6459,7 +6459,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H210" t="n">
         <v>4401</v>
@@ -6546,7 +6546,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H213" t="n">
         <v>14225</v>
@@ -6720,7 +6720,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H219" t="n">
         <v>109205</v>
@@ -6981,7 +6981,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H228" t="n">
         <v>32762</v>
@@ -7358,7 +7358,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501838684082</v>
+        <v>4.59501791000366</v>
       </c>
       <c r="H241" t="n">
         <v>82951</v>
@@ -7416,7 +7416,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H243" t="n">
         <v>10325</v>
@@ -7445,7 +7445,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H244" t="n">
         <v>8300</v>
@@ -7590,7 +7590,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761623382568</v>
+        <v>4.80761575698853</v>
       </c>
       <c r="H249" t="n">
         <v>50047</v>
@@ -7619,7 +7619,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761623382568</v>
+        <v>4.80761575698853</v>
       </c>
       <c r="H250" t="n">
         <v>91315</v>
@@ -7648,7 +7648,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H251" t="n">
         <v>63937</v>
@@ -7677,7 +7677,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929880142212</v>
+        <v>4.75929832458496</v>
       </c>
       <c r="H252" t="n">
         <v>3333</v>
@@ -7793,7 +7793,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H256" t="n">
         <v>24390</v>
@@ -7967,7 +7967,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H262" t="n">
         <v>8895</v>
@@ -8025,7 +8025,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727933883667</v>
+        <v>4.81727981567383</v>
       </c>
       <c r="H264" t="n">
         <v>44506</v>
@@ -8054,7 +8054,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H265" t="n">
         <v>48189</v>
@@ -8083,7 +8083,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H266" t="n">
         <v>41705</v>
@@ -8141,7 +8141,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H268" t="n">
         <v>123324</v>
@@ -8228,7 +8228,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740127563477</v>
+        <v>4.95740079879761</v>
       </c>
       <c r="H271" t="n">
         <v>6925</v>
@@ -8315,7 +8315,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H274" t="n">
         <v>136710</v>
@@ -8344,7 +8344,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H275" t="n">
         <v>260348</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H278" t="n">
         <v>25684</v>
@@ -8547,7 +8547,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H282" t="n">
         <v>57869</v>
@@ -8924,7 +8924,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H295" t="n">
         <v>20573</v>
@@ -9040,7 +9040,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H299" t="n">
         <v>19695</v>
@@ -9243,7 +9243,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H306" t="n">
         <v>19157</v>
@@ -9359,7 +9359,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596162796021</v>
+        <v>5.28596115112305</v>
       </c>
       <c r="H310" t="n">
         <v>19428</v>
@@ -9417,7 +9417,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H312" t="n">
         <v>4283</v>
@@ -9533,7 +9533,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H316" t="n">
         <v>151029</v>
@@ -9620,7 +9620,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H319" t="n">
         <v>12312</v>
@@ -9649,7 +9649,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H320" t="n">
         <v>162473</v>
@@ -9765,7 +9765,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H324" t="n">
         <v>99309</v>
@@ -9852,7 +9852,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134479522705</v>
+        <v>5.13134527206421</v>
       </c>
       <c r="H327" t="n">
         <v>34058</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H329" t="n">
         <v>26368</v>
@@ -9968,7 +9968,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H331" t="n">
         <v>32218</v>
@@ -9997,7 +9997,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H332" t="n">
         <v>81218</v>
@@ -10026,7 +10026,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H333" t="n">
         <v>14865</v>
@@ -10258,7 +10258,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H341" t="n">
         <v>82529</v>
@@ -10287,7 +10287,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H342" t="n">
         <v>98211</v>
@@ -10461,7 +10461,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H348" t="n">
         <v>32626</v>
@@ -10635,7 +10635,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H354" t="n">
         <v>33125</v>
@@ -10751,7 +10751,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H358" t="n">
         <v>44086</v>
@@ -10867,7 +10867,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H362" t="n">
         <v>11155</v>
@@ -11041,7 +11041,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H368" t="n">
         <v>26463</v>
@@ -11099,7 +11099,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H370" t="n">
         <v>8841</v>
@@ -11186,7 +11186,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263502120972</v>
+        <v>4.23263454437256</v>
       </c>
       <c r="H373" t="n">
         <v>16343</v>
@@ -11302,7 +11302,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489645004272</v>
+        <v>4.45489692687988</v>
       </c>
       <c r="H377" t="n">
         <v>6689</v>
@@ -11418,7 +11418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H381" t="n">
         <v>31236</v>
@@ -11447,7 +11447,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H382" t="n">
         <v>9513</v>
@@ -11505,7 +11505,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H384" t="n">
         <v>12160</v>
@@ -11563,7 +11563,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H386" t="n">
         <v>5668</v>
@@ -11679,7 +11679,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H390" t="n">
         <v>5996</v>
@@ -11737,7 +11737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H392" t="n">
         <v>19706</v>
@@ -11795,7 +11795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H394" t="n">
         <v>18905</v>
@@ -12027,7 +12027,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H402" t="n">
         <v>20308</v>
@@ -12288,7 +12288,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H411" t="n">
         <v>7185</v>
@@ -12317,7 +12317,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H412" t="n">
         <v>7082</v>
@@ -12375,7 +12375,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H414" t="n">
         <v>49474</v>
@@ -12520,7 +12520,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H419" t="n">
         <v>7439</v>
@@ -12549,7 +12549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H420" t="n">
         <v>15236</v>
@@ -12607,7 +12607,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H422" t="n">
         <v>10351</v>
@@ -12636,7 +12636,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H423" t="n">
         <v>17376</v>
@@ -12810,7 +12810,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H429" t="n">
         <v>7532</v>
@@ -12868,7 +12868,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H431" t="n">
         <v>2225</v>
@@ -12984,7 +12984,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H435" t="n">
         <v>6281</v>
@@ -13013,7 +13013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H436" t="n">
         <v>7095</v>
@@ -13332,7 +13332,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H447" t="n">
         <v>1474</v>
@@ -13361,7 +13361,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H452" t="n">
         <v>5271</v>
@@ -13564,7 +13564,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H455" t="n">
         <v>7161</v>
@@ -13622,7 +13622,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H457" t="n">
         <v>13780</v>
@@ -13825,7 +13825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H464" t="n">
         <v>16567</v>
@@ -13883,7 +13883,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H466" t="n">
         <v>4338</v>
@@ -13912,7 +13912,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H467" t="n">
         <v>6710</v>
@@ -14028,7 +14028,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H471" t="n">
         <v>8536</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H487" t="n">
         <v>22603</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H491" t="n">
         <v>18592</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H493" t="n">
         <v>6171</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H494" t="n">
         <v>7707</v>
@@ -14927,7 +14927,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H502" t="n">
         <v>22877</v>
@@ -15130,7 +15130,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H509" t="n">
         <v>4568</v>
@@ -15304,7 +15304,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H515" t="n">
         <v>32842</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H517" t="n">
         <v>11854</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H518" t="n">
         <v>8330</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H522" t="n">
         <v>3006</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H524" t="n">
         <v>29907</v>
@@ -15623,7 +15623,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H526" t="n">
         <v>1616</v>
@@ -15855,7 +15855,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H534" t="n">
         <v>33564</v>
@@ -15884,7 +15884,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H535" t="n">
         <v>17947</v>
@@ -16116,7 +16116,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H543" t="n">
         <v>7536</v>
@@ -16145,7 +16145,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H544" t="n">
         <v>20916</v>
@@ -16203,7 +16203,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H546" t="n">
         <v>18431</v>
@@ -16232,7 +16232,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H547" t="n">
         <v>18024</v>
@@ -16261,7 +16261,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H548" t="n">
         <v>5276</v>
@@ -16290,7 +16290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H549" t="n">
         <v>11659</v>
@@ -16319,7 +16319,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H550" t="n">
         <v>9307</v>
@@ -16464,7 +16464,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H555" t="n">
         <v>211195</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H558" t="n">
         <v>68260</v>
@@ -16725,7 +16725,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H564" t="n">
         <v>44216</v>
@@ -16928,7 +16928,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H571" t="n">
         <v>137820</v>
@@ -16957,7 +16957,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H572" t="n">
         <v>46726</v>
@@ -17102,7 +17102,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H577" t="n">
         <v>232133</v>
@@ -17218,7 +17218,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H581" t="n">
         <v>183006</v>
@@ -17276,7 +17276,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H583" t="n">
         <v>110634</v>
@@ -17334,7 +17334,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H585" t="n">
         <v>83401</v>
@@ -17450,7 +17450,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H589" t="n">
         <v>48955</v>
@@ -17479,7 +17479,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H590" t="n">
         <v>54246</v>
@@ -17595,7 +17595,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H594" t="n">
         <v>141610</v>
@@ -17798,7 +17798,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H601" t="n">
         <v>21002</v>
@@ -17885,7 +17885,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H604" t="n">
         <v>23320</v>
@@ -17972,7 +17972,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H607" t="n">
         <v>46484</v>
@@ -18320,7 +18320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H619" t="n">
         <v>4323</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H623" t="n">
         <v>16947</v>
@@ -18465,7 +18465,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H624" t="n">
         <v>5894</v>
@@ -18523,7 +18523,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H626" t="n">
         <v>25679</v>
@@ -18639,7 +18639,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H630" t="n">
         <v>33871</v>
@@ -18697,7 +18697,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H632" t="n">
         <v>24188</v>
@@ -18784,7 +18784,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H635" t="n">
         <v>57265</v>
@@ -19074,7 +19074,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H645" t="n">
         <v>121832</v>
@@ -19103,7 +19103,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H646" t="n">
         <v>46978</v>
@@ -19480,7 +19480,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H659" t="n">
         <v>58410</v>
@@ -19509,7 +19509,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H660" t="n">
         <v>94430</v>
@@ -19538,7 +19538,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H661" t="n">
         <v>16435</v>
@@ -19625,7 +19625,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H664" t="n">
         <v>36840</v>
@@ -19770,7 +19770,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H669" t="n">
         <v>26798</v>
@@ -20002,7 +20002,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H677" t="n">
         <v>3700</v>
@@ -20031,7 +20031,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H678" t="n">
         <v>31808</v>
@@ -20060,7 +20060,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H679" t="n">
         <v>28368</v>
@@ -20118,7 +20118,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H681" t="n">
         <v>19635</v>
@@ -20321,7 +20321,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H688" t="n">
         <v>116323</v>
@@ -20350,7 +20350,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H689" t="n">
         <v>33063</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H690" t="n">
         <v>12669</v>
@@ -20582,7 +20582,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H697" t="n">
         <v>29126</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H698" t="n">
         <v>31677</v>
@@ -20669,7 +20669,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H700" t="n">
         <v>1753</v>
@@ -20698,7 +20698,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H701" t="n">
         <v>9847</v>
@@ -20727,7 +20727,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H702" t="n">
         <v>15481</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H703" t="n">
         <v>4841</v>
@@ -20785,7 +20785,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H704" t="n">
         <v>20397</v>
@@ -20814,7 +20814,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H705" t="n">
         <v>22265</v>
@@ -20872,7 +20872,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H707" t="n">
         <v>56099</v>
@@ -20901,7 +20901,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H708" t="n">
         <v>72110</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H710" t="n">
         <v>41126</v>
@@ -20988,7 +20988,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H711" t="n">
         <v>41372</v>
@@ -21075,7 +21075,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H714" t="n">
         <v>27761</v>
@@ -21249,7 +21249,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H720" t="n">
         <v>30084</v>
@@ -21365,7 +21365,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H724" t="n">
         <v>22097</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H725" t="n">
         <v>21424</v>
@@ -21481,7 +21481,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H728" t="n">
         <v>28785</v>
@@ -21539,7 +21539,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H730" t="n">
         <v>63831</v>
@@ -21568,7 +21568,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H731" t="n">
         <v>14790</v>
@@ -21626,7 +21626,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H733" t="n">
         <v>54638</v>
@@ -21655,7 +21655,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H734" t="n">
         <v>25806</v>
@@ -21771,7 +21771,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H738" t="n">
         <v>9042</v>
@@ -21858,7 +21858,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H741" t="n">
         <v>25001</v>
@@ -21945,7 +21945,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H744" t="n">
         <v>36541</v>
@@ -22119,7 +22119,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H750" t="n">
         <v>24595</v>
@@ -22148,7 +22148,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H751" t="n">
         <v>7605</v>
@@ -22177,7 +22177,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H752" t="n">
         <v>31505</v>
@@ -22235,7 +22235,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H754" t="n">
         <v>15983</v>
@@ -22293,7 +22293,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H756" t="n">
         <v>24115</v>
@@ -22322,7 +22322,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H757" t="n">
         <v>23156</v>
@@ -22351,7 +22351,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H758" t="n">
         <v>22826</v>
@@ -22380,7 +22380,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H759" t="n">
         <v>27789</v>
@@ -22554,7 +22554,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H765" t="n">
         <v>90704</v>
@@ -22641,7 +22641,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H768" t="n">
         <v>25948</v>
@@ -22699,7 +22699,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H770" t="n">
         <v>21002</v>
@@ -22728,7 +22728,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745719909668</v>
+        <v>5.81745672225952</v>
       </c>
       <c r="H771" t="n">
         <v>45095</v>
@@ -22757,7 +22757,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745719909668</v>
+        <v>5.81745672225952</v>
       </c>
       <c r="H772" t="n">
         <v>32302</v>
@@ -22786,7 +22786,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H773" t="n">
         <v>48385</v>
@@ -22873,7 +22873,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H776" t="n">
         <v>33170</v>
@@ -22902,7 +22902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H777" t="n">
         <v>140269</v>
@@ -22931,7 +22931,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H778" t="n">
         <v>51904</v>
@@ -22989,7 +22989,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H780" t="n">
         <v>26033</v>
@@ -23018,7 +23018,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H781" t="n">
         <v>69932</v>
@@ -23134,7 +23134,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H785" t="n">
         <v>21254</v>
@@ -23424,7 +23424,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H795" t="n">
         <v>129207</v>
@@ -23453,7 +23453,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H796" t="n">
         <v>74996</v>
@@ -23656,7 +23656,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H803" t="n">
         <v>95136</v>
@@ -23830,7 +23830,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H809" t="n">
         <v>42616</v>
@@ -23975,7 +23975,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H814" t="n">
         <v>147606</v>
@@ -24004,7 +24004,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H815" t="n">
         <v>20160</v>
@@ -24062,7 +24062,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H817" t="n">
         <v>48978</v>
@@ -24091,7 +24091,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H818" t="n">
         <v>17601</v>
@@ -24178,7 +24178,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H821" t="n">
         <v>17172</v>
@@ -24207,7 +24207,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H822" t="n">
         <v>21711</v>
@@ -24236,7 +24236,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H823" t="n">
         <v>13038</v>
@@ -24381,7 +24381,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H828" t="n">
         <v>13399</v>
@@ -24700,7 +24700,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H839" t="n">
         <v>10091</v>
@@ -24729,7 +24729,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H840" t="n">
         <v>20843</v>
@@ -24990,7 +24990,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725185394287</v>
+        <v>4.38725137710571</v>
       </c>
       <c r="H849" t="n">
         <v>88040</v>
@@ -25048,7 +25048,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H851" t="n">
         <v>61678</v>
@@ -25077,7 +25077,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H852" t="n">
         <v>25922</v>
@@ -25222,7 +25222,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H857" t="n">
         <v>26131</v>
@@ -25309,7 +25309,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H860" t="n">
         <v>25865</v>
@@ -25483,7 +25483,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H866" t="n">
         <v>10855</v>
@@ -25541,7 +25541,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H868" t="n">
         <v>4022</v>
@@ -25570,7 +25570,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.6240086555481</v>
+        <v>4.62400817871094</v>
       </c>
       <c r="H869" t="n">
         <v>9713</v>
@@ -25628,7 +25628,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602716445923</v>
+        <v>4.56602764129639</v>
       </c>
       <c r="H871" t="n">
         <v>3876</v>
@@ -25802,7 +25802,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602716445923</v>
+        <v>4.56602764129639</v>
       </c>
       <c r="H877" t="n">
         <v>1609</v>
@@ -26179,7 +26179,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H890" t="n">
         <v>21852</v>
@@ -26208,7 +26208,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309242248535</v>
+        <v>4.36309289932251</v>
       </c>
       <c r="H891" t="n">
         <v>19273</v>
@@ -26237,7 +26237,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H892" t="n">
         <v>9208</v>
@@ -26295,7 +26295,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H894" t="n">
         <v>13445</v>
@@ -26324,7 +26324,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645708084106</v>
+        <v>4.26645755767822</v>
       </c>
       <c r="H895" t="n">
         <v>43685</v>
@@ -26440,7 +26440,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H899" t="n">
         <v>27960</v>
@@ -26498,7 +26498,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095245361328</v>
+        <v>4.28095197677612</v>
       </c>
       <c r="H901" t="n">
         <v>33825</v>
@@ -26672,7 +26672,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.04419565200806</v>
+        <v>4.0441951751709</v>
       </c>
       <c r="H907" t="n">
         <v>15181</v>
@@ -26730,7 +26730,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621416091919</v>
+        <v>3.98621439933777</v>
       </c>
       <c r="H909" t="n">
         <v>14992</v>
@@ -26904,7 +26904,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H915" t="n">
         <v>53863</v>
@@ -27049,7 +27049,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H920" t="n">
         <v>5004</v>
@@ -27078,7 +27078,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H921" t="n">
         <v>4290</v>
@@ -27136,7 +27136,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H923" t="n">
         <v>8482</v>
@@ -27165,7 +27165,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453207015991</v>
+        <v>4.03453254699707</v>
       </c>
       <c r="H924" t="n">
         <v>16764</v>
@@ -27513,7 +27513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H936" t="n">
         <v>1516</v>
@@ -27629,7 +27629,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H940" t="n">
         <v>4899</v>
@@ -27658,7 +27658,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.8557562828064</v>
+        <v>3.85575652122498</v>
       </c>
       <c r="H941" t="n">
         <v>56027</v>
@@ -27716,7 +27716,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H943" t="n">
         <v>7945</v>
@@ -27861,7 +27861,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H948" t="n">
         <v>9054</v>
@@ -27890,7 +27890,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H949" t="n">
         <v>974</v>
@@ -28006,7 +28006,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H953" t="n">
         <v>15215</v>
@@ -28122,7 +28122,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193398475647</v>
+        <v>3.82193374633789</v>
       </c>
       <c r="H957" t="n">
         <v>1040</v>
@@ -28151,7 +28151,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327965736389</v>
+        <v>3.78327989578247</v>
       </c>
       <c r="H958" t="n">
         <v>5878</v>
@@ -28296,7 +28296,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327965736389</v>
+        <v>3.78327989578247</v>
       </c>
       <c r="H963" t="n">
         <v>1069</v>
@@ -28325,7 +28325,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H964" t="n">
         <v>4985</v>
@@ -28354,7 +28354,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H965" t="n">
         <v>1586</v>
@@ -28412,7 +28412,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H967" t="n">
         <v>22825</v>
@@ -28499,7 +28499,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945759773254</v>
+        <v>3.74945735931396</v>
       </c>
       <c r="H970" t="n">
         <v>1519</v>
@@ -28615,7 +28615,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H974" t="n">
         <v>61487</v>
@@ -28702,7 +28702,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.8557562828064</v>
+        <v>3.85575652122498</v>
       </c>
       <c r="H977" t="n">
         <v>13657</v>
@@ -28731,7 +28731,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H978" t="n">
         <v>26282</v>
@@ -28818,7 +28818,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H981" t="n">
         <v>4451</v>
@@ -28876,7 +28876,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H983" t="n">
         <v>36877</v>
@@ -28905,7 +28905,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H984" t="n">
         <v>1838</v>
@@ -28963,7 +28963,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H986" t="n">
         <v>12068</v>
@@ -28992,7 +28992,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H987" t="n">
         <v>26097</v>
@@ -29021,7 +29021,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945759773254</v>
+        <v>3.74945735931396</v>
       </c>
       <c r="H988" t="n">
         <v>6234</v>
@@ -29224,7 +29224,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H995" t="n">
         <v>11228</v>
@@ -29253,7 +29253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H996" t="n">
         <v>4330</v>
@@ -29282,7 +29282,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H997" t="n">
         <v>8092</v>
@@ -29398,7 +29398,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.96688747406006</v>
+        <v>3.9668869972229</v>
       </c>
       <c r="H1001" t="n">
         <v>517</v>
@@ -29514,7 +29514,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856908798218</v>
+        <v>3.91856932640076</v>
       </c>
       <c r="H1005" t="n">
         <v>15349</v>
@@ -29804,7 +29804,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1015" t="n">
         <v>20471</v>
@@ -29891,7 +29891,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1018" t="n">
         <v>24364</v>
@@ -29920,7 +29920,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1019" t="n">
         <v>19551</v>
@@ -30007,7 +30007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1022" t="n">
         <v>3870</v>
@@ -30616,7 +30616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1043" t="n">
         <v>7439</v>
@@ -30703,7 +30703,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1046" t="n">
         <v>15720</v>
@@ -30732,7 +30732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1047" t="n">
         <v>13320</v>
@@ -30790,7 +30790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1049" t="n">
         <v>1434</v>
@@ -30848,7 +30848,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820470809937</v>
+        <v>3.49820494651794</v>
       </c>
       <c r="H1051" t="n">
         <v>22296</v>
@@ -30906,7 +30906,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1053" t="n">
         <v>16504</v>
@@ -30935,7 +30935,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1054" t="n">
         <v>12412</v>
@@ -30993,7 +30993,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1056" t="n">
         <v>12576</v>
@@ -31051,7 +31051,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H1058" t="n">
         <v>9513</v>
@@ -31225,7 +31225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1064" t="n">
         <v>11552</v>
@@ -31254,7 +31254,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H1065" t="n">
         <v>34413</v>
@@ -31283,7 +31283,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135464668274</v>
+        <v>3.55135440826416</v>
       </c>
       <c r="H1066" t="n">
         <v>64042</v>
@@ -31341,7 +31341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1068" t="n">
         <v>24424</v>
@@ -31399,7 +31399,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1070" t="n">
         <v>18126</v>
@@ -31457,7 +31457,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.5368595123291</v>
+        <v>3.53685927391052</v>
       </c>
       <c r="H1072" t="n">
         <v>26947</v>
@@ -31515,7 +31515,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1074" t="n">
         <v>76053</v>
@@ -31689,7 +31689,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1080" t="n">
         <v>11888</v>
@@ -31718,7 +31718,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.59967231750488</v>
+        <v>3.5996720790863</v>
       </c>
       <c r="H1081" t="n">
         <v>87040</v>
@@ -31776,7 +31776,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1083" t="n">
         <v>27634</v>
@@ -31805,7 +31805,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135464668274</v>
+        <v>3.55135440826416</v>
       </c>
       <c r="H1084" t="n">
         <v>183394</v>
@@ -31863,7 +31863,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1086" t="n">
         <v>39968</v>
@@ -31892,7 +31892,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1087" t="n">
         <v>19044</v>
@@ -31950,7 +31950,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59967231750488</v>
+        <v>3.5996720790863</v>
       </c>
       <c r="H1089" t="n">
         <v>21496</v>
@@ -32037,7 +32037,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1092" t="n">
         <v>4199</v>
@@ -32095,7 +32095,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1094" t="n">
         <v>2930</v>
@@ -32124,7 +32124,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1095" t="n">
         <v>17824</v>
@@ -32414,7 +32414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1105" t="n">
         <v>8012</v>
@@ -32501,7 +32501,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1108" t="n">
         <v>20364</v>
@@ -32617,7 +32617,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1112" t="n">
         <v>8014</v>
@@ -32646,7 +32646,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H1113" t="n">
         <v>5992</v>
@@ -32791,7 +32791,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1118" t="n">
         <v>7468</v>
@@ -32878,7 +32878,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1121" t="n">
         <v>7108</v>
@@ -32907,7 +32907,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1122" t="n">
         <v>3566</v>
@@ -32965,7 +32965,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1124" t="n">
         <v>6159</v>
@@ -32994,7 +32994,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1125" t="n">
         <v>36559</v>
@@ -33023,7 +33023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1126" t="n">
         <v>5854</v>
@@ -33081,7 +33081,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1128" t="n">
         <v>85216</v>
@@ -33110,7 +33110,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1129" t="n">
         <v>44308</v>
@@ -33168,7 +33168,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1131" t="n">
         <v>2341</v>
@@ -33197,7 +33197,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1132" t="n">
         <v>13385</v>
@@ -33371,7 +33371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1138" t="n">
         <v>23416</v>
@@ -33516,7 +33516,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H1143" t="n">
         <v>14293</v>
@@ -33574,7 +33574,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1145" t="n">
         <v>44949</v>
@@ -33719,7 +33719,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H1150" t="n">
         <v>7061</v>
@@ -33748,7 +33748,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H1151" t="n">
         <v>5770</v>
@@ -33777,7 +33777,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1152" t="n">
         <v>12871</v>
@@ -33806,7 +33806,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1153" t="n">
         <v>21159</v>
@@ -33835,7 +33835,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1154" t="n">
         <v>63339</v>
@@ -33864,7 +33864,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1155" t="n">
         <v>13966</v>
@@ -34125,7 +34125,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1164" t="n">
         <v>8374</v>
@@ -34154,7 +34154,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1165" t="n">
         <v>8257</v>
@@ -34241,7 +34241,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1168" t="n">
         <v>51543</v>
@@ -34299,7 +34299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1170" t="n">
         <v>8138</v>
@@ -34415,7 +34415,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1174" t="n">
         <v>18764</v>
@@ -34589,7 +34589,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1180" t="n">
         <v>22131</v>
@@ -34705,7 +34705,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1184" t="n">
         <v>1634</v>
@@ -34734,7 +34734,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1185" t="n">
         <v>1460</v>
@@ -34792,7 +34792,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1187" t="n">
         <v>21143</v>
@@ -34821,7 +34821,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1188" t="n">
         <v>8937</v>
@@ -34850,7 +34850,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1189" t="n">
         <v>9771</v>
@@ -34908,7 +34908,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1191" t="n">
         <v>3139</v>
@@ -34966,7 +34966,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1193" t="n">
         <v>23650</v>
@@ -34995,7 +34995,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1194" t="n">
         <v>30769</v>
@@ -35024,7 +35024,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1195" t="n">
         <v>53170</v>
@@ -35053,7 +35053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1196" t="n">
         <v>8141</v>
@@ -35082,7 +35082,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1197" t="n">
         <v>18888</v>
@@ -35111,7 +35111,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1198" t="n">
         <v>2167</v>
@@ -35140,7 +35140,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1199" t="n">
         <v>21694</v>
@@ -35169,7 +35169,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1200" t="n">
         <v>30561</v>
@@ -35227,7 +35227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1202" t="n">
         <v>13802</v>
@@ -35285,7 +35285,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1204" t="n">
         <v>39802</v>
@@ -35430,7 +35430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1209" t="n">
         <v>13920</v>
@@ -35952,7 +35952,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H1227" t="n">
         <v>11126</v>
@@ -36010,7 +36010,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263502120972</v>
+        <v>4.23263454437256</v>
       </c>
       <c r="H1229" t="n">
         <v>30135</v>
@@ -36184,7 +36184,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1235" t="n">
         <v>87770</v>
@@ -36242,7 +36242,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1237" t="n">
         <v>86783</v>
@@ -36271,7 +36271,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095245361328</v>
+        <v>4.28095197677612</v>
       </c>
       <c r="H1238" t="n">
         <v>10697</v>
@@ -36300,7 +36300,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1239" t="n">
         <v>633742</v>
@@ -36387,7 +36387,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1242" t="n">
         <v>33483</v>
@@ -36416,7 +36416,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297096252441</v>
+        <v>4.22297143936157</v>
       </c>
       <c r="H1243" t="n">
         <v>111404</v>
@@ -36474,7 +36474,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1245" t="n">
         <v>71817</v>
@@ -36503,7 +36503,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1246" t="n">
         <v>15207</v>
@@ -36561,7 +36561,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1248" t="n">
         <v>263769</v>
@@ -36648,7 +36648,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H1251" t="n">
         <v>22609</v>
@@ -36822,7 +36822,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1257" t="n">
         <v>38711</v>
@@ -36909,7 +36909,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1260" t="n">
         <v>48866</v>
@@ -36938,7 +36938,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1261" t="n">
         <v>88377</v>
@@ -37054,7 +37054,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1265" t="n">
         <v>106306</v>
@@ -37547,7 +37547,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1282" t="n">
         <v>41916</v>
@@ -37663,7 +37663,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1286" t="n">
         <v>18275</v>
@@ -37692,7 +37692,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1287" t="n">
         <v>38266</v>
@@ -37721,7 +37721,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1288" t="n">
         <v>44950</v>
@@ -37750,7 +37750,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1289" t="n">
         <v>154179</v>
@@ -37808,7 +37808,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1291" t="n">
         <v>48801</v>
@@ -37895,7 +37895,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1294" t="n">
         <v>76505</v>
@@ -38011,7 +38011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1298" t="n">
         <v>108894</v>
@@ -38040,7 +38040,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1299" t="n">
         <v>13424</v>
@@ -38098,7 +38098,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1301" t="n">
         <v>3761</v>
@@ -38127,7 +38127,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725185394287</v>
+        <v>4.38725137710571</v>
       </c>
       <c r="H1302" t="n">
         <v>18383</v>
@@ -38272,7 +38272,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1307" t="n">
         <v>33977</v>
@@ -38330,7 +38330,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1309" t="n">
         <v>8950</v>
@@ -38562,7 +38562,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1317" t="n">
         <v>2395</v>
@@ -38620,7 +38620,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1319" t="n">
         <v>2013</v>
@@ -38649,7 +38649,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1320" t="n">
         <v>19847</v>
@@ -38678,7 +38678,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1321" t="n">
         <v>6721</v>
@@ -38707,7 +38707,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1322" t="n">
         <v>4183885</v>
@@ -38968,7 +38968,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1331" t="n">
         <v>17017</v>
@@ -38997,7 +38997,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1332" t="n">
         <v>17023</v>
@@ -39113,7 +39113,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1336" t="n">
         <v>7875</v>
@@ -39171,7 +39171,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1338" t="n">
         <v>579091</v>
@@ -39200,7 +39200,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1339" t="n">
         <v>13097</v>
@@ -39258,7 +39258,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1341" t="n">
         <v>18512</v>
@@ -39345,7 +39345,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1344" t="n">
         <v>142420</v>
@@ -39374,7 +39374,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1345" t="n">
         <v>32214</v>
@@ -39403,7 +39403,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1346" t="n">
         <v>117615</v>
@@ -39461,7 +39461,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1348" t="n">
         <v>45261</v>
@@ -39490,7 +39490,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1349" t="n">
         <v>53301</v>
@@ -39519,7 +39519,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1350" t="n">
         <v>53244</v>
@@ -39548,7 +39548,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1351" t="n">
         <v>128034</v>
@@ -39751,7 +39751,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1358" t="n">
         <v>28701</v>
@@ -39954,7 +39954,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1365" t="n">
         <v>13059</v>
@@ -40012,7 +40012,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1367" t="n">
         <v>15645</v>
@@ -40041,7 +40041,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1368" t="n">
         <v>36938</v>
@@ -40070,7 +40070,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1369" t="n">
         <v>30397</v>
@@ -40099,7 +40099,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1370" t="n">
         <v>59503</v>
@@ -40128,7 +40128,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1371" t="n">
         <v>7128</v>
@@ -40186,7 +40186,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1373" t="n">
         <v>53763</v>
@@ -40244,7 +40244,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1375" t="n">
         <v>80223</v>
@@ -40360,7 +40360,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1379" t="n">
         <v>35399</v>
@@ -40389,7 +40389,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1380" t="n">
         <v>66631</v>
@@ -40418,7 +40418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1381" t="n">
         <v>36618</v>
@@ -40476,7 +40476,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1383" t="n">
         <v>9917</v>
@@ -40563,7 +40563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1386" t="n">
         <v>14411</v>
@@ -40592,7 +40592,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1387" t="n">
         <v>5736</v>
@@ -40650,7 +40650,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1389" t="n">
         <v>33151</v>
@@ -40708,7 +40708,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1391" t="n">
         <v>172952</v>
@@ -40737,7 +40737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1392" t="n">
         <v>27304</v>
@@ -40766,7 +40766,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1393" t="n">
         <v>10573</v>
@@ -40824,7 +40824,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1395" t="n">
         <v>16020</v>
@@ -40882,7 +40882,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1397" t="n">
         <v>25629</v>
@@ -40911,7 +40911,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1398" t="n">
         <v>21495</v>
@@ -40940,7 +40940,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1399" t="n">
         <v>11491</v>
@@ -40969,7 +40969,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1400" t="n">
         <v>70839</v>
@@ -41027,7 +41027,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1402" t="n">
         <v>25324</v>
@@ -41346,7 +41346,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1413" t="n">
         <v>23278</v>
@@ -41433,7 +41433,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1416" t="n">
         <v>86929</v>
@@ -41578,7 +41578,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1421" t="n">
         <v>84292</v>
@@ -41636,7 +41636,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1423" t="n">
         <v>17733</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1430" t="n">
         <v>17929</v>
@@ -42100,7 +42100,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1439" t="n">
         <v>30849</v>
@@ -42245,7 +42245,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1444" t="n">
         <v>16400</v>
@@ -42448,7 +42448,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1451" t="n">
         <v>10674</v>
@@ -42593,7 +42593,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1456" t="n">
         <v>14950</v>
@@ -42651,7 +42651,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1458" t="n">
         <v>53885</v>
@@ -42680,7 +42680,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1459" t="n">
         <v>43894</v>
@@ -42825,7 +42825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1464" t="n">
         <v>6023</v>
@@ -42854,7 +42854,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1465" t="n">
         <v>13746</v>
@@ -42941,7 +42941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1468" t="n">
         <v>17342</v>
@@ -43318,7 +43318,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1481" t="n">
         <v>4088</v>
@@ -43434,7 +43434,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1485" t="n">
         <v>18559</v>
@@ -43463,7 +43463,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1486" t="n">
         <v>5313</v>
@@ -43695,7 +43695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1494" t="n">
         <v>10058</v>
@@ -43724,7 +43724,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1495" t="n">
         <v>6566</v>
@@ -43898,7 +43898,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1501" t="n">
         <v>24701</v>
@@ -43927,7 +43927,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1502" t="n">
         <v>13712</v>
@@ -43985,7 +43985,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1504" t="n">
         <v>17967</v>
@@ -44014,7 +44014,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1505" t="n">
         <v>12753</v>
@@ -44043,7 +44043,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1506" t="n">
         <v>4017</v>
@@ -44304,7 +44304,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1515" t="n">
         <v>32760</v>
@@ -44420,7 +44420,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1519" t="n">
         <v>13224</v>
@@ -44449,7 +44449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1520" t="n">
         <v>15389</v>
@@ -44536,7 +44536,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H1523" t="n">
         <v>23568</v>
@@ -44652,7 +44652,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1527" t="n">
         <v>12057</v>
@@ -44681,7 +44681,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1528" t="n">
         <v>10102</v>
@@ -44710,7 +44710,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H1529" t="n">
         <v>11999</v>
@@ -44768,7 +44768,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H1531" t="n">
         <v>23916</v>
@@ -44797,7 +44797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1532" t="n">
         <v>53597</v>
@@ -44826,7 +44826,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1533" t="n">
         <v>35027</v>
@@ -44913,7 +44913,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H1536" t="n">
         <v>27398</v>
@@ -45087,7 +45087,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1542" t="n">
         <v>10776</v>
@@ -45290,7 +45290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H1549" t="n">
         <v>17670</v>
@@ -45348,7 +45348,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H1551" t="n">
         <v>6270</v>
@@ -45551,7 +45551,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1558" t="n">
         <v>9714</v>
@@ -45580,7 +45580,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1559" t="n">
         <v>9223</v>
@@ -45667,7 +45667,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1562" t="n">
         <v>3769</v>
@@ -45870,7 +45870,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1569" t="n">
         <v>59041</v>
@@ -45928,7 +45928,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1571" t="n">
         <v>19659</v>
@@ -45986,7 +45986,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1573" t="n">
         <v>6033</v>
@@ -46102,7 +46102,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1577" t="n">
         <v>16481</v>
@@ -46131,7 +46131,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1578" t="n">
         <v>16827</v>
@@ -46247,7 +46247,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1582" t="n">
         <v>12336</v>
@@ -46537,7 +46537,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1592" t="n">
         <v>40020</v>
@@ -46566,7 +46566,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1593" t="n">
         <v>20842</v>
@@ -47175,7 +47175,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1614" t="n">
         <v>15568</v>
@@ -47262,7 +47262,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1617" t="n">
         <v>1706</v>
@@ -47320,7 +47320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1619" t="n">
         <v>97926</v>
@@ -47349,7 +47349,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1620" t="n">
         <v>14080</v>
@@ -47378,7 +47378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1621" t="n">
         <v>19839</v>
@@ -47436,7 +47436,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1623" t="n">
         <v>16886</v>
@@ -47552,7 +47552,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605512619019</v>
+        <v>4.99605560302734</v>
       </c>
       <c r="H1627" t="n">
         <v>60722</v>
@@ -47581,7 +47581,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1628" t="n">
         <v>24838</v>
@@ -47610,7 +47610,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1629" t="n">
         <v>21313</v>
@@ -47639,7 +47639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1630" t="n">
         <v>23268</v>
@@ -47668,7 +47668,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1631" t="n">
         <v>2356</v>
@@ -47697,7 +47697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1632" t="n">
         <v>26681</v>
@@ -47755,7 +47755,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H1634" t="n">
         <v>18116</v>
@@ -47842,7 +47842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1637" t="n">
         <v>9629</v>
@@ -47900,7 +47900,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H1639" t="n">
         <v>10513</v>
@@ -47929,7 +47929,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1640" t="n">
         <v>5633</v>
@@ -47987,7 +47987,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H1642" t="n">
         <v>29183</v>
@@ -58781,6 +58781,64 @@
         <v>41592</v>
       </c>
       <c r="I2014" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2015" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2015" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="G2015" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="H2015" t="n">
+        <v>19859</v>
+      </c>
+      <c r="I2015" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2016" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2016" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="D2016" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="E2016" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="G2016" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="H2016" t="n">
+        <v>13322</v>
+      </c>
+      <c r="I2016" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835204124451</v>
+        <v>3.50835180282593</v>
       </c>
       <c r="H5" t="n">
         <v>168607</v>
@@ -572,7 +572,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290766716003</v>
+        <v>3.59290790557861</v>
       </c>
       <c r="H7" t="n">
         <v>115707</v>
@@ -630,7 +630,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555630683899</v>
+        <v>3.54555654525757</v>
       </c>
       <c r="H9" t="n">
         <v>18987</v>
@@ -717,7 +717,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694540023804</v>
+        <v>3.47694516181946</v>
       </c>
       <c r="H12" t="n">
         <v>25574</v>
@@ -775,7 +775,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018098831177</v>
+        <v>3.47018074989319</v>
       </c>
       <c r="H14" t="n">
         <v>14046</v>
@@ -804,7 +804,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H15" t="n">
         <v>25673</v>
@@ -833,7 +833,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H16" t="n">
         <v>17829</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H20" t="n">
         <v>24337</v>
@@ -1007,7 +1007,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H22" t="n">
         <v>15060</v>
@@ -1065,7 +1065,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710980415344</v>
+        <v>3.58710956573486</v>
       </c>
       <c r="H24" t="n">
         <v>31246</v>
@@ -1297,7 +1297,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299379348755</v>
+        <v>3.53299355506897</v>
       </c>
       <c r="H32" t="n">
         <v>12155</v>
@@ -1326,7 +1326,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H33" t="n">
         <v>2992</v>
@@ -1384,7 +1384,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185546875</v>
+        <v>3.65185570716858</v>
       </c>
       <c r="H35" t="n">
         <v>9616</v>
@@ -1500,7 +1500,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H39" t="n">
         <v>33223</v>
@@ -1558,7 +1558,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464311599731</v>
+        <v>3.84464335441589</v>
       </c>
       <c r="H41" t="n">
         <v>67310</v>
@@ -1674,7 +1674,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869815826416</v>
+        <v>3.82869839668274</v>
       </c>
       <c r="H45" t="n">
         <v>15050</v>
@@ -1761,7 +1761,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243480682373</v>
+        <v>3.92243504524231</v>
       </c>
       <c r="H48" t="n">
         <v>7064</v>
@@ -1848,7 +1848,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H51" t="n">
         <v>10244</v>
@@ -2138,7 +2138,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863742828369</v>
+        <v>3.75863766670227</v>
       </c>
       <c r="H61" t="n">
         <v>18963</v>
@@ -2167,7 +2167,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H62" t="n">
         <v>25241</v>
@@ -2254,7 +2254,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H65" t="n">
         <v>14098</v>
@@ -2283,7 +2283,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364147186279</v>
+        <v>3.64364123344421</v>
       </c>
       <c r="H66" t="n">
         <v>24444</v>
@@ -2312,7 +2312,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H67" t="n">
         <v>14328</v>
@@ -2457,7 +2457,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422080993652</v>
+        <v>3.91422057151794</v>
       </c>
       <c r="H72" t="n">
         <v>37886</v>
@@ -2544,7 +2544,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H75" t="n">
         <v>61176</v>
@@ -2573,7 +2573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H76" t="n">
         <v>4871</v>
@@ -2631,7 +2631,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615319252014</v>
+        <v>3.91615343093872</v>
       </c>
       <c r="H78" t="n">
         <v>28408</v>
@@ -2660,7 +2660,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331522941589</v>
+        <v>3.98331546783447</v>
       </c>
       <c r="H79" t="n">
         <v>15491</v>
@@ -2689,7 +2689,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H80" t="n">
         <v>8568</v>
@@ -2718,7 +2718,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.95287489891052</v>
+        <v>3.9528751373291</v>
       </c>
       <c r="H81" t="n">
         <v>11304</v>
@@ -2747,7 +2747,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354797363281</v>
+        <v>3.93354773521423</v>
       </c>
       <c r="H82" t="n">
         <v>1333</v>
@@ -2805,7 +2805,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445379257202</v>
+        <v>3.86445355415344</v>
       </c>
       <c r="H84" t="n">
         <v>14743</v>
@@ -2892,7 +2892,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H87" t="n">
         <v>16436</v>
@@ -2921,7 +2921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H88" t="n">
         <v>70067</v>
@@ -2950,7 +2950,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H89" t="n">
         <v>20248</v>
@@ -2979,7 +2979,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H90" t="n">
         <v>9804</v>
@@ -3008,7 +3008,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H91" t="n">
         <v>8029</v>
@@ -3124,7 +3124,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H95" t="n">
         <v>6789</v>
@@ -3153,7 +3153,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H96" t="n">
         <v>16453</v>
@@ -3182,7 +3182,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H97" t="n">
         <v>13893</v>
@@ -3211,7 +3211,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H98" t="n">
         <v>34445</v>
@@ -3269,7 +3269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H100" t="n">
         <v>5569</v>
@@ -3327,7 +3327,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H102" t="n">
         <v>17175</v>
@@ -3385,7 +3385,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H104" t="n">
         <v>4792</v>
@@ -3443,7 +3443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H106" t="n">
         <v>12618</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H107" t="n">
         <v>7801</v>
@@ -3530,7 +3530,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H109" t="n">
         <v>27377</v>
@@ -3559,7 +3559,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H110" t="n">
         <v>9652</v>
@@ -3588,7 +3588,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H111" t="n">
         <v>22427</v>
@@ -3646,7 +3646,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H113" t="n">
         <v>5635</v>
@@ -3675,7 +3675,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H114" t="n">
         <v>12247</v>
@@ -3704,7 +3704,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H115" t="n">
         <v>46534</v>
@@ -3762,7 +3762,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H117" t="n">
         <v>14370</v>
@@ -3791,7 +3791,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H118" t="n">
         <v>20871</v>
@@ -3849,7 +3849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H120" t="n">
         <v>51861</v>
@@ -3907,7 +3907,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H122" t="n">
         <v>24632</v>
@@ -3965,7 +3965,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H124" t="n">
         <v>9251</v>
@@ -4023,7 +4023,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H126" t="n">
         <v>23445</v>
@@ -4052,7 +4052,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H127" t="n">
         <v>13288</v>
@@ -4226,7 +4226,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H133" t="n">
         <v>69275</v>
@@ -4255,7 +4255,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.6866443157196</v>
+        <v>3.68664455413818</v>
       </c>
       <c r="H134" t="n">
         <v>83826</v>
@@ -4284,7 +4284,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H135" t="n">
         <v>38411</v>
@@ -4342,7 +4342,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H137" t="n">
         <v>28361</v>
@@ -4371,7 +4371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H138" t="n">
         <v>16251</v>
@@ -4400,7 +4400,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H139" t="n">
         <v>24663</v>
@@ -4661,7 +4661,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H148" t="n">
         <v>6408</v>
@@ -4690,7 +4690,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H149" t="n">
         <v>17007</v>
@@ -4748,7 +4748,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H151" t="n">
         <v>51508</v>
@@ -4893,7 +4893,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H156" t="n">
         <v>57059</v>
@@ -4951,7 +4951,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H158" t="n">
         <v>51199</v>
@@ -5821,7 +5821,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251308441162</v>
+        <v>4.09251356124878</v>
       </c>
       <c r="H188" t="n">
         <v>3584</v>
@@ -5995,7 +5995,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H194" t="n">
         <v>11423</v>
@@ -6459,7 +6459,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H210" t="n">
         <v>4401</v>
@@ -6546,7 +6546,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H213" t="n">
         <v>14225</v>
@@ -6720,7 +6720,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H219" t="n">
         <v>109205</v>
@@ -6981,7 +6981,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H228" t="n">
         <v>32762</v>
@@ -7358,7 +7358,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501791000366</v>
+        <v>4.59501838684082</v>
       </c>
       <c r="H241" t="n">
         <v>82951</v>
@@ -7416,7 +7416,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H243" t="n">
         <v>10325</v>
@@ -7445,7 +7445,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H244" t="n">
         <v>8300</v>
@@ -7590,7 +7590,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H249" t="n">
         <v>50047</v>
@@ -7619,7 +7619,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H250" t="n">
         <v>91315</v>
@@ -7648,7 +7648,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H251" t="n">
         <v>63937</v>
@@ -7677,7 +7677,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929832458496</v>
+        <v>4.75929880142212</v>
       </c>
       <c r="H252" t="n">
         <v>3333</v>
@@ -7793,7 +7793,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H256" t="n">
         <v>24390</v>
@@ -7967,7 +7967,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H262" t="n">
         <v>8895</v>
@@ -8025,7 +8025,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727981567383</v>
+        <v>4.81727933883667</v>
       </c>
       <c r="H264" t="n">
         <v>44506</v>
@@ -8054,7 +8054,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H265" t="n">
         <v>48189</v>
@@ -8083,7 +8083,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H266" t="n">
         <v>41705</v>
@@ -8141,7 +8141,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H268" t="n">
         <v>123324</v>
@@ -8228,7 +8228,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740079879761</v>
+        <v>4.95740127563477</v>
       </c>
       <c r="H271" t="n">
         <v>6925</v>
@@ -8315,7 +8315,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H274" t="n">
         <v>136710</v>
@@ -8344,7 +8344,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H275" t="n">
         <v>260348</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H278" t="n">
         <v>25684</v>
@@ -8547,7 +8547,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H282" t="n">
         <v>57869</v>
@@ -8924,7 +8924,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H295" t="n">
         <v>20573</v>
@@ -9040,7 +9040,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H299" t="n">
         <v>19695</v>
@@ -9243,7 +9243,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H306" t="n">
         <v>19157</v>
@@ -9359,7 +9359,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596115112305</v>
+        <v>5.28596162796021</v>
       </c>
       <c r="H310" t="n">
         <v>19428</v>
@@ -9417,7 +9417,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H312" t="n">
         <v>4283</v>
@@ -9533,7 +9533,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H316" t="n">
         <v>151029</v>
@@ -9620,7 +9620,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H319" t="n">
         <v>12312</v>
@@ -9649,7 +9649,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H320" t="n">
         <v>162473</v>
@@ -9765,7 +9765,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H324" t="n">
         <v>99309</v>
@@ -9852,7 +9852,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134527206421</v>
+        <v>5.13134479522705</v>
       </c>
       <c r="H327" t="n">
         <v>34058</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H329" t="n">
         <v>26368</v>
@@ -9968,7 +9968,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H331" t="n">
         <v>32218</v>
@@ -9997,7 +9997,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H332" t="n">
         <v>81218</v>
@@ -10026,7 +10026,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H333" t="n">
         <v>14865</v>
@@ -10258,7 +10258,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H341" t="n">
         <v>82529</v>
@@ -10287,7 +10287,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H342" t="n">
         <v>98211</v>
@@ -10461,7 +10461,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H348" t="n">
         <v>32626</v>
@@ -10635,7 +10635,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H354" t="n">
         <v>33125</v>
@@ -10751,7 +10751,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H358" t="n">
         <v>44086</v>
@@ -10867,7 +10867,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H362" t="n">
         <v>11155</v>
@@ -11041,7 +11041,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H368" t="n">
         <v>26463</v>
@@ -11099,7 +11099,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H370" t="n">
         <v>8841</v>
@@ -11186,7 +11186,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H373" t="n">
         <v>16343</v>
@@ -11302,7 +11302,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489692687988</v>
+        <v>4.45489645004272</v>
       </c>
       <c r="H377" t="n">
         <v>6689</v>
@@ -11418,7 +11418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H381" t="n">
         <v>31236</v>
@@ -11447,7 +11447,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H382" t="n">
         <v>9513</v>
@@ -11505,7 +11505,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H384" t="n">
         <v>12160</v>
@@ -11563,7 +11563,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H386" t="n">
         <v>5668</v>
@@ -11679,7 +11679,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H390" t="n">
         <v>5996</v>
@@ -11737,7 +11737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H392" t="n">
         <v>19706</v>
@@ -11795,7 +11795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H394" t="n">
         <v>18905</v>
@@ -12027,7 +12027,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H402" t="n">
         <v>20308</v>
@@ -12288,7 +12288,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H411" t="n">
         <v>7185</v>
@@ -12317,7 +12317,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H412" t="n">
         <v>7082</v>
@@ -12375,7 +12375,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H414" t="n">
         <v>49474</v>
@@ -12520,7 +12520,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H419" t="n">
         <v>7439</v>
@@ -12549,7 +12549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H420" t="n">
         <v>15236</v>
@@ -12607,7 +12607,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H422" t="n">
         <v>10351</v>
@@ -12636,7 +12636,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H423" t="n">
         <v>17376</v>
@@ -12810,7 +12810,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H429" t="n">
         <v>7532</v>
@@ -12868,7 +12868,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H431" t="n">
         <v>2225</v>
@@ -12984,7 +12984,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H435" t="n">
         <v>6281</v>
@@ -13013,7 +13013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H436" t="n">
         <v>7095</v>
@@ -13332,7 +13332,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H447" t="n">
         <v>1474</v>
@@ -13361,7 +13361,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H452" t="n">
         <v>5271</v>
@@ -13564,7 +13564,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H455" t="n">
         <v>7161</v>
@@ -13622,7 +13622,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H457" t="n">
         <v>13780</v>
@@ -13825,7 +13825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H464" t="n">
         <v>16567</v>
@@ -13883,7 +13883,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H466" t="n">
         <v>4338</v>
@@ -13912,7 +13912,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H467" t="n">
         <v>6710</v>
@@ -14028,7 +14028,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H471" t="n">
         <v>8536</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H487" t="n">
         <v>22603</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H491" t="n">
         <v>18592</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H493" t="n">
         <v>6171</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H494" t="n">
         <v>7707</v>
@@ -14927,7 +14927,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H502" t="n">
         <v>22877</v>
@@ -15130,7 +15130,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H509" t="n">
         <v>4568</v>
@@ -15304,7 +15304,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H515" t="n">
         <v>32842</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H517" t="n">
         <v>11854</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H518" t="n">
         <v>8330</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H522" t="n">
         <v>3006</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H524" t="n">
         <v>29907</v>
@@ -15623,7 +15623,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H526" t="n">
         <v>1616</v>
@@ -15855,7 +15855,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H534" t="n">
         <v>33564</v>
@@ -15884,7 +15884,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H535" t="n">
         <v>17947</v>
@@ -16116,7 +16116,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H543" t="n">
         <v>7536</v>
@@ -16145,7 +16145,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H544" t="n">
         <v>20916</v>
@@ -16203,7 +16203,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H546" t="n">
         <v>18431</v>
@@ -16232,7 +16232,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H547" t="n">
         <v>18024</v>
@@ -16261,7 +16261,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H548" t="n">
         <v>5276</v>
@@ -16290,7 +16290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H549" t="n">
         <v>11659</v>
@@ -16319,7 +16319,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H550" t="n">
         <v>9307</v>
@@ -16464,7 +16464,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H555" t="n">
         <v>211195</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H558" t="n">
         <v>68260</v>
@@ -16725,7 +16725,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H564" t="n">
         <v>44216</v>
@@ -16928,7 +16928,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H571" t="n">
         <v>137820</v>
@@ -16957,7 +16957,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H572" t="n">
         <v>46726</v>
@@ -17102,7 +17102,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H577" t="n">
         <v>232133</v>
@@ -17218,7 +17218,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H581" t="n">
         <v>183006</v>
@@ -17276,7 +17276,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H583" t="n">
         <v>110634</v>
@@ -17334,7 +17334,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H585" t="n">
         <v>83401</v>
@@ -17450,7 +17450,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H589" t="n">
         <v>48955</v>
@@ -17479,7 +17479,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H590" t="n">
         <v>54246</v>
@@ -17595,7 +17595,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H594" t="n">
         <v>141610</v>
@@ -17798,7 +17798,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H601" t="n">
         <v>21002</v>
@@ -17885,7 +17885,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H604" t="n">
         <v>23320</v>
@@ -17972,7 +17972,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H607" t="n">
         <v>46484</v>
@@ -18320,7 +18320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H619" t="n">
         <v>4323</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H623" t="n">
         <v>16947</v>
@@ -18465,7 +18465,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H624" t="n">
         <v>5894</v>
@@ -18523,7 +18523,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H626" t="n">
         <v>25679</v>
@@ -18639,7 +18639,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H630" t="n">
         <v>33871</v>
@@ -18697,7 +18697,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H632" t="n">
         <v>24188</v>
@@ -18784,7 +18784,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H635" t="n">
         <v>57265</v>
@@ -19074,7 +19074,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H645" t="n">
         <v>121832</v>
@@ -19103,7 +19103,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H646" t="n">
         <v>46978</v>
@@ -19480,7 +19480,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H659" t="n">
         <v>58410</v>
@@ -19509,7 +19509,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H660" t="n">
         <v>94430</v>
@@ -19538,7 +19538,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H661" t="n">
         <v>16435</v>
@@ -19625,7 +19625,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H664" t="n">
         <v>36840</v>
@@ -19770,7 +19770,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H669" t="n">
         <v>26798</v>
@@ -20002,7 +20002,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H677" t="n">
         <v>3700</v>
@@ -20031,7 +20031,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H678" t="n">
         <v>31808</v>
@@ -20060,7 +20060,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H679" t="n">
         <v>28368</v>
@@ -20118,7 +20118,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H681" t="n">
         <v>19635</v>
@@ -20321,7 +20321,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H688" t="n">
         <v>116323</v>
@@ -20350,7 +20350,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H689" t="n">
         <v>33063</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H690" t="n">
         <v>12669</v>
@@ -20582,7 +20582,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H697" t="n">
         <v>29126</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H698" t="n">
         <v>31677</v>
@@ -20669,7 +20669,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H700" t="n">
         <v>1753</v>
@@ -20698,7 +20698,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H701" t="n">
         <v>9847</v>
@@ -20727,7 +20727,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H702" t="n">
         <v>15481</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H703" t="n">
         <v>4841</v>
@@ -20785,7 +20785,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H704" t="n">
         <v>20397</v>
@@ -20814,7 +20814,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H705" t="n">
         <v>22265</v>
@@ -20872,7 +20872,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H707" t="n">
         <v>56099</v>
@@ -20901,7 +20901,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H708" t="n">
         <v>72110</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H710" t="n">
         <v>41126</v>
@@ -20988,7 +20988,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H711" t="n">
         <v>41372</v>
@@ -21075,7 +21075,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H714" t="n">
         <v>27761</v>
@@ -21249,7 +21249,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H720" t="n">
         <v>30084</v>
@@ -21365,7 +21365,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H724" t="n">
         <v>22097</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H725" t="n">
         <v>21424</v>
@@ -21481,7 +21481,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H728" t="n">
         <v>28785</v>
@@ -21539,7 +21539,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H730" t="n">
         <v>63831</v>
@@ -21568,7 +21568,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H731" t="n">
         <v>14790</v>
@@ -21626,7 +21626,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H733" t="n">
         <v>54638</v>
@@ -21655,7 +21655,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H734" t="n">
         <v>25806</v>
@@ -21771,7 +21771,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H738" t="n">
         <v>9042</v>
@@ -21858,7 +21858,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H741" t="n">
         <v>25001</v>
@@ -21945,7 +21945,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H744" t="n">
         <v>36541</v>
@@ -22119,7 +22119,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H750" t="n">
         <v>24595</v>
@@ -22148,7 +22148,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H751" t="n">
         <v>7605</v>
@@ -22177,7 +22177,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H752" t="n">
         <v>31505</v>
@@ -22235,7 +22235,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H754" t="n">
         <v>15983</v>
@@ -22293,7 +22293,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H756" t="n">
         <v>24115</v>
@@ -22322,7 +22322,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H757" t="n">
         <v>23156</v>
@@ -22351,7 +22351,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H758" t="n">
         <v>22826</v>
@@ -22380,7 +22380,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H759" t="n">
         <v>27789</v>
@@ -22554,7 +22554,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H765" t="n">
         <v>90704</v>
@@ -22641,7 +22641,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H768" t="n">
         <v>25948</v>
@@ -22699,7 +22699,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H770" t="n">
         <v>21002</v>
@@ -22728,7 +22728,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H771" t="n">
         <v>45095</v>
@@ -22757,7 +22757,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H772" t="n">
         <v>32302</v>
@@ -22786,7 +22786,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H773" t="n">
         <v>48385</v>
@@ -22873,7 +22873,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H776" t="n">
         <v>33170</v>
@@ -22902,7 +22902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H777" t="n">
         <v>140269</v>
@@ -22931,7 +22931,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H778" t="n">
         <v>51904</v>
@@ -22989,7 +22989,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H780" t="n">
         <v>26033</v>
@@ -23018,7 +23018,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H781" t="n">
         <v>69932</v>
@@ -23134,7 +23134,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H785" t="n">
         <v>21254</v>
@@ -23424,7 +23424,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H795" t="n">
         <v>129207</v>
@@ -23453,7 +23453,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H796" t="n">
         <v>74996</v>
@@ -23656,7 +23656,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H803" t="n">
         <v>95136</v>
@@ -23830,7 +23830,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H809" t="n">
         <v>42616</v>
@@ -23975,7 +23975,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H814" t="n">
         <v>147606</v>
@@ -24004,7 +24004,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H815" t="n">
         <v>20160</v>
@@ -24062,7 +24062,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H817" t="n">
         <v>48978</v>
@@ -24091,7 +24091,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H818" t="n">
         <v>17601</v>
@@ -24178,7 +24178,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H821" t="n">
         <v>17172</v>
@@ -24207,7 +24207,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H822" t="n">
         <v>21711</v>
@@ -24236,7 +24236,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H823" t="n">
         <v>13038</v>
@@ -24381,7 +24381,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H828" t="n">
         <v>13399</v>
@@ -24700,7 +24700,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H839" t="n">
         <v>10091</v>
@@ -24729,7 +24729,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H840" t="n">
         <v>20843</v>
@@ -24990,7 +24990,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H849" t="n">
         <v>88040</v>
@@ -25048,7 +25048,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H851" t="n">
         <v>61678</v>
@@ -25077,7 +25077,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H852" t="n">
         <v>25922</v>
@@ -25222,7 +25222,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H857" t="n">
         <v>26131</v>
@@ -25309,7 +25309,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H860" t="n">
         <v>25865</v>
@@ -25483,7 +25483,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H866" t="n">
         <v>10855</v>
@@ -25541,7 +25541,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H868" t="n">
         <v>4022</v>
@@ -25570,7 +25570,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.62400817871094</v>
+        <v>4.6240086555481</v>
       </c>
       <c r="H869" t="n">
         <v>9713</v>
@@ -25628,7 +25628,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H871" t="n">
         <v>3876</v>
@@ -25802,7 +25802,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H877" t="n">
         <v>1609</v>
@@ -26179,7 +26179,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H890" t="n">
         <v>21852</v>
@@ -26208,7 +26208,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309289932251</v>
+        <v>4.36309242248535</v>
       </c>
       <c r="H891" t="n">
         <v>19273</v>
@@ -26237,7 +26237,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H892" t="n">
         <v>9208</v>
@@ -26295,7 +26295,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H894" t="n">
         <v>13445</v>
@@ -26324,7 +26324,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645755767822</v>
+        <v>4.26645708084106</v>
       </c>
       <c r="H895" t="n">
         <v>43685</v>
@@ -26440,7 +26440,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H899" t="n">
         <v>27960</v>
@@ -26498,7 +26498,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H901" t="n">
         <v>33825</v>
@@ -26672,7 +26672,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H907" t="n">
         <v>15181</v>
@@ -26730,7 +26730,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621439933777</v>
+        <v>3.98621416091919</v>
       </c>
       <c r="H909" t="n">
         <v>14992</v>
@@ -26904,7 +26904,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H915" t="n">
         <v>53863</v>
@@ -27049,7 +27049,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H920" t="n">
         <v>5004</v>
@@ -27078,7 +27078,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H921" t="n">
         <v>4290</v>
@@ -27136,7 +27136,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H923" t="n">
         <v>8482</v>
@@ -27165,7 +27165,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453254699707</v>
+        <v>4.03453207015991</v>
       </c>
       <c r="H924" t="n">
         <v>16764</v>
@@ -27513,7 +27513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H936" t="n">
         <v>1516</v>
@@ -27629,7 +27629,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H940" t="n">
         <v>4899</v>
@@ -27658,7 +27658,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H941" t="n">
         <v>56027</v>
@@ -27716,7 +27716,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H943" t="n">
         <v>7945</v>
@@ -27861,7 +27861,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H948" t="n">
         <v>9054</v>
@@ -27890,7 +27890,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H949" t="n">
         <v>974</v>
@@ -28006,7 +28006,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H953" t="n">
         <v>15215</v>
@@ -28122,7 +28122,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193374633789</v>
+        <v>3.82193398475647</v>
       </c>
       <c r="H957" t="n">
         <v>1040</v>
@@ -28151,7 +28151,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H958" t="n">
         <v>5878</v>
@@ -28296,7 +28296,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H963" t="n">
         <v>1069</v>
@@ -28325,7 +28325,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H964" t="n">
         <v>4985</v>
@@ -28354,7 +28354,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H965" t="n">
         <v>1586</v>
@@ -28412,7 +28412,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H967" t="n">
         <v>22825</v>
@@ -28499,7 +28499,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H970" t="n">
         <v>1519</v>
@@ -28615,7 +28615,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H974" t="n">
         <v>61487</v>
@@ -28702,7 +28702,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H977" t="n">
         <v>13657</v>
@@ -28731,7 +28731,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H978" t="n">
         <v>26282</v>
@@ -28818,7 +28818,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H981" t="n">
         <v>4451</v>
@@ -28876,7 +28876,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H983" t="n">
         <v>36877</v>
@@ -28905,7 +28905,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H984" t="n">
         <v>1838</v>
@@ -28963,7 +28963,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H986" t="n">
         <v>12068</v>
@@ -28992,7 +28992,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H987" t="n">
         <v>26097</v>
@@ -29021,7 +29021,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H988" t="n">
         <v>6234</v>
@@ -29224,7 +29224,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H995" t="n">
         <v>11228</v>
@@ -29253,7 +29253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H996" t="n">
         <v>4330</v>
@@ -29282,7 +29282,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H997" t="n">
         <v>8092</v>
@@ -29398,7 +29398,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.9668869972229</v>
+        <v>3.96688747406006</v>
       </c>
       <c r="H1001" t="n">
         <v>517</v>
@@ -29514,7 +29514,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H1005" t="n">
         <v>15349</v>
@@ -29804,7 +29804,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1015" t="n">
         <v>20471</v>
@@ -29891,7 +29891,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1018" t="n">
         <v>24364</v>
@@ -29920,7 +29920,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1019" t="n">
         <v>19551</v>
@@ -30007,7 +30007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1022" t="n">
         <v>3870</v>
@@ -30616,7 +30616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1043" t="n">
         <v>7439</v>
@@ -30703,7 +30703,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1046" t="n">
         <v>15720</v>
@@ -30732,7 +30732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1047" t="n">
         <v>13320</v>
@@ -30790,7 +30790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1049" t="n">
         <v>1434</v>
@@ -30848,7 +30848,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820494651794</v>
+        <v>3.49820470809937</v>
       </c>
       <c r="H1051" t="n">
         <v>22296</v>
@@ -30906,7 +30906,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1053" t="n">
         <v>16504</v>
@@ -30935,7 +30935,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1054" t="n">
         <v>12412</v>
@@ -30993,7 +30993,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1056" t="n">
         <v>12576</v>
@@ -31051,7 +31051,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H1058" t="n">
         <v>9513</v>
@@ -31225,7 +31225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1064" t="n">
         <v>11552</v>
@@ -31254,7 +31254,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H1065" t="n">
         <v>34413</v>
@@ -31283,7 +31283,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1066" t="n">
         <v>64042</v>
@@ -31341,7 +31341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1068" t="n">
         <v>24424</v>
@@ -31399,7 +31399,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1070" t="n">
         <v>18126</v>
@@ -31457,7 +31457,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H1072" t="n">
         <v>26947</v>
@@ -31515,7 +31515,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1074" t="n">
         <v>76053</v>
@@ -31689,7 +31689,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1080" t="n">
         <v>11888</v>
@@ -31718,7 +31718,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1081" t="n">
         <v>87040</v>
@@ -31776,7 +31776,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1083" t="n">
         <v>27634</v>
@@ -31805,7 +31805,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1084" t="n">
         <v>183394</v>
@@ -31863,7 +31863,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1086" t="n">
         <v>39968</v>
@@ -31892,7 +31892,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1087" t="n">
         <v>19044</v>
@@ -31950,7 +31950,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1089" t="n">
         <v>21496</v>
@@ -32037,7 +32037,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1092" t="n">
         <v>4199</v>
@@ -32095,7 +32095,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1094" t="n">
         <v>2930</v>
@@ -32124,7 +32124,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1095" t="n">
         <v>17824</v>
@@ -32414,7 +32414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1105" t="n">
         <v>8012</v>
@@ -32501,7 +32501,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1108" t="n">
         <v>20364</v>
@@ -32617,7 +32617,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1112" t="n">
         <v>8014</v>
@@ -32646,7 +32646,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H1113" t="n">
         <v>5992</v>
@@ -32791,7 +32791,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1118" t="n">
         <v>7468</v>
@@ -32878,7 +32878,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1121" t="n">
         <v>7108</v>
@@ -32907,7 +32907,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1122" t="n">
         <v>3566</v>
@@ -32965,7 +32965,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1124" t="n">
         <v>6159</v>
@@ -32994,7 +32994,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1125" t="n">
         <v>36559</v>
@@ -33023,7 +33023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1126" t="n">
         <v>5854</v>
@@ -33081,7 +33081,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1128" t="n">
         <v>85216</v>
@@ -33110,7 +33110,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1129" t="n">
         <v>44308</v>
@@ -33168,7 +33168,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1131" t="n">
         <v>2341</v>
@@ -33197,7 +33197,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1132" t="n">
         <v>13385</v>
@@ -33371,7 +33371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1138" t="n">
         <v>23416</v>
@@ -33516,7 +33516,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H1143" t="n">
         <v>14293</v>
@@ -33574,7 +33574,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1145" t="n">
         <v>44949</v>
@@ -33719,7 +33719,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H1150" t="n">
         <v>7061</v>
@@ -33748,7 +33748,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1151" t="n">
         <v>5770</v>
@@ -33777,7 +33777,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1152" t="n">
         <v>12871</v>
@@ -33806,7 +33806,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1153" t="n">
         <v>21159</v>
@@ -33835,7 +33835,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1154" t="n">
         <v>63339</v>
@@ -33864,7 +33864,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1155" t="n">
         <v>13966</v>
@@ -34125,7 +34125,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1164" t="n">
         <v>8374</v>
@@ -34154,7 +34154,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1165" t="n">
         <v>8257</v>
@@ -34241,7 +34241,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1168" t="n">
         <v>51543</v>
@@ -34299,7 +34299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1170" t="n">
         <v>8138</v>
@@ -34415,7 +34415,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1174" t="n">
         <v>18764</v>
@@ -34589,7 +34589,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1180" t="n">
         <v>22131</v>
@@ -34705,7 +34705,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1184" t="n">
         <v>1634</v>
@@ -34734,7 +34734,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1185" t="n">
         <v>1460</v>
@@ -34792,7 +34792,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1187" t="n">
         <v>21143</v>
@@ -34821,7 +34821,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1188" t="n">
         <v>8937</v>
@@ -34850,7 +34850,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1189" t="n">
         <v>9771</v>
@@ -34908,7 +34908,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1191" t="n">
         <v>3139</v>
@@ -34966,7 +34966,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1193" t="n">
         <v>23650</v>
@@ -34995,7 +34995,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1194" t="n">
         <v>30769</v>
@@ -35024,7 +35024,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1195" t="n">
         <v>53170</v>
@@ -35053,7 +35053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1196" t="n">
         <v>8141</v>
@@ -35082,7 +35082,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1197" t="n">
         <v>18888</v>
@@ -35111,7 +35111,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1198" t="n">
         <v>2167</v>
@@ -35140,7 +35140,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1199" t="n">
         <v>21694</v>
@@ -35169,7 +35169,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1200" t="n">
         <v>30561</v>
@@ -35227,7 +35227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1202" t="n">
         <v>13802</v>
@@ -35285,7 +35285,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1204" t="n">
         <v>39802</v>
@@ -35430,7 +35430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1209" t="n">
         <v>13920</v>
@@ -35952,7 +35952,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1227" t="n">
         <v>11126</v>
@@ -36010,7 +36010,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H1229" t="n">
         <v>30135</v>
@@ -36184,7 +36184,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1235" t="n">
         <v>87770</v>
@@ -36242,7 +36242,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1237" t="n">
         <v>86783</v>
@@ -36271,7 +36271,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H1238" t="n">
         <v>10697</v>
@@ -36300,7 +36300,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1239" t="n">
         <v>633742</v>
@@ -36387,7 +36387,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1242" t="n">
         <v>33483</v>
@@ -36416,7 +36416,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297143936157</v>
+        <v>4.22297096252441</v>
       </c>
       <c r="H1243" t="n">
         <v>111404</v>
@@ -36474,7 +36474,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1245" t="n">
         <v>71817</v>
@@ -36503,7 +36503,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1246" t="n">
         <v>15207</v>
@@ -36561,7 +36561,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1248" t="n">
         <v>263769</v>
@@ -36648,7 +36648,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H1251" t="n">
         <v>22609</v>
@@ -36822,7 +36822,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1257" t="n">
         <v>38711</v>
@@ -36909,7 +36909,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1260" t="n">
         <v>48866</v>
@@ -36938,7 +36938,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1261" t="n">
         <v>88377</v>
@@ -37054,7 +37054,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1265" t="n">
         <v>106306</v>
@@ -37547,7 +37547,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1282" t="n">
         <v>41916</v>
@@ -37663,7 +37663,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1286" t="n">
         <v>18275</v>
@@ -37692,7 +37692,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1287" t="n">
         <v>38266</v>
@@ -37721,7 +37721,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1288" t="n">
         <v>44950</v>
@@ -37750,7 +37750,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1289" t="n">
         <v>154179</v>
@@ -37808,7 +37808,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1291" t="n">
         <v>48801</v>
@@ -37895,7 +37895,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1294" t="n">
         <v>76505</v>
@@ -38011,7 +38011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1298" t="n">
         <v>108894</v>
@@ -38040,7 +38040,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1299" t="n">
         <v>13424</v>
@@ -38098,7 +38098,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1301" t="n">
         <v>3761</v>
@@ -38127,7 +38127,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H1302" t="n">
         <v>18383</v>
@@ -38272,7 +38272,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1307" t="n">
         <v>33977</v>
@@ -38330,7 +38330,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1309" t="n">
         <v>8950</v>
@@ -38562,7 +38562,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1317" t="n">
         <v>2395</v>
@@ -38620,7 +38620,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1319" t="n">
         <v>2013</v>
@@ -38649,7 +38649,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1320" t="n">
         <v>19847</v>
@@ -38678,7 +38678,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1321" t="n">
         <v>6721</v>
@@ -38707,7 +38707,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1322" t="n">
         <v>4183885</v>
@@ -38968,7 +38968,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1331" t="n">
         <v>17017</v>
@@ -38997,7 +38997,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1332" t="n">
         <v>17023</v>
@@ -39113,7 +39113,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1336" t="n">
         <v>7875</v>
@@ -39171,7 +39171,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1338" t="n">
         <v>579091</v>
@@ -39200,7 +39200,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1339" t="n">
         <v>13097</v>
@@ -39258,7 +39258,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1341" t="n">
         <v>18512</v>
@@ -39345,7 +39345,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1344" t="n">
         <v>142420</v>
@@ -39374,7 +39374,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1345" t="n">
         <v>32214</v>
@@ -39403,7 +39403,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1346" t="n">
         <v>117615</v>
@@ -39461,7 +39461,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1348" t="n">
         <v>45261</v>
@@ -39490,7 +39490,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1349" t="n">
         <v>53301</v>
@@ -39519,7 +39519,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1350" t="n">
         <v>53244</v>
@@ -39548,7 +39548,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1351" t="n">
         <v>128034</v>
@@ -39751,7 +39751,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1358" t="n">
         <v>28701</v>
@@ -39954,7 +39954,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1365" t="n">
         <v>13059</v>
@@ -40012,7 +40012,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1367" t="n">
         <v>15645</v>
@@ -40041,7 +40041,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1368" t="n">
         <v>36938</v>
@@ -40070,7 +40070,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1369" t="n">
         <v>30397</v>
@@ -40099,7 +40099,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1370" t="n">
         <v>59503</v>
@@ -40128,7 +40128,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1371" t="n">
         <v>7128</v>
@@ -40186,7 +40186,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1373" t="n">
         <v>53763</v>
@@ -40244,7 +40244,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1375" t="n">
         <v>80223</v>
@@ -40360,7 +40360,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1379" t="n">
         <v>35399</v>
@@ -40389,7 +40389,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1380" t="n">
         <v>66631</v>
@@ -40418,7 +40418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1381" t="n">
         <v>36618</v>
@@ -40476,7 +40476,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1383" t="n">
         <v>9917</v>
@@ -40563,7 +40563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1386" t="n">
         <v>14411</v>
@@ -40592,7 +40592,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1387" t="n">
         <v>5736</v>
@@ -40650,7 +40650,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1389" t="n">
         <v>33151</v>
@@ -40708,7 +40708,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1391" t="n">
         <v>172952</v>
@@ -40737,7 +40737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1392" t="n">
         <v>27304</v>
@@ -40766,7 +40766,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1393" t="n">
         <v>10573</v>
@@ -40824,7 +40824,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1395" t="n">
         <v>16020</v>
@@ -40882,7 +40882,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1397" t="n">
         <v>25629</v>
@@ -40911,7 +40911,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1398" t="n">
         <v>21495</v>
@@ -40940,7 +40940,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1399" t="n">
         <v>11491</v>
@@ -40969,7 +40969,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1400" t="n">
         <v>70839</v>
@@ -41027,7 +41027,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1402" t="n">
         <v>25324</v>
@@ -41346,7 +41346,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1413" t="n">
         <v>23278</v>
@@ -41433,7 +41433,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1416" t="n">
         <v>86929</v>
@@ -41578,7 +41578,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1421" t="n">
         <v>84292</v>
@@ -41636,7 +41636,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1423" t="n">
         <v>17733</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1430" t="n">
         <v>17929</v>
@@ -42100,7 +42100,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1439" t="n">
         <v>30849</v>
@@ -42245,7 +42245,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1444" t="n">
         <v>16400</v>
@@ -42448,7 +42448,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1451" t="n">
         <v>10674</v>
@@ -42593,7 +42593,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1456" t="n">
         <v>14950</v>
@@ -42651,7 +42651,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1458" t="n">
         <v>53885</v>
@@ -42680,7 +42680,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1459" t="n">
         <v>43894</v>
@@ -42825,7 +42825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1464" t="n">
         <v>6023</v>
@@ -42854,7 +42854,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1465" t="n">
         <v>13746</v>
@@ -42941,7 +42941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1468" t="n">
         <v>17342</v>
@@ -43318,7 +43318,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1481" t="n">
         <v>4088</v>
@@ -43434,7 +43434,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1485" t="n">
         <v>18559</v>
@@ -43463,7 +43463,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1486" t="n">
         <v>5313</v>
@@ -43695,7 +43695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1494" t="n">
         <v>10058</v>
@@ -43724,7 +43724,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1495" t="n">
         <v>6566</v>
@@ -43898,7 +43898,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1501" t="n">
         <v>24701</v>
@@ -43927,7 +43927,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1502" t="n">
         <v>13712</v>
@@ -43985,7 +43985,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1504" t="n">
         <v>17967</v>
@@ -44014,7 +44014,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1505" t="n">
         <v>12753</v>
@@ -44043,7 +44043,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1506" t="n">
         <v>4017</v>
@@ -44304,7 +44304,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1515" t="n">
         <v>32760</v>
@@ -44420,7 +44420,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1519" t="n">
         <v>13224</v>
@@ -44449,7 +44449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1520" t="n">
         <v>15389</v>
@@ -44536,7 +44536,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1523" t="n">
         <v>23568</v>
@@ -44652,7 +44652,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1527" t="n">
         <v>12057</v>
@@ -44681,7 +44681,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1528" t="n">
         <v>10102</v>
@@ -44710,7 +44710,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1529" t="n">
         <v>11999</v>
@@ -44768,7 +44768,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H1531" t="n">
         <v>23916</v>
@@ -44797,7 +44797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1532" t="n">
         <v>53597</v>
@@ -44826,7 +44826,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1533" t="n">
         <v>35027</v>
@@ -44913,7 +44913,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H1536" t="n">
         <v>27398</v>
@@ -45087,7 +45087,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1542" t="n">
         <v>10776</v>
@@ -45290,7 +45290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1549" t="n">
         <v>17670</v>
@@ -45348,7 +45348,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1551" t="n">
         <v>6270</v>
@@ -45551,7 +45551,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1558" t="n">
         <v>9714</v>
@@ -45580,7 +45580,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1559" t="n">
         <v>9223</v>
@@ -45667,7 +45667,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1562" t="n">
         <v>3769</v>
@@ -45870,7 +45870,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1569" t="n">
         <v>59041</v>
@@ -45928,7 +45928,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1571" t="n">
         <v>19659</v>
@@ -45986,7 +45986,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1573" t="n">
         <v>6033</v>
@@ -46102,7 +46102,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1577" t="n">
         <v>16481</v>
@@ -46131,7 +46131,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1578" t="n">
         <v>16827</v>
@@ -46247,7 +46247,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1582" t="n">
         <v>12336</v>
@@ -46537,7 +46537,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1592" t="n">
         <v>40020</v>
@@ -46566,7 +46566,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1593" t="n">
         <v>20842</v>
@@ -47175,7 +47175,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1614" t="n">
         <v>15568</v>
@@ -47262,7 +47262,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1617" t="n">
         <v>1706</v>
@@ -47320,7 +47320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1619" t="n">
         <v>97926</v>
@@ -47349,7 +47349,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1620" t="n">
         <v>14080</v>
@@ -47378,7 +47378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1621" t="n">
         <v>19839</v>
@@ -47436,7 +47436,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1623" t="n">
         <v>16886</v>
@@ -47552,7 +47552,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605560302734</v>
+        <v>4.99605512619019</v>
       </c>
       <c r="H1627" t="n">
         <v>60722</v>
@@ -47581,7 +47581,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1628" t="n">
         <v>24838</v>
@@ -47610,7 +47610,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1629" t="n">
         <v>21313</v>
@@ -47639,7 +47639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1630" t="n">
         <v>23268</v>
@@ -47668,7 +47668,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1631" t="n">
         <v>2356</v>
@@ -47697,7 +47697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1632" t="n">
         <v>26681</v>
@@ -47755,7 +47755,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1634" t="n">
         <v>18116</v>
@@ -47842,7 +47842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1637" t="n">
         <v>9629</v>
@@ -47900,7 +47900,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1639" t="n">
         <v>10513</v>
@@ -47929,7 +47929,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1640" t="n">
         <v>5633</v>
@@ -47987,7 +47987,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H1642" t="n">
         <v>29183</v>
@@ -58836,9 +58836,38 @@
         <v>5.30000019073486</v>
       </c>
       <c r="H2016" t="n">
-        <v>13322</v>
+        <v>14424</v>
       </c>
       <c r="I2016" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2017" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2017" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D2017" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="G2017" t="n">
+        <v>5.28000020980835</v>
+      </c>
+      <c r="H2017" t="n">
+        <v>9406</v>
+      </c>
+      <c r="I2017" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835180282593</v>
+        <v>3.50835204124451</v>
       </c>
       <c r="H5" t="n">
         <v>168607</v>
@@ -572,7 +572,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290790557861</v>
+        <v>3.59290766716003</v>
       </c>
       <c r="H7" t="n">
         <v>115707</v>
@@ -630,7 +630,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555654525757</v>
+        <v>3.54555630683899</v>
       </c>
       <c r="H9" t="n">
         <v>18987</v>
@@ -717,7 +717,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694516181946</v>
+        <v>3.47694540023804</v>
       </c>
       <c r="H12" t="n">
         <v>25574</v>
@@ -775,7 +775,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018074989319</v>
+        <v>3.47018098831177</v>
       </c>
       <c r="H14" t="n">
         <v>14046</v>
@@ -804,7 +804,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887778282166</v>
+        <v>3.47887802124023</v>
       </c>
       <c r="H15" t="n">
         <v>25673</v>
@@ -833,7 +833,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786876678467</v>
+        <v>3.50786852836609</v>
       </c>
       <c r="H16" t="n">
         <v>17829</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887778282166</v>
+        <v>3.47887802124023</v>
       </c>
       <c r="H20" t="n">
         <v>24337</v>
@@ -1007,7 +1007,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786876678467</v>
+        <v>3.50786852836609</v>
       </c>
       <c r="H22" t="n">
         <v>15060</v>
@@ -1065,7 +1065,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710956573486</v>
+        <v>3.58710980415344</v>
       </c>
       <c r="H24" t="n">
         <v>31246</v>
@@ -1297,7 +1297,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299355506897</v>
+        <v>3.53299379348755</v>
       </c>
       <c r="H32" t="n">
         <v>12155</v>
@@ -1326,7 +1326,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5368595123291</v>
+        <v>3.53685927391052</v>
       </c>
       <c r="H33" t="n">
         <v>2992</v>
@@ -1384,7 +1384,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185570716858</v>
+        <v>3.65185546875</v>
       </c>
       <c r="H35" t="n">
         <v>9616</v>
@@ -1500,7 +1500,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H39" t="n">
         <v>33223</v>
@@ -1558,7 +1558,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464335441589</v>
+        <v>3.84464311599731</v>
       </c>
       <c r="H41" t="n">
         <v>67310</v>
@@ -1674,7 +1674,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869839668274</v>
+        <v>3.82869815826416</v>
       </c>
       <c r="H45" t="n">
         <v>15050</v>
@@ -1761,7 +1761,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243504524231</v>
+        <v>3.92243480682373</v>
       </c>
       <c r="H48" t="n">
         <v>7064</v>
@@ -1848,7 +1848,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H51" t="n">
         <v>10244</v>
@@ -2138,7 +2138,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863766670227</v>
+        <v>3.75863742828369</v>
       </c>
       <c r="H61" t="n">
         <v>18963</v>
@@ -2167,7 +2167,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H62" t="n">
         <v>25241</v>
@@ -2254,7 +2254,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H65" t="n">
         <v>14098</v>
@@ -2283,7 +2283,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364123344421</v>
+        <v>3.64364147186279</v>
       </c>
       <c r="H66" t="n">
         <v>24444</v>
@@ -2312,7 +2312,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H67" t="n">
         <v>14328</v>
@@ -2457,7 +2457,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422057151794</v>
+        <v>3.91422080993652</v>
       </c>
       <c r="H72" t="n">
         <v>37886</v>
@@ -2544,7 +2544,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H75" t="n">
         <v>61176</v>
@@ -2573,7 +2573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H76" t="n">
         <v>4871</v>
@@ -2631,7 +2631,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615343093872</v>
+        <v>3.91615319252014</v>
       </c>
       <c r="H78" t="n">
         <v>28408</v>
@@ -2660,7 +2660,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331546783447</v>
+        <v>3.98331522941589</v>
       </c>
       <c r="H79" t="n">
         <v>15491</v>
@@ -2689,7 +2689,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H80" t="n">
         <v>8568</v>
@@ -2718,7 +2718,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.9528751373291</v>
+        <v>3.95287489891052</v>
       </c>
       <c r="H81" t="n">
         <v>11304</v>
@@ -2747,7 +2747,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354773521423</v>
+        <v>3.93354797363281</v>
       </c>
       <c r="H82" t="n">
         <v>1333</v>
@@ -2805,7 +2805,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445355415344</v>
+        <v>3.86445379257202</v>
       </c>
       <c r="H84" t="n">
         <v>14743</v>
@@ -2892,7 +2892,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H87" t="n">
         <v>16436</v>
@@ -2921,7 +2921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H88" t="n">
         <v>70067</v>
@@ -2950,7 +2950,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H89" t="n">
         <v>20248</v>
@@ -2979,7 +2979,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H90" t="n">
         <v>9804</v>
@@ -3008,7 +3008,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H91" t="n">
         <v>8029</v>
@@ -3124,7 +3124,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H95" t="n">
         <v>6789</v>
@@ -3153,7 +3153,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H96" t="n">
         <v>16453</v>
@@ -3182,7 +3182,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H97" t="n">
         <v>13893</v>
@@ -3211,7 +3211,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H98" t="n">
         <v>34445</v>
@@ -3269,7 +3269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H100" t="n">
         <v>5569</v>
@@ -3327,7 +3327,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H102" t="n">
         <v>17175</v>
@@ -3385,7 +3385,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H104" t="n">
         <v>4792</v>
@@ -3443,7 +3443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H106" t="n">
         <v>12618</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H107" t="n">
         <v>7801</v>
@@ -3530,7 +3530,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H109" t="n">
         <v>27377</v>
@@ -3559,7 +3559,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H110" t="n">
         <v>9652</v>
@@ -3588,7 +3588,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H111" t="n">
         <v>22427</v>
@@ -3646,7 +3646,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H113" t="n">
         <v>5635</v>
@@ -3675,7 +3675,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H114" t="n">
         <v>12247</v>
@@ -3704,7 +3704,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H115" t="n">
         <v>46534</v>
@@ -3762,7 +3762,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H117" t="n">
         <v>14370</v>
@@ -3791,7 +3791,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H118" t="n">
         <v>20871</v>
@@ -3849,7 +3849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H120" t="n">
         <v>51861</v>
@@ -3907,7 +3907,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890598297119</v>
+        <v>3.90890622138977</v>
       </c>
       <c r="H122" t="n">
         <v>24632</v>
@@ -3965,7 +3965,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856908798218</v>
+        <v>3.91856932640076</v>
       </c>
       <c r="H124" t="n">
         <v>9251</v>
@@ -4023,7 +4023,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H126" t="n">
         <v>23445</v>
@@ -4052,7 +4052,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H127" t="n">
         <v>13288</v>
@@ -4226,7 +4226,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H133" t="n">
         <v>69275</v>
@@ -4255,7 +4255,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.68664455413818</v>
+        <v>3.6866443157196</v>
       </c>
       <c r="H134" t="n">
         <v>83826</v>
@@ -4284,7 +4284,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H135" t="n">
         <v>38411</v>
@@ -4342,7 +4342,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H137" t="n">
         <v>28361</v>
@@ -4371,7 +4371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H138" t="n">
         <v>16251</v>
@@ -4400,7 +4400,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890598297119</v>
+        <v>3.90890622138977</v>
       </c>
       <c r="H139" t="n">
         <v>24663</v>
@@ -4661,7 +4661,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H148" t="n">
         <v>6408</v>
@@ -4690,7 +4690,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H149" t="n">
         <v>17007</v>
@@ -4748,7 +4748,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H151" t="n">
         <v>51508</v>
@@ -4893,7 +4893,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.04419565200806</v>
+        <v>4.0441951751709</v>
       </c>
       <c r="H156" t="n">
         <v>57059</v>
@@ -4951,7 +4951,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431663513184</v>
+        <v>4.18431711196899</v>
       </c>
       <c r="H158" t="n">
         <v>51199</v>
@@ -5821,7 +5821,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251356124878</v>
+        <v>4.09251308441162</v>
       </c>
       <c r="H188" t="n">
         <v>3584</v>
@@ -5995,7 +5995,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431663513184</v>
+        <v>4.18431711196899</v>
       </c>
       <c r="H194" t="n">
         <v>11423</v>
@@ -6459,7 +6459,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H210" t="n">
         <v>4401</v>
@@ -6546,7 +6546,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H213" t="n">
         <v>14225</v>
@@ -6720,7 +6720,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H219" t="n">
         <v>109205</v>
@@ -6981,7 +6981,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H228" t="n">
         <v>32762</v>
@@ -7358,7 +7358,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501838684082</v>
+        <v>4.59501791000366</v>
       </c>
       <c r="H241" t="n">
         <v>82951</v>
@@ -7416,7 +7416,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H243" t="n">
         <v>10325</v>
@@ -7445,7 +7445,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H244" t="n">
         <v>8300</v>
@@ -7590,7 +7590,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761623382568</v>
+        <v>4.80761575698853</v>
       </c>
       <c r="H249" t="n">
         <v>50047</v>
@@ -7619,7 +7619,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761623382568</v>
+        <v>4.80761575698853</v>
       </c>
       <c r="H250" t="n">
         <v>91315</v>
@@ -7648,7 +7648,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H251" t="n">
         <v>63937</v>
@@ -7677,7 +7677,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929880142212</v>
+        <v>4.75929832458496</v>
       </c>
       <c r="H252" t="n">
         <v>3333</v>
@@ -7793,7 +7793,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H256" t="n">
         <v>24390</v>
@@ -7967,7 +7967,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H262" t="n">
         <v>8895</v>
@@ -8025,7 +8025,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727933883667</v>
+        <v>4.81727981567383</v>
       </c>
       <c r="H264" t="n">
         <v>44506</v>
@@ -8054,7 +8054,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H265" t="n">
         <v>48189</v>
@@ -8083,7 +8083,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H266" t="n">
         <v>41705</v>
@@ -8141,7 +8141,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H268" t="n">
         <v>123324</v>
@@ -8228,7 +8228,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740127563477</v>
+        <v>4.95740079879761</v>
       </c>
       <c r="H271" t="n">
         <v>6925</v>
@@ -8315,7 +8315,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H274" t="n">
         <v>136710</v>
@@ -8344,7 +8344,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H275" t="n">
         <v>260348</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H278" t="n">
         <v>25684</v>
@@ -8547,7 +8547,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H282" t="n">
         <v>57869</v>
@@ -8924,7 +8924,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H295" t="n">
         <v>20573</v>
@@ -9040,7 +9040,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H299" t="n">
         <v>19695</v>
@@ -9243,7 +9243,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H306" t="n">
         <v>19157</v>
@@ -9359,7 +9359,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596162796021</v>
+        <v>5.28596115112305</v>
       </c>
       <c r="H310" t="n">
         <v>19428</v>
@@ -9417,7 +9417,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H312" t="n">
         <v>4283</v>
@@ -9533,7 +9533,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H316" t="n">
         <v>151029</v>
@@ -9620,7 +9620,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H319" t="n">
         <v>12312</v>
@@ -9649,7 +9649,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H320" t="n">
         <v>162473</v>
@@ -9765,7 +9765,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H324" t="n">
         <v>99309</v>
@@ -9852,7 +9852,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134479522705</v>
+        <v>5.13134527206421</v>
       </c>
       <c r="H327" t="n">
         <v>34058</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H329" t="n">
         <v>26368</v>
@@ -9968,7 +9968,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H331" t="n">
         <v>32218</v>
@@ -9997,7 +9997,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H332" t="n">
         <v>81218</v>
@@ -10026,7 +10026,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H333" t="n">
         <v>14865</v>
@@ -10258,7 +10258,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H341" t="n">
         <v>82529</v>
@@ -10287,7 +10287,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H342" t="n">
         <v>98211</v>
@@ -10461,7 +10461,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H348" t="n">
         <v>32626</v>
@@ -10635,7 +10635,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H354" t="n">
         <v>33125</v>
@@ -10751,7 +10751,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H358" t="n">
         <v>44086</v>
@@ -10867,7 +10867,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H362" t="n">
         <v>11155</v>
@@ -11041,7 +11041,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H368" t="n">
         <v>26463</v>
@@ -11099,7 +11099,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H370" t="n">
         <v>8841</v>
@@ -11186,7 +11186,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263502120972</v>
+        <v>4.23263454437256</v>
       </c>
       <c r="H373" t="n">
         <v>16343</v>
@@ -11302,7 +11302,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489645004272</v>
+        <v>4.45489692687988</v>
       </c>
       <c r="H377" t="n">
         <v>6689</v>
@@ -11418,7 +11418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H381" t="n">
         <v>31236</v>
@@ -11447,7 +11447,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H382" t="n">
         <v>9513</v>
@@ -11505,7 +11505,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H384" t="n">
         <v>12160</v>
@@ -11563,7 +11563,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H386" t="n">
         <v>5668</v>
@@ -11679,7 +11679,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H390" t="n">
         <v>5996</v>
@@ -11737,7 +11737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H392" t="n">
         <v>19706</v>
@@ -11795,7 +11795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H394" t="n">
         <v>18905</v>
@@ -12027,7 +12027,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H402" t="n">
         <v>20308</v>
@@ -12288,7 +12288,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H411" t="n">
         <v>7185</v>
@@ -12317,7 +12317,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H412" t="n">
         <v>7082</v>
@@ -12375,7 +12375,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H414" t="n">
         <v>49474</v>
@@ -12520,7 +12520,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H419" t="n">
         <v>7439</v>
@@ -12549,7 +12549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H420" t="n">
         <v>15236</v>
@@ -12607,7 +12607,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H422" t="n">
         <v>10351</v>
@@ -12636,7 +12636,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H423" t="n">
         <v>17376</v>
@@ -12810,7 +12810,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H429" t="n">
         <v>7532</v>
@@ -12868,7 +12868,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H431" t="n">
         <v>2225</v>
@@ -12984,7 +12984,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H435" t="n">
         <v>6281</v>
@@ -13013,7 +13013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H436" t="n">
         <v>7095</v>
@@ -13332,7 +13332,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H447" t="n">
         <v>1474</v>
@@ -13361,7 +13361,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H452" t="n">
         <v>5271</v>
@@ -13564,7 +13564,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H455" t="n">
         <v>7161</v>
@@ -13622,7 +13622,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H457" t="n">
         <v>13780</v>
@@ -13825,7 +13825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H464" t="n">
         <v>16567</v>
@@ -13883,7 +13883,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H466" t="n">
         <v>4338</v>
@@ -13912,7 +13912,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H467" t="n">
         <v>6710</v>
@@ -14028,7 +14028,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H471" t="n">
         <v>8536</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H487" t="n">
         <v>22603</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H491" t="n">
         <v>18592</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H493" t="n">
         <v>6171</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H494" t="n">
         <v>7707</v>
@@ -14927,7 +14927,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H502" t="n">
         <v>22877</v>
@@ -15130,7 +15130,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H509" t="n">
         <v>4568</v>
@@ -15304,7 +15304,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H515" t="n">
         <v>32842</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H517" t="n">
         <v>11854</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H518" t="n">
         <v>8330</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H522" t="n">
         <v>3006</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H524" t="n">
         <v>29907</v>
@@ -15623,7 +15623,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H526" t="n">
         <v>1616</v>
@@ -15855,7 +15855,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H534" t="n">
         <v>33564</v>
@@ -15884,7 +15884,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H535" t="n">
         <v>17947</v>
@@ -16116,7 +16116,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H543" t="n">
         <v>7536</v>
@@ -16145,7 +16145,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H544" t="n">
         <v>20916</v>
@@ -16203,7 +16203,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H546" t="n">
         <v>18431</v>
@@ -16232,7 +16232,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H547" t="n">
         <v>18024</v>
@@ -16261,7 +16261,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H548" t="n">
         <v>5276</v>
@@ -16290,7 +16290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H549" t="n">
         <v>11659</v>
@@ -16319,7 +16319,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H550" t="n">
         <v>9307</v>
@@ -16464,7 +16464,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H555" t="n">
         <v>211195</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H558" t="n">
         <v>68260</v>
@@ -16725,7 +16725,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H564" t="n">
         <v>44216</v>
@@ -16928,7 +16928,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H571" t="n">
         <v>137820</v>
@@ -16957,7 +16957,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H572" t="n">
         <v>46726</v>
@@ -17102,7 +17102,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H577" t="n">
         <v>232133</v>
@@ -17218,7 +17218,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H581" t="n">
         <v>183006</v>
@@ -17276,7 +17276,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H583" t="n">
         <v>110634</v>
@@ -17334,7 +17334,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H585" t="n">
         <v>83401</v>
@@ -17450,7 +17450,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H589" t="n">
         <v>48955</v>
@@ -17479,7 +17479,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H590" t="n">
         <v>54246</v>
@@ -17595,7 +17595,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H594" t="n">
         <v>141610</v>
@@ -17798,7 +17798,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H601" t="n">
         <v>21002</v>
@@ -17885,7 +17885,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H604" t="n">
         <v>23320</v>
@@ -17972,7 +17972,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H607" t="n">
         <v>46484</v>
@@ -18320,7 +18320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H619" t="n">
         <v>4323</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H623" t="n">
         <v>16947</v>
@@ -18465,7 +18465,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H624" t="n">
         <v>5894</v>
@@ -18523,7 +18523,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H626" t="n">
         <v>25679</v>
@@ -18639,7 +18639,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H630" t="n">
         <v>33871</v>
@@ -18697,7 +18697,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H632" t="n">
         <v>24188</v>
@@ -18784,7 +18784,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H635" t="n">
         <v>57265</v>
@@ -19074,7 +19074,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H645" t="n">
         <v>121832</v>
@@ -19103,7 +19103,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H646" t="n">
         <v>46978</v>
@@ -19480,7 +19480,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H659" t="n">
         <v>58410</v>
@@ -19509,7 +19509,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H660" t="n">
         <v>94430</v>
@@ -19538,7 +19538,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H661" t="n">
         <v>16435</v>
@@ -19625,7 +19625,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H664" t="n">
         <v>36840</v>
@@ -19770,7 +19770,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H669" t="n">
         <v>26798</v>
@@ -20002,7 +20002,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H677" t="n">
         <v>3700</v>
@@ -20031,7 +20031,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H678" t="n">
         <v>31808</v>
@@ -20060,7 +20060,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H679" t="n">
         <v>28368</v>
@@ -20118,7 +20118,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H681" t="n">
         <v>19635</v>
@@ -20321,7 +20321,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H688" t="n">
         <v>116323</v>
@@ -20350,7 +20350,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H689" t="n">
         <v>33063</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H690" t="n">
         <v>12669</v>
@@ -20582,7 +20582,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H697" t="n">
         <v>29126</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H698" t="n">
         <v>31677</v>
@@ -20669,7 +20669,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H700" t="n">
         <v>1753</v>
@@ -20698,7 +20698,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H701" t="n">
         <v>9847</v>
@@ -20727,7 +20727,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H702" t="n">
         <v>15481</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H703" t="n">
         <v>4841</v>
@@ -20785,7 +20785,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H704" t="n">
         <v>20397</v>
@@ -20814,7 +20814,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H705" t="n">
         <v>22265</v>
@@ -20872,7 +20872,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H707" t="n">
         <v>56099</v>
@@ -20901,7 +20901,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H708" t="n">
         <v>72110</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H710" t="n">
         <v>41126</v>
@@ -20988,7 +20988,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H711" t="n">
         <v>41372</v>
@@ -21075,7 +21075,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H714" t="n">
         <v>27761</v>
@@ -21249,7 +21249,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H720" t="n">
         <v>30084</v>
@@ -21365,7 +21365,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H724" t="n">
         <v>22097</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H725" t="n">
         <v>21424</v>
@@ -21481,7 +21481,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H728" t="n">
         <v>28785</v>
@@ -21539,7 +21539,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H730" t="n">
         <v>63831</v>
@@ -21568,7 +21568,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H731" t="n">
         <v>14790</v>
@@ -21626,7 +21626,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H733" t="n">
         <v>54638</v>
@@ -21655,7 +21655,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H734" t="n">
         <v>25806</v>
@@ -21771,7 +21771,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H738" t="n">
         <v>9042</v>
@@ -21858,7 +21858,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H741" t="n">
         <v>25001</v>
@@ -21945,7 +21945,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H744" t="n">
         <v>36541</v>
@@ -22119,7 +22119,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H750" t="n">
         <v>24595</v>
@@ -22148,7 +22148,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H751" t="n">
         <v>7605</v>
@@ -22177,7 +22177,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H752" t="n">
         <v>31505</v>
@@ -22235,7 +22235,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H754" t="n">
         <v>15983</v>
@@ -22293,7 +22293,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H756" t="n">
         <v>24115</v>
@@ -22322,7 +22322,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H757" t="n">
         <v>23156</v>
@@ -22351,7 +22351,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H758" t="n">
         <v>22826</v>
@@ -22380,7 +22380,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H759" t="n">
         <v>27789</v>
@@ -22554,7 +22554,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H765" t="n">
         <v>90704</v>
@@ -22641,7 +22641,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H768" t="n">
         <v>25948</v>
@@ -22699,7 +22699,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H770" t="n">
         <v>21002</v>
@@ -22728,7 +22728,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745719909668</v>
+        <v>5.81745672225952</v>
       </c>
       <c r="H771" t="n">
         <v>45095</v>
@@ -22757,7 +22757,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745719909668</v>
+        <v>5.81745672225952</v>
       </c>
       <c r="H772" t="n">
         <v>32302</v>
@@ -22786,7 +22786,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H773" t="n">
         <v>48385</v>
@@ -22873,7 +22873,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H776" t="n">
         <v>33170</v>
@@ -22902,7 +22902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H777" t="n">
         <v>140269</v>
@@ -22931,7 +22931,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H778" t="n">
         <v>51904</v>
@@ -22989,7 +22989,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H780" t="n">
         <v>26033</v>
@@ -23018,7 +23018,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H781" t="n">
         <v>69932</v>
@@ -23134,7 +23134,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H785" t="n">
         <v>21254</v>
@@ -23424,7 +23424,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H795" t="n">
         <v>129207</v>
@@ -23453,7 +23453,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H796" t="n">
         <v>74996</v>
@@ -23656,7 +23656,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H803" t="n">
         <v>95136</v>
@@ -23830,7 +23830,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H809" t="n">
         <v>42616</v>
@@ -23975,7 +23975,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H814" t="n">
         <v>147606</v>
@@ -24004,7 +24004,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H815" t="n">
         <v>20160</v>
@@ -24062,7 +24062,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H817" t="n">
         <v>48978</v>
@@ -24091,7 +24091,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H818" t="n">
         <v>17601</v>
@@ -24178,7 +24178,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H821" t="n">
         <v>17172</v>
@@ -24207,7 +24207,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H822" t="n">
         <v>21711</v>
@@ -24236,7 +24236,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H823" t="n">
         <v>13038</v>
@@ -24381,7 +24381,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H828" t="n">
         <v>13399</v>
@@ -24700,7 +24700,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H839" t="n">
         <v>10091</v>
@@ -24729,7 +24729,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H840" t="n">
         <v>20843</v>
@@ -24990,7 +24990,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725185394287</v>
+        <v>4.38725137710571</v>
       </c>
       <c r="H849" t="n">
         <v>88040</v>
@@ -25048,7 +25048,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H851" t="n">
         <v>61678</v>
@@ -25077,7 +25077,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H852" t="n">
         <v>25922</v>
@@ -25222,7 +25222,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H857" t="n">
         <v>26131</v>
@@ -25309,7 +25309,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H860" t="n">
         <v>25865</v>
@@ -25483,7 +25483,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H866" t="n">
         <v>10855</v>
@@ -25541,7 +25541,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H868" t="n">
         <v>4022</v>
@@ -25570,7 +25570,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.6240086555481</v>
+        <v>4.62400817871094</v>
       </c>
       <c r="H869" t="n">
         <v>9713</v>
@@ -25628,7 +25628,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602716445923</v>
+        <v>4.56602764129639</v>
       </c>
       <c r="H871" t="n">
         <v>3876</v>
@@ -25802,7 +25802,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602716445923</v>
+        <v>4.56602764129639</v>
       </c>
       <c r="H877" t="n">
         <v>1609</v>
@@ -26179,7 +26179,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H890" t="n">
         <v>21852</v>
@@ -26208,7 +26208,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309242248535</v>
+        <v>4.36309289932251</v>
       </c>
       <c r="H891" t="n">
         <v>19273</v>
@@ -26237,7 +26237,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H892" t="n">
         <v>9208</v>
@@ -26295,7 +26295,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H894" t="n">
         <v>13445</v>
@@ -26324,7 +26324,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645708084106</v>
+        <v>4.26645755767822</v>
       </c>
       <c r="H895" t="n">
         <v>43685</v>
@@ -26440,7 +26440,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H899" t="n">
         <v>27960</v>
@@ -26498,7 +26498,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095245361328</v>
+        <v>4.28095197677612</v>
       </c>
       <c r="H901" t="n">
         <v>33825</v>
@@ -26672,7 +26672,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.04419565200806</v>
+        <v>4.0441951751709</v>
       </c>
       <c r="H907" t="n">
         <v>15181</v>
@@ -26730,7 +26730,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621416091919</v>
+        <v>3.98621439933777</v>
       </c>
       <c r="H909" t="n">
         <v>14992</v>
@@ -26904,7 +26904,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H915" t="n">
         <v>53863</v>
@@ -27049,7 +27049,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H920" t="n">
         <v>5004</v>
@@ -27078,7 +27078,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H921" t="n">
         <v>4290</v>
@@ -27136,7 +27136,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H923" t="n">
         <v>8482</v>
@@ -27165,7 +27165,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453207015991</v>
+        <v>4.03453254699707</v>
       </c>
       <c r="H924" t="n">
         <v>16764</v>
@@ -27513,7 +27513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H936" t="n">
         <v>1516</v>
@@ -27629,7 +27629,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H940" t="n">
         <v>4899</v>
@@ -27658,7 +27658,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.8557562828064</v>
+        <v>3.85575652122498</v>
       </c>
       <c r="H941" t="n">
         <v>56027</v>
@@ -27716,7 +27716,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H943" t="n">
         <v>7945</v>
@@ -27861,7 +27861,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H948" t="n">
         <v>9054</v>
@@ -27890,7 +27890,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H949" t="n">
         <v>974</v>
@@ -28006,7 +28006,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H953" t="n">
         <v>15215</v>
@@ -28122,7 +28122,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193398475647</v>
+        <v>3.82193374633789</v>
       </c>
       <c r="H957" t="n">
         <v>1040</v>
@@ -28151,7 +28151,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327965736389</v>
+        <v>3.78327989578247</v>
       </c>
       <c r="H958" t="n">
         <v>5878</v>
@@ -28296,7 +28296,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327965736389</v>
+        <v>3.78327989578247</v>
       </c>
       <c r="H963" t="n">
         <v>1069</v>
@@ -28325,7 +28325,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H964" t="n">
         <v>4985</v>
@@ -28354,7 +28354,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H965" t="n">
         <v>1586</v>
@@ -28412,7 +28412,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H967" t="n">
         <v>22825</v>
@@ -28499,7 +28499,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945759773254</v>
+        <v>3.74945735931396</v>
       </c>
       <c r="H970" t="n">
         <v>1519</v>
@@ -28615,7 +28615,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H974" t="n">
         <v>61487</v>
@@ -28702,7 +28702,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.8557562828064</v>
+        <v>3.85575652122498</v>
       </c>
       <c r="H977" t="n">
         <v>13657</v>
@@ -28731,7 +28731,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H978" t="n">
         <v>26282</v>
@@ -28818,7 +28818,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H981" t="n">
         <v>4451</v>
@@ -28876,7 +28876,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H983" t="n">
         <v>36877</v>
@@ -28905,7 +28905,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H984" t="n">
         <v>1838</v>
@@ -28963,7 +28963,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H986" t="n">
         <v>12068</v>
@@ -28992,7 +28992,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H987" t="n">
         <v>26097</v>
@@ -29021,7 +29021,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945759773254</v>
+        <v>3.74945735931396</v>
       </c>
       <c r="H988" t="n">
         <v>6234</v>
@@ -29224,7 +29224,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H995" t="n">
         <v>11228</v>
@@ -29253,7 +29253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H996" t="n">
         <v>4330</v>
@@ -29282,7 +29282,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H997" t="n">
         <v>8092</v>
@@ -29398,7 +29398,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.96688747406006</v>
+        <v>3.9668869972229</v>
       </c>
       <c r="H1001" t="n">
         <v>517</v>
@@ -29514,7 +29514,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856908798218</v>
+        <v>3.91856932640076</v>
       </c>
       <c r="H1005" t="n">
         <v>15349</v>
@@ -29804,7 +29804,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1015" t="n">
         <v>20471</v>
@@ -29891,7 +29891,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1018" t="n">
         <v>24364</v>
@@ -29920,7 +29920,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1019" t="n">
         <v>19551</v>
@@ -30007,7 +30007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1022" t="n">
         <v>3870</v>
@@ -30616,7 +30616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1043" t="n">
         <v>7439</v>
@@ -30703,7 +30703,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1046" t="n">
         <v>15720</v>
@@ -30732,7 +30732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1047" t="n">
         <v>13320</v>
@@ -30790,7 +30790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1049" t="n">
         <v>1434</v>
@@ -30848,7 +30848,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820470809937</v>
+        <v>3.49820494651794</v>
       </c>
       <c r="H1051" t="n">
         <v>22296</v>
@@ -30906,7 +30906,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1053" t="n">
         <v>16504</v>
@@ -30935,7 +30935,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1054" t="n">
         <v>12412</v>
@@ -30993,7 +30993,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1056" t="n">
         <v>12576</v>
@@ -31051,7 +31051,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H1058" t="n">
         <v>9513</v>
@@ -31225,7 +31225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1064" t="n">
         <v>11552</v>
@@ -31254,7 +31254,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H1065" t="n">
         <v>34413</v>
@@ -31283,7 +31283,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135464668274</v>
+        <v>3.55135440826416</v>
       </c>
       <c r="H1066" t="n">
         <v>64042</v>
@@ -31341,7 +31341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1068" t="n">
         <v>24424</v>
@@ -31399,7 +31399,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1070" t="n">
         <v>18126</v>
@@ -31457,7 +31457,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.5368595123291</v>
+        <v>3.53685927391052</v>
       </c>
       <c r="H1072" t="n">
         <v>26947</v>
@@ -31515,7 +31515,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1074" t="n">
         <v>76053</v>
@@ -31689,7 +31689,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1080" t="n">
         <v>11888</v>
@@ -31718,7 +31718,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.59967231750488</v>
+        <v>3.5996720790863</v>
       </c>
       <c r="H1081" t="n">
         <v>87040</v>
@@ -31776,7 +31776,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1083" t="n">
         <v>27634</v>
@@ -31805,7 +31805,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135464668274</v>
+        <v>3.55135440826416</v>
       </c>
       <c r="H1084" t="n">
         <v>183394</v>
@@ -31863,7 +31863,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1086" t="n">
         <v>39968</v>
@@ -31892,7 +31892,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1087" t="n">
         <v>19044</v>
@@ -31950,7 +31950,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59967231750488</v>
+        <v>3.5996720790863</v>
       </c>
       <c r="H1089" t="n">
         <v>21496</v>
@@ -32037,7 +32037,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1092" t="n">
         <v>4199</v>
@@ -32095,7 +32095,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1094" t="n">
         <v>2930</v>
@@ -32124,7 +32124,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1095" t="n">
         <v>17824</v>
@@ -32414,7 +32414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1105" t="n">
         <v>8012</v>
@@ -32501,7 +32501,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1108" t="n">
         <v>20364</v>
@@ -32617,7 +32617,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1112" t="n">
         <v>8014</v>
@@ -32646,7 +32646,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H1113" t="n">
         <v>5992</v>
@@ -32791,7 +32791,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1118" t="n">
         <v>7468</v>
@@ -32878,7 +32878,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1121" t="n">
         <v>7108</v>
@@ -32907,7 +32907,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1122" t="n">
         <v>3566</v>
@@ -32965,7 +32965,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1124" t="n">
         <v>6159</v>
@@ -32994,7 +32994,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1125" t="n">
         <v>36559</v>
@@ -33023,7 +33023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1126" t="n">
         <v>5854</v>
@@ -33081,7 +33081,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1128" t="n">
         <v>85216</v>
@@ -33110,7 +33110,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1129" t="n">
         <v>44308</v>
@@ -33168,7 +33168,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1131" t="n">
         <v>2341</v>
@@ -33197,7 +33197,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1132" t="n">
         <v>13385</v>
@@ -33371,7 +33371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1138" t="n">
         <v>23416</v>
@@ -33516,7 +33516,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H1143" t="n">
         <v>14293</v>
@@ -33574,7 +33574,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1145" t="n">
         <v>44949</v>
@@ -33719,7 +33719,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H1150" t="n">
         <v>7061</v>
@@ -33748,7 +33748,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H1151" t="n">
         <v>5770</v>
@@ -33777,7 +33777,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1152" t="n">
         <v>12871</v>
@@ -33806,7 +33806,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1153" t="n">
         <v>21159</v>
@@ -33835,7 +33835,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1154" t="n">
         <v>63339</v>
@@ -33864,7 +33864,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1155" t="n">
         <v>13966</v>
@@ -34125,7 +34125,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1164" t="n">
         <v>8374</v>
@@ -34154,7 +34154,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1165" t="n">
         <v>8257</v>
@@ -34241,7 +34241,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1168" t="n">
         <v>51543</v>
@@ -34299,7 +34299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1170" t="n">
         <v>8138</v>
@@ -34415,7 +34415,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1174" t="n">
         <v>18764</v>
@@ -34589,7 +34589,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1180" t="n">
         <v>22131</v>
@@ -34705,7 +34705,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1184" t="n">
         <v>1634</v>
@@ -34734,7 +34734,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1185" t="n">
         <v>1460</v>
@@ -34792,7 +34792,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1187" t="n">
         <v>21143</v>
@@ -34821,7 +34821,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1188" t="n">
         <v>8937</v>
@@ -34850,7 +34850,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1189" t="n">
         <v>9771</v>
@@ -34908,7 +34908,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1191" t="n">
         <v>3139</v>
@@ -34966,7 +34966,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1193" t="n">
         <v>23650</v>
@@ -34995,7 +34995,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1194" t="n">
         <v>30769</v>
@@ -35024,7 +35024,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1195" t="n">
         <v>53170</v>
@@ -35053,7 +35053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1196" t="n">
         <v>8141</v>
@@ -35082,7 +35082,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1197" t="n">
         <v>18888</v>
@@ -35111,7 +35111,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1198" t="n">
         <v>2167</v>
@@ -35140,7 +35140,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1199" t="n">
         <v>21694</v>
@@ -35169,7 +35169,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1200" t="n">
         <v>30561</v>
@@ -35227,7 +35227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1202" t="n">
         <v>13802</v>
@@ -35285,7 +35285,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1204" t="n">
         <v>39802</v>
@@ -35430,7 +35430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1209" t="n">
         <v>13920</v>
@@ -35952,7 +35952,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H1227" t="n">
         <v>11126</v>
@@ -36010,7 +36010,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263502120972</v>
+        <v>4.23263454437256</v>
       </c>
       <c r="H1229" t="n">
         <v>30135</v>
@@ -36184,7 +36184,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1235" t="n">
         <v>87770</v>
@@ -36242,7 +36242,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1237" t="n">
         <v>86783</v>
@@ -36271,7 +36271,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095245361328</v>
+        <v>4.28095197677612</v>
       </c>
       <c r="H1238" t="n">
         <v>10697</v>
@@ -36300,7 +36300,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1239" t="n">
         <v>633742</v>
@@ -36387,7 +36387,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1242" t="n">
         <v>33483</v>
@@ -36416,7 +36416,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297096252441</v>
+        <v>4.22297143936157</v>
       </c>
       <c r="H1243" t="n">
         <v>111404</v>
@@ -36474,7 +36474,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1245" t="n">
         <v>71817</v>
@@ -36503,7 +36503,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1246" t="n">
         <v>15207</v>
@@ -36561,7 +36561,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1248" t="n">
         <v>263769</v>
@@ -36648,7 +36648,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H1251" t="n">
         <v>22609</v>
@@ -36822,7 +36822,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1257" t="n">
         <v>38711</v>
@@ -36909,7 +36909,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1260" t="n">
         <v>48866</v>
@@ -36938,7 +36938,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1261" t="n">
         <v>88377</v>
@@ -37054,7 +37054,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1265" t="n">
         <v>106306</v>
@@ -37547,7 +37547,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1282" t="n">
         <v>41916</v>
@@ -37663,7 +37663,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1286" t="n">
         <v>18275</v>
@@ -37692,7 +37692,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1287" t="n">
         <v>38266</v>
@@ -37721,7 +37721,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1288" t="n">
         <v>44950</v>
@@ -37750,7 +37750,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1289" t="n">
         <v>154179</v>
@@ -37808,7 +37808,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1291" t="n">
         <v>48801</v>
@@ -37895,7 +37895,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1294" t="n">
         <v>76505</v>
@@ -38011,7 +38011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1298" t="n">
         <v>108894</v>
@@ -38040,7 +38040,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1299" t="n">
         <v>13424</v>
@@ -38098,7 +38098,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1301" t="n">
         <v>3761</v>
@@ -38127,7 +38127,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725185394287</v>
+        <v>4.38725137710571</v>
       </c>
       <c r="H1302" t="n">
         <v>18383</v>
@@ -38272,7 +38272,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1307" t="n">
         <v>33977</v>
@@ -38330,7 +38330,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1309" t="n">
         <v>8950</v>
@@ -38562,7 +38562,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1317" t="n">
         <v>2395</v>
@@ -38620,7 +38620,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1319" t="n">
         <v>2013</v>
@@ -38649,7 +38649,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1320" t="n">
         <v>19847</v>
@@ -38678,7 +38678,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1321" t="n">
         <v>6721</v>
@@ -38707,7 +38707,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1322" t="n">
         <v>4183885</v>
@@ -38968,7 +38968,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1331" t="n">
         <v>17017</v>
@@ -38997,7 +38997,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1332" t="n">
         <v>17023</v>
@@ -39113,7 +39113,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1336" t="n">
         <v>7875</v>
@@ -39171,7 +39171,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1338" t="n">
         <v>579091</v>
@@ -39200,7 +39200,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1339" t="n">
         <v>13097</v>
@@ -39258,7 +39258,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1341" t="n">
         <v>18512</v>
@@ -39345,7 +39345,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1344" t="n">
         <v>142420</v>
@@ -39374,7 +39374,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1345" t="n">
         <v>32214</v>
@@ -39403,7 +39403,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1346" t="n">
         <v>117615</v>
@@ -39461,7 +39461,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1348" t="n">
         <v>45261</v>
@@ -39490,7 +39490,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1349" t="n">
         <v>53301</v>
@@ -39519,7 +39519,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1350" t="n">
         <v>53244</v>
@@ -39548,7 +39548,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1351" t="n">
         <v>128034</v>
@@ -39751,7 +39751,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1358" t="n">
         <v>28701</v>
@@ -39954,7 +39954,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1365" t="n">
         <v>13059</v>
@@ -40012,7 +40012,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1367" t="n">
         <v>15645</v>
@@ -40041,7 +40041,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1368" t="n">
         <v>36938</v>
@@ -40070,7 +40070,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1369" t="n">
         <v>30397</v>
@@ -40099,7 +40099,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1370" t="n">
         <v>59503</v>
@@ -40128,7 +40128,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1371" t="n">
         <v>7128</v>
@@ -40186,7 +40186,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1373" t="n">
         <v>53763</v>
@@ -40244,7 +40244,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1375" t="n">
         <v>80223</v>
@@ -40360,7 +40360,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1379" t="n">
         <v>35399</v>
@@ -40389,7 +40389,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1380" t="n">
         <v>66631</v>
@@ -40418,7 +40418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1381" t="n">
         <v>36618</v>
@@ -40476,7 +40476,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1383" t="n">
         <v>9917</v>
@@ -40563,7 +40563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1386" t="n">
         <v>14411</v>
@@ -40592,7 +40592,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1387" t="n">
         <v>5736</v>
@@ -40650,7 +40650,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1389" t="n">
         <v>33151</v>
@@ -40708,7 +40708,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1391" t="n">
         <v>172952</v>
@@ -40737,7 +40737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1392" t="n">
         <v>27304</v>
@@ -40766,7 +40766,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1393" t="n">
         <v>10573</v>
@@ -40824,7 +40824,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1395" t="n">
         <v>16020</v>
@@ -40882,7 +40882,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1397" t="n">
         <v>25629</v>
@@ -40911,7 +40911,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1398" t="n">
         <v>21495</v>
@@ -40940,7 +40940,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1399" t="n">
         <v>11491</v>
@@ -40969,7 +40969,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1400" t="n">
         <v>70839</v>
@@ -41027,7 +41027,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1402" t="n">
         <v>25324</v>
@@ -41346,7 +41346,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1413" t="n">
         <v>23278</v>
@@ -41433,7 +41433,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1416" t="n">
         <v>86929</v>
@@ -41578,7 +41578,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1421" t="n">
         <v>84292</v>
@@ -41636,7 +41636,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1423" t="n">
         <v>17733</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1430" t="n">
         <v>17929</v>
@@ -42100,7 +42100,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1439" t="n">
         <v>30849</v>
@@ -42245,7 +42245,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1444" t="n">
         <v>16400</v>
@@ -42448,7 +42448,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1451" t="n">
         <v>10674</v>
@@ -42593,7 +42593,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1456" t="n">
         <v>14950</v>
@@ -42651,7 +42651,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1458" t="n">
         <v>53885</v>
@@ -42680,7 +42680,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1459" t="n">
         <v>43894</v>
@@ -42825,7 +42825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1464" t="n">
         <v>6023</v>
@@ -42854,7 +42854,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1465" t="n">
         <v>13746</v>
@@ -42941,7 +42941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1468" t="n">
         <v>17342</v>
@@ -43318,7 +43318,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1481" t="n">
         <v>4088</v>
@@ -43434,7 +43434,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1485" t="n">
         <v>18559</v>
@@ -43463,7 +43463,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1486" t="n">
         <v>5313</v>
@@ -43695,7 +43695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1494" t="n">
         <v>10058</v>
@@ -43724,7 +43724,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1495" t="n">
         <v>6566</v>
@@ -43898,7 +43898,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1501" t="n">
         <v>24701</v>
@@ -43927,7 +43927,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1502" t="n">
         <v>13712</v>
@@ -43985,7 +43985,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1504" t="n">
         <v>17967</v>
@@ -44014,7 +44014,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1505" t="n">
         <v>12753</v>
@@ -44043,7 +44043,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1506" t="n">
         <v>4017</v>
@@ -44304,7 +44304,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1515" t="n">
         <v>32760</v>
@@ -44420,7 +44420,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1519" t="n">
         <v>13224</v>
@@ -44449,7 +44449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1520" t="n">
         <v>15389</v>
@@ -44536,7 +44536,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H1523" t="n">
         <v>23568</v>
@@ -44652,7 +44652,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1527" t="n">
         <v>12057</v>
@@ -44681,7 +44681,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1528" t="n">
         <v>10102</v>
@@ -44710,7 +44710,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H1529" t="n">
         <v>11999</v>
@@ -44768,7 +44768,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H1531" t="n">
         <v>23916</v>
@@ -44797,7 +44797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1532" t="n">
         <v>53597</v>
@@ -44826,7 +44826,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1533" t="n">
         <v>35027</v>
@@ -44913,7 +44913,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H1536" t="n">
         <v>27398</v>
@@ -45087,7 +45087,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1542" t="n">
         <v>10776</v>
@@ -45290,7 +45290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H1549" t="n">
         <v>17670</v>
@@ -45348,7 +45348,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H1551" t="n">
         <v>6270</v>
@@ -45551,7 +45551,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1558" t="n">
         <v>9714</v>
@@ -45580,7 +45580,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1559" t="n">
         <v>9223</v>
@@ -45667,7 +45667,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1562" t="n">
         <v>3769</v>
@@ -45870,7 +45870,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1569" t="n">
         <v>59041</v>
@@ -45928,7 +45928,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1571" t="n">
         <v>19659</v>
@@ -45986,7 +45986,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1573" t="n">
         <v>6033</v>
@@ -46102,7 +46102,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1577" t="n">
         <v>16481</v>
@@ -46131,7 +46131,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1578" t="n">
         <v>16827</v>
@@ -46247,7 +46247,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1582" t="n">
         <v>12336</v>
@@ -46537,7 +46537,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1592" t="n">
         <v>40020</v>
@@ -46566,7 +46566,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1593" t="n">
         <v>20842</v>
@@ -47175,7 +47175,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1614" t="n">
         <v>15568</v>
@@ -47262,7 +47262,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1617" t="n">
         <v>1706</v>
@@ -47320,7 +47320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1619" t="n">
         <v>97926</v>
@@ -47349,7 +47349,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1620" t="n">
         <v>14080</v>
@@ -47378,7 +47378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1621" t="n">
         <v>19839</v>
@@ -47436,7 +47436,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1623" t="n">
         <v>16886</v>
@@ -47552,7 +47552,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605512619019</v>
+        <v>4.99605560302734</v>
       </c>
       <c r="H1627" t="n">
         <v>60722</v>
@@ -47581,7 +47581,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1628" t="n">
         <v>24838</v>
@@ -47610,7 +47610,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1629" t="n">
         <v>21313</v>
@@ -47639,7 +47639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1630" t="n">
         <v>23268</v>
@@ -47668,7 +47668,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1631" t="n">
         <v>2356</v>
@@ -47697,7 +47697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1632" t="n">
         <v>26681</v>
@@ -47755,7 +47755,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H1634" t="n">
         <v>18116</v>
@@ -47842,7 +47842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1637" t="n">
         <v>9629</v>
@@ -47900,7 +47900,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H1639" t="n">
         <v>10513</v>
@@ -47929,7 +47929,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1640" t="n">
         <v>5633</v>
@@ -47987,7 +47987,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H1642" t="n">
         <v>29183</v>
@@ -58868,6 +58868,35 @@
         <v>9406</v>
       </c>
       <c r="I2017" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2018" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2018" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D2018" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="G2018" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="H2018" t="n">
+        <v>23235</v>
+      </c>
+      <c r="I2018" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835204124451</v>
+        <v>3.50835180282593</v>
       </c>
       <c r="H5" t="n">
         <v>168607</v>
@@ -572,7 +572,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290766716003</v>
+        <v>3.59290790557861</v>
       </c>
       <c r="H7" t="n">
         <v>115707</v>
@@ -630,7 +630,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555630683899</v>
+        <v>3.54555654525757</v>
       </c>
       <c r="H9" t="n">
         <v>18987</v>
@@ -717,7 +717,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694540023804</v>
+        <v>3.47694516181946</v>
       </c>
       <c r="H12" t="n">
         <v>25574</v>
@@ -775,7 +775,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018098831177</v>
+        <v>3.47018074989319</v>
       </c>
       <c r="H14" t="n">
         <v>14046</v>
@@ -804,7 +804,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H15" t="n">
         <v>25673</v>
@@ -833,7 +833,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H16" t="n">
         <v>17829</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H20" t="n">
         <v>24337</v>
@@ -1007,7 +1007,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H22" t="n">
         <v>15060</v>
@@ -1065,7 +1065,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710980415344</v>
+        <v>3.58710956573486</v>
       </c>
       <c r="H24" t="n">
         <v>31246</v>
@@ -1297,7 +1297,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299379348755</v>
+        <v>3.53299355506897</v>
       </c>
       <c r="H32" t="n">
         <v>12155</v>
@@ -1326,7 +1326,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H33" t="n">
         <v>2992</v>
@@ -1384,7 +1384,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185546875</v>
+        <v>3.65185570716858</v>
       </c>
       <c r="H35" t="n">
         <v>9616</v>
@@ -1500,7 +1500,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H39" t="n">
         <v>33223</v>
@@ -1558,7 +1558,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464311599731</v>
+        <v>3.84464335441589</v>
       </c>
       <c r="H41" t="n">
         <v>67310</v>
@@ -1674,7 +1674,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869815826416</v>
+        <v>3.82869839668274</v>
       </c>
       <c r="H45" t="n">
         <v>15050</v>
@@ -1761,7 +1761,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243480682373</v>
+        <v>3.92243504524231</v>
       </c>
       <c r="H48" t="n">
         <v>7064</v>
@@ -1848,7 +1848,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H51" t="n">
         <v>10244</v>
@@ -2138,7 +2138,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863742828369</v>
+        <v>3.75863766670227</v>
       </c>
       <c r="H61" t="n">
         <v>18963</v>
@@ -2167,7 +2167,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H62" t="n">
         <v>25241</v>
@@ -2254,7 +2254,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H65" t="n">
         <v>14098</v>
@@ -2283,7 +2283,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364147186279</v>
+        <v>3.64364123344421</v>
       </c>
       <c r="H66" t="n">
         <v>24444</v>
@@ -2312,7 +2312,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H67" t="n">
         <v>14328</v>
@@ -2457,7 +2457,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422080993652</v>
+        <v>3.91422057151794</v>
       </c>
       <c r="H72" t="n">
         <v>37886</v>
@@ -2544,7 +2544,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H75" t="n">
         <v>61176</v>
@@ -2573,7 +2573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H76" t="n">
         <v>4871</v>
@@ -2631,7 +2631,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615319252014</v>
+        <v>3.91615343093872</v>
       </c>
       <c r="H78" t="n">
         <v>28408</v>
@@ -2660,7 +2660,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331522941589</v>
+        <v>3.98331546783447</v>
       </c>
       <c r="H79" t="n">
         <v>15491</v>
@@ -2689,7 +2689,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H80" t="n">
         <v>8568</v>
@@ -2718,7 +2718,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.95287489891052</v>
+        <v>3.9528751373291</v>
       </c>
       <c r="H81" t="n">
         <v>11304</v>
@@ -2747,7 +2747,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354797363281</v>
+        <v>3.93354773521423</v>
       </c>
       <c r="H82" t="n">
         <v>1333</v>
@@ -2805,7 +2805,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445379257202</v>
+        <v>3.86445355415344</v>
       </c>
       <c r="H84" t="n">
         <v>14743</v>
@@ -2892,7 +2892,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H87" t="n">
         <v>16436</v>
@@ -2921,7 +2921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H88" t="n">
         <v>70067</v>
@@ -2950,7 +2950,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H89" t="n">
         <v>20248</v>
@@ -2979,7 +2979,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H90" t="n">
         <v>9804</v>
@@ -3008,7 +3008,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H91" t="n">
         <v>8029</v>
@@ -3124,7 +3124,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H95" t="n">
         <v>6789</v>
@@ -3153,7 +3153,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H96" t="n">
         <v>16453</v>
@@ -3182,7 +3182,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H97" t="n">
         <v>13893</v>
@@ -3211,7 +3211,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H98" t="n">
         <v>34445</v>
@@ -3269,7 +3269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H100" t="n">
         <v>5569</v>
@@ -3327,7 +3327,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H102" t="n">
         <v>17175</v>
@@ -3385,7 +3385,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H104" t="n">
         <v>4792</v>
@@ -3443,7 +3443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H106" t="n">
         <v>12618</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H107" t="n">
         <v>7801</v>
@@ -3530,7 +3530,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H109" t="n">
         <v>27377</v>
@@ -3559,7 +3559,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H110" t="n">
         <v>9652</v>
@@ -3588,7 +3588,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H111" t="n">
         <v>22427</v>
@@ -3646,7 +3646,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H113" t="n">
         <v>5635</v>
@@ -3675,7 +3675,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H114" t="n">
         <v>12247</v>
@@ -3704,7 +3704,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H115" t="n">
         <v>46534</v>
@@ -3762,7 +3762,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H117" t="n">
         <v>14370</v>
@@ -3791,7 +3791,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H118" t="n">
         <v>20871</v>
@@ -3849,7 +3849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H120" t="n">
         <v>51861</v>
@@ -3907,7 +3907,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H122" t="n">
         <v>24632</v>
@@ -3965,7 +3965,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H124" t="n">
         <v>9251</v>
@@ -4023,7 +4023,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H126" t="n">
         <v>23445</v>
@@ -4052,7 +4052,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H127" t="n">
         <v>13288</v>
@@ -4226,7 +4226,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H133" t="n">
         <v>69275</v>
@@ -4255,7 +4255,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.6866443157196</v>
+        <v>3.68664455413818</v>
       </c>
       <c r="H134" t="n">
         <v>83826</v>
@@ -4284,7 +4284,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H135" t="n">
         <v>38411</v>
@@ -4342,7 +4342,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H137" t="n">
         <v>28361</v>
@@ -4371,7 +4371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H138" t="n">
         <v>16251</v>
@@ -4400,7 +4400,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H139" t="n">
         <v>24663</v>
@@ -4661,7 +4661,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H148" t="n">
         <v>6408</v>
@@ -4690,7 +4690,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H149" t="n">
         <v>17007</v>
@@ -4748,7 +4748,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H151" t="n">
         <v>51508</v>
@@ -4893,7 +4893,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H156" t="n">
         <v>57059</v>
@@ -4951,7 +4951,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H158" t="n">
         <v>51199</v>
@@ -5821,7 +5821,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251308441162</v>
+        <v>4.09251356124878</v>
       </c>
       <c r="H188" t="n">
         <v>3584</v>
@@ -5995,7 +5995,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H194" t="n">
         <v>11423</v>
@@ -6459,7 +6459,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H210" t="n">
         <v>4401</v>
@@ -6546,7 +6546,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H213" t="n">
         <v>14225</v>
@@ -6720,7 +6720,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H219" t="n">
         <v>109205</v>
@@ -6981,7 +6981,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H228" t="n">
         <v>32762</v>
@@ -7358,7 +7358,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501791000366</v>
+        <v>4.59501838684082</v>
       </c>
       <c r="H241" t="n">
         <v>82951</v>
@@ -7416,7 +7416,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H243" t="n">
         <v>10325</v>
@@ -7445,7 +7445,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H244" t="n">
         <v>8300</v>
@@ -7590,7 +7590,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H249" t="n">
         <v>50047</v>
@@ -7619,7 +7619,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H250" t="n">
         <v>91315</v>
@@ -7648,7 +7648,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H251" t="n">
         <v>63937</v>
@@ -7677,7 +7677,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929832458496</v>
+        <v>4.75929880142212</v>
       </c>
       <c r="H252" t="n">
         <v>3333</v>
@@ -7793,7 +7793,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H256" t="n">
         <v>24390</v>
@@ -7967,7 +7967,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H262" t="n">
         <v>8895</v>
@@ -8025,7 +8025,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727981567383</v>
+        <v>4.81727933883667</v>
       </c>
       <c r="H264" t="n">
         <v>44506</v>
@@ -8054,7 +8054,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H265" t="n">
         <v>48189</v>
@@ -8083,7 +8083,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H266" t="n">
         <v>41705</v>
@@ -8141,7 +8141,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H268" t="n">
         <v>123324</v>
@@ -8228,7 +8228,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740079879761</v>
+        <v>4.95740127563477</v>
       </c>
       <c r="H271" t="n">
         <v>6925</v>
@@ -8315,7 +8315,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H274" t="n">
         <v>136710</v>
@@ -8344,7 +8344,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H275" t="n">
         <v>260348</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H278" t="n">
         <v>25684</v>
@@ -8547,7 +8547,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H282" t="n">
         <v>57869</v>
@@ -8924,7 +8924,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H295" t="n">
         <v>20573</v>
@@ -9040,7 +9040,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H299" t="n">
         <v>19695</v>
@@ -9243,7 +9243,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H306" t="n">
         <v>19157</v>
@@ -9359,7 +9359,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596115112305</v>
+        <v>5.28596162796021</v>
       </c>
       <c r="H310" t="n">
         <v>19428</v>
@@ -9417,7 +9417,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H312" t="n">
         <v>4283</v>
@@ -9533,7 +9533,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H316" t="n">
         <v>151029</v>
@@ -9620,7 +9620,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H319" t="n">
         <v>12312</v>
@@ -9649,7 +9649,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H320" t="n">
         <v>162473</v>
@@ -9765,7 +9765,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H324" t="n">
         <v>99309</v>
@@ -9852,7 +9852,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134527206421</v>
+        <v>5.13134479522705</v>
       </c>
       <c r="H327" t="n">
         <v>34058</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H329" t="n">
         <v>26368</v>
@@ -9968,7 +9968,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H331" t="n">
         <v>32218</v>
@@ -9997,7 +9997,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H332" t="n">
         <v>81218</v>
@@ -10026,7 +10026,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H333" t="n">
         <v>14865</v>
@@ -10258,7 +10258,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H341" t="n">
         <v>82529</v>
@@ -10287,7 +10287,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H342" t="n">
         <v>98211</v>
@@ -10461,7 +10461,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H348" t="n">
         <v>32626</v>
@@ -10635,7 +10635,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H354" t="n">
         <v>33125</v>
@@ -10751,7 +10751,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H358" t="n">
         <v>44086</v>
@@ -10867,7 +10867,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H362" t="n">
         <v>11155</v>
@@ -11041,7 +11041,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H368" t="n">
         <v>26463</v>
@@ -11099,7 +11099,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H370" t="n">
         <v>8841</v>
@@ -11186,7 +11186,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H373" t="n">
         <v>16343</v>
@@ -11302,7 +11302,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489692687988</v>
+        <v>4.45489645004272</v>
       </c>
       <c r="H377" t="n">
         <v>6689</v>
@@ -11418,7 +11418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H381" t="n">
         <v>31236</v>
@@ -11447,7 +11447,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H382" t="n">
         <v>9513</v>
@@ -11505,7 +11505,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H384" t="n">
         <v>12160</v>
@@ -11563,7 +11563,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H386" t="n">
         <v>5668</v>
@@ -11679,7 +11679,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H390" t="n">
         <v>5996</v>
@@ -11737,7 +11737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H392" t="n">
         <v>19706</v>
@@ -11795,7 +11795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H394" t="n">
         <v>18905</v>
@@ -12027,7 +12027,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H402" t="n">
         <v>20308</v>
@@ -12288,7 +12288,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H411" t="n">
         <v>7185</v>
@@ -12317,7 +12317,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H412" t="n">
         <v>7082</v>
@@ -12375,7 +12375,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H414" t="n">
         <v>49474</v>
@@ -12520,7 +12520,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H419" t="n">
         <v>7439</v>
@@ -12549,7 +12549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H420" t="n">
         <v>15236</v>
@@ -12607,7 +12607,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H422" t="n">
         <v>10351</v>
@@ -12636,7 +12636,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H423" t="n">
         <v>17376</v>
@@ -12810,7 +12810,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H429" t="n">
         <v>7532</v>
@@ -12868,7 +12868,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H431" t="n">
         <v>2225</v>
@@ -12984,7 +12984,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H435" t="n">
         <v>6281</v>
@@ -13013,7 +13013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H436" t="n">
         <v>7095</v>
@@ -13332,7 +13332,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H447" t="n">
         <v>1474</v>
@@ -13361,7 +13361,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H452" t="n">
         <v>5271</v>
@@ -13564,7 +13564,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H455" t="n">
         <v>7161</v>
@@ -13622,7 +13622,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H457" t="n">
         <v>13780</v>
@@ -13825,7 +13825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H464" t="n">
         <v>16567</v>
@@ -13883,7 +13883,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H466" t="n">
         <v>4338</v>
@@ -13912,7 +13912,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H467" t="n">
         <v>6710</v>
@@ -14028,7 +14028,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H471" t="n">
         <v>8536</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H487" t="n">
         <v>22603</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H491" t="n">
         <v>18592</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H493" t="n">
         <v>6171</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H494" t="n">
         <v>7707</v>
@@ -14927,7 +14927,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H502" t="n">
         <v>22877</v>
@@ -15130,7 +15130,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H509" t="n">
         <v>4568</v>
@@ -15304,7 +15304,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H515" t="n">
         <v>32842</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H517" t="n">
         <v>11854</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H518" t="n">
         <v>8330</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H522" t="n">
         <v>3006</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H524" t="n">
         <v>29907</v>
@@ -15623,7 +15623,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H526" t="n">
         <v>1616</v>
@@ -15855,7 +15855,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H534" t="n">
         <v>33564</v>
@@ -15884,7 +15884,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H535" t="n">
         <v>17947</v>
@@ -16116,7 +16116,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H543" t="n">
         <v>7536</v>
@@ -16145,7 +16145,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H544" t="n">
         <v>20916</v>
@@ -16203,7 +16203,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H546" t="n">
         <v>18431</v>
@@ -16232,7 +16232,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H547" t="n">
         <v>18024</v>
@@ -16261,7 +16261,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H548" t="n">
         <v>5276</v>
@@ -16290,7 +16290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H549" t="n">
         <v>11659</v>
@@ -16319,7 +16319,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H550" t="n">
         <v>9307</v>
@@ -16464,7 +16464,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H555" t="n">
         <v>211195</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H558" t="n">
         <v>68260</v>
@@ -16725,7 +16725,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H564" t="n">
         <v>44216</v>
@@ -16928,7 +16928,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H571" t="n">
         <v>137820</v>
@@ -16957,7 +16957,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H572" t="n">
         <v>46726</v>
@@ -17102,7 +17102,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H577" t="n">
         <v>232133</v>
@@ -17218,7 +17218,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H581" t="n">
         <v>183006</v>
@@ -17276,7 +17276,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H583" t="n">
         <v>110634</v>
@@ -17334,7 +17334,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H585" t="n">
         <v>83401</v>
@@ -17450,7 +17450,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H589" t="n">
         <v>48955</v>
@@ -17479,7 +17479,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H590" t="n">
         <v>54246</v>
@@ -17595,7 +17595,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H594" t="n">
         <v>141610</v>
@@ -17798,7 +17798,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H601" t="n">
         <v>21002</v>
@@ -17885,7 +17885,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H604" t="n">
         <v>23320</v>
@@ -17972,7 +17972,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H607" t="n">
         <v>46484</v>
@@ -18320,7 +18320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H619" t="n">
         <v>4323</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H623" t="n">
         <v>16947</v>
@@ -18465,7 +18465,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H624" t="n">
         <v>5894</v>
@@ -18523,7 +18523,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H626" t="n">
         <v>25679</v>
@@ -18639,7 +18639,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H630" t="n">
         <v>33871</v>
@@ -18697,7 +18697,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H632" t="n">
         <v>24188</v>
@@ -18784,7 +18784,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H635" t="n">
         <v>57265</v>
@@ -19074,7 +19074,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H645" t="n">
         <v>121832</v>
@@ -19103,7 +19103,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H646" t="n">
         <v>46978</v>
@@ -19480,7 +19480,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H659" t="n">
         <v>58410</v>
@@ -19509,7 +19509,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H660" t="n">
         <v>94430</v>
@@ -19538,7 +19538,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H661" t="n">
         <v>16435</v>
@@ -19625,7 +19625,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H664" t="n">
         <v>36840</v>
@@ -19770,7 +19770,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H669" t="n">
         <v>26798</v>
@@ -20002,7 +20002,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H677" t="n">
         <v>3700</v>
@@ -20031,7 +20031,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H678" t="n">
         <v>31808</v>
@@ -20060,7 +20060,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H679" t="n">
         <v>28368</v>
@@ -20118,7 +20118,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H681" t="n">
         <v>19635</v>
@@ -20321,7 +20321,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H688" t="n">
         <v>116323</v>
@@ -20350,7 +20350,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H689" t="n">
         <v>33063</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H690" t="n">
         <v>12669</v>
@@ -20582,7 +20582,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H697" t="n">
         <v>29126</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H698" t="n">
         <v>31677</v>
@@ -20669,7 +20669,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H700" t="n">
         <v>1753</v>
@@ -20698,7 +20698,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H701" t="n">
         <v>9847</v>
@@ -20727,7 +20727,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H702" t="n">
         <v>15481</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H703" t="n">
         <v>4841</v>
@@ -20785,7 +20785,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H704" t="n">
         <v>20397</v>
@@ -20814,7 +20814,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H705" t="n">
         <v>22265</v>
@@ -20872,7 +20872,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H707" t="n">
         <v>56099</v>
@@ -20901,7 +20901,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H708" t="n">
         <v>72110</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H710" t="n">
         <v>41126</v>
@@ -20988,7 +20988,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H711" t="n">
         <v>41372</v>
@@ -21075,7 +21075,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H714" t="n">
         <v>27761</v>
@@ -21249,7 +21249,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H720" t="n">
         <v>30084</v>
@@ -21365,7 +21365,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H724" t="n">
         <v>22097</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H725" t="n">
         <v>21424</v>
@@ -21481,7 +21481,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H728" t="n">
         <v>28785</v>
@@ -21539,7 +21539,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H730" t="n">
         <v>63831</v>
@@ -21568,7 +21568,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H731" t="n">
         <v>14790</v>
@@ -21626,7 +21626,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H733" t="n">
         <v>54638</v>
@@ -21655,7 +21655,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H734" t="n">
         <v>25806</v>
@@ -21771,7 +21771,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H738" t="n">
         <v>9042</v>
@@ -21858,7 +21858,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H741" t="n">
         <v>25001</v>
@@ -21945,7 +21945,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H744" t="n">
         <v>36541</v>
@@ -22119,7 +22119,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H750" t="n">
         <v>24595</v>
@@ -22148,7 +22148,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H751" t="n">
         <v>7605</v>
@@ -22177,7 +22177,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H752" t="n">
         <v>31505</v>
@@ -22235,7 +22235,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H754" t="n">
         <v>15983</v>
@@ -22293,7 +22293,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H756" t="n">
         <v>24115</v>
@@ -22322,7 +22322,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H757" t="n">
         <v>23156</v>
@@ -22351,7 +22351,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H758" t="n">
         <v>22826</v>
@@ -22380,7 +22380,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H759" t="n">
         <v>27789</v>
@@ -22554,7 +22554,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H765" t="n">
         <v>90704</v>
@@ -22641,7 +22641,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H768" t="n">
         <v>25948</v>
@@ -22699,7 +22699,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H770" t="n">
         <v>21002</v>
@@ -22728,7 +22728,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H771" t="n">
         <v>45095</v>
@@ -22757,7 +22757,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H772" t="n">
         <v>32302</v>
@@ -22786,7 +22786,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H773" t="n">
         <v>48385</v>
@@ -22873,7 +22873,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H776" t="n">
         <v>33170</v>
@@ -22902,7 +22902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H777" t="n">
         <v>140269</v>
@@ -22931,7 +22931,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H778" t="n">
         <v>51904</v>
@@ -22989,7 +22989,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H780" t="n">
         <v>26033</v>
@@ -23018,7 +23018,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H781" t="n">
         <v>69932</v>
@@ -23134,7 +23134,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H785" t="n">
         <v>21254</v>
@@ -23424,7 +23424,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H795" t="n">
         <v>129207</v>
@@ -23453,7 +23453,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H796" t="n">
         <v>74996</v>
@@ -23656,7 +23656,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H803" t="n">
         <v>95136</v>
@@ -23830,7 +23830,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H809" t="n">
         <v>42616</v>
@@ -23975,7 +23975,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H814" t="n">
         <v>147606</v>
@@ -24004,7 +24004,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H815" t="n">
         <v>20160</v>
@@ -24062,7 +24062,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H817" t="n">
         <v>48978</v>
@@ -24091,7 +24091,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H818" t="n">
         <v>17601</v>
@@ -24178,7 +24178,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H821" t="n">
         <v>17172</v>
@@ -24207,7 +24207,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H822" t="n">
         <v>21711</v>
@@ -24236,7 +24236,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H823" t="n">
         <v>13038</v>
@@ -24381,7 +24381,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H828" t="n">
         <v>13399</v>
@@ -24700,7 +24700,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H839" t="n">
         <v>10091</v>
@@ -24729,7 +24729,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H840" t="n">
         <v>20843</v>
@@ -24990,7 +24990,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H849" t="n">
         <v>88040</v>
@@ -25048,7 +25048,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H851" t="n">
         <v>61678</v>
@@ -25077,7 +25077,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H852" t="n">
         <v>25922</v>
@@ -25222,7 +25222,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H857" t="n">
         <v>26131</v>
@@ -25309,7 +25309,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H860" t="n">
         <v>25865</v>
@@ -25483,7 +25483,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H866" t="n">
         <v>10855</v>
@@ -25541,7 +25541,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H868" t="n">
         <v>4022</v>
@@ -25570,7 +25570,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.62400817871094</v>
+        <v>4.6240086555481</v>
       </c>
       <c r="H869" t="n">
         <v>9713</v>
@@ -25628,7 +25628,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H871" t="n">
         <v>3876</v>
@@ -25802,7 +25802,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H877" t="n">
         <v>1609</v>
@@ -26179,7 +26179,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H890" t="n">
         <v>21852</v>
@@ -26208,7 +26208,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309289932251</v>
+        <v>4.36309242248535</v>
       </c>
       <c r="H891" t="n">
         <v>19273</v>
@@ -26237,7 +26237,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H892" t="n">
         <v>9208</v>
@@ -26295,7 +26295,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H894" t="n">
         <v>13445</v>
@@ -26324,7 +26324,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645755767822</v>
+        <v>4.26645708084106</v>
       </c>
       <c r="H895" t="n">
         <v>43685</v>
@@ -26440,7 +26440,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H899" t="n">
         <v>27960</v>
@@ -26498,7 +26498,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H901" t="n">
         <v>33825</v>
@@ -26672,7 +26672,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H907" t="n">
         <v>15181</v>
@@ -26730,7 +26730,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621439933777</v>
+        <v>3.98621416091919</v>
       </c>
       <c r="H909" t="n">
         <v>14992</v>
@@ -26904,7 +26904,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H915" t="n">
         <v>53863</v>
@@ -27049,7 +27049,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H920" t="n">
         <v>5004</v>
@@ -27078,7 +27078,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H921" t="n">
         <v>4290</v>
@@ -27136,7 +27136,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H923" t="n">
         <v>8482</v>
@@ -27165,7 +27165,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453254699707</v>
+        <v>4.03453207015991</v>
       </c>
       <c r="H924" t="n">
         <v>16764</v>
@@ -27513,7 +27513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H936" t="n">
         <v>1516</v>
@@ -27629,7 +27629,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H940" t="n">
         <v>4899</v>
@@ -27658,7 +27658,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H941" t="n">
         <v>56027</v>
@@ -27716,7 +27716,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H943" t="n">
         <v>7945</v>
@@ -27861,7 +27861,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H948" t="n">
         <v>9054</v>
@@ -27890,7 +27890,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H949" t="n">
         <v>974</v>
@@ -28006,7 +28006,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H953" t="n">
         <v>15215</v>
@@ -28122,7 +28122,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193374633789</v>
+        <v>3.82193398475647</v>
       </c>
       <c r="H957" t="n">
         <v>1040</v>
@@ -28151,7 +28151,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H958" t="n">
         <v>5878</v>
@@ -28296,7 +28296,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H963" t="n">
         <v>1069</v>
@@ -28325,7 +28325,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H964" t="n">
         <v>4985</v>
@@ -28354,7 +28354,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H965" t="n">
         <v>1586</v>
@@ -28412,7 +28412,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H967" t="n">
         <v>22825</v>
@@ -28499,7 +28499,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H970" t="n">
         <v>1519</v>
@@ -28615,7 +28615,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H974" t="n">
         <v>61487</v>
@@ -28702,7 +28702,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H977" t="n">
         <v>13657</v>
@@ -28731,7 +28731,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H978" t="n">
         <v>26282</v>
@@ -28818,7 +28818,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H981" t="n">
         <v>4451</v>
@@ -28876,7 +28876,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H983" t="n">
         <v>36877</v>
@@ -28905,7 +28905,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H984" t="n">
         <v>1838</v>
@@ -28963,7 +28963,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H986" t="n">
         <v>12068</v>
@@ -28992,7 +28992,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H987" t="n">
         <v>26097</v>
@@ -29021,7 +29021,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H988" t="n">
         <v>6234</v>
@@ -29224,7 +29224,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H995" t="n">
         <v>11228</v>
@@ -29253,7 +29253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H996" t="n">
         <v>4330</v>
@@ -29282,7 +29282,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H997" t="n">
         <v>8092</v>
@@ -29398,7 +29398,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.9668869972229</v>
+        <v>3.96688747406006</v>
       </c>
       <c r="H1001" t="n">
         <v>517</v>
@@ -29514,7 +29514,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H1005" t="n">
         <v>15349</v>
@@ -29804,7 +29804,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1015" t="n">
         <v>20471</v>
@@ -29891,7 +29891,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1018" t="n">
         <v>24364</v>
@@ -29920,7 +29920,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1019" t="n">
         <v>19551</v>
@@ -30007,7 +30007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1022" t="n">
         <v>3870</v>
@@ -30616,7 +30616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1043" t="n">
         <v>7439</v>
@@ -30703,7 +30703,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1046" t="n">
         <v>15720</v>
@@ -30732,7 +30732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1047" t="n">
         <v>13320</v>
@@ -30790,7 +30790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1049" t="n">
         <v>1434</v>
@@ -30848,7 +30848,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820494651794</v>
+        <v>3.49820470809937</v>
       </c>
       <c r="H1051" t="n">
         <v>22296</v>
@@ -30906,7 +30906,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1053" t="n">
         <v>16504</v>
@@ -30935,7 +30935,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1054" t="n">
         <v>12412</v>
@@ -30993,7 +30993,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1056" t="n">
         <v>12576</v>
@@ -31051,7 +31051,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H1058" t="n">
         <v>9513</v>
@@ -31225,7 +31225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1064" t="n">
         <v>11552</v>
@@ -31254,7 +31254,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H1065" t="n">
         <v>34413</v>
@@ -31283,7 +31283,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1066" t="n">
         <v>64042</v>
@@ -31341,7 +31341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1068" t="n">
         <v>24424</v>
@@ -31399,7 +31399,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1070" t="n">
         <v>18126</v>
@@ -31457,7 +31457,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H1072" t="n">
         <v>26947</v>
@@ -31515,7 +31515,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1074" t="n">
         <v>76053</v>
@@ -31689,7 +31689,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1080" t="n">
         <v>11888</v>
@@ -31718,7 +31718,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1081" t="n">
         <v>87040</v>
@@ -31776,7 +31776,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1083" t="n">
         <v>27634</v>
@@ -31805,7 +31805,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1084" t="n">
         <v>183394</v>
@@ -31863,7 +31863,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1086" t="n">
         <v>39968</v>
@@ -31892,7 +31892,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1087" t="n">
         <v>19044</v>
@@ -31950,7 +31950,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1089" t="n">
         <v>21496</v>
@@ -32037,7 +32037,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1092" t="n">
         <v>4199</v>
@@ -32095,7 +32095,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1094" t="n">
         <v>2930</v>
@@ -32124,7 +32124,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1095" t="n">
         <v>17824</v>
@@ -32414,7 +32414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1105" t="n">
         <v>8012</v>
@@ -32501,7 +32501,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1108" t="n">
         <v>20364</v>
@@ -32617,7 +32617,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1112" t="n">
         <v>8014</v>
@@ -32646,7 +32646,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H1113" t="n">
         <v>5992</v>
@@ -32791,7 +32791,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1118" t="n">
         <v>7468</v>
@@ -32878,7 +32878,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1121" t="n">
         <v>7108</v>
@@ -32907,7 +32907,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1122" t="n">
         <v>3566</v>
@@ -32965,7 +32965,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1124" t="n">
         <v>6159</v>
@@ -32994,7 +32994,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1125" t="n">
         <v>36559</v>
@@ -33023,7 +33023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1126" t="n">
         <v>5854</v>
@@ -33081,7 +33081,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1128" t="n">
         <v>85216</v>
@@ -33110,7 +33110,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1129" t="n">
         <v>44308</v>
@@ -33168,7 +33168,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1131" t="n">
         <v>2341</v>
@@ -33197,7 +33197,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1132" t="n">
         <v>13385</v>
@@ -33371,7 +33371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1138" t="n">
         <v>23416</v>
@@ -33516,7 +33516,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H1143" t="n">
         <v>14293</v>
@@ -33574,7 +33574,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1145" t="n">
         <v>44949</v>
@@ -33719,7 +33719,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H1150" t="n">
         <v>7061</v>
@@ -33748,7 +33748,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1151" t="n">
         <v>5770</v>
@@ -33777,7 +33777,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1152" t="n">
         <v>12871</v>
@@ -33806,7 +33806,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1153" t="n">
         <v>21159</v>
@@ -33835,7 +33835,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1154" t="n">
         <v>63339</v>
@@ -33864,7 +33864,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1155" t="n">
         <v>13966</v>
@@ -34125,7 +34125,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1164" t="n">
         <v>8374</v>
@@ -34154,7 +34154,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1165" t="n">
         <v>8257</v>
@@ -34241,7 +34241,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1168" t="n">
         <v>51543</v>
@@ -34299,7 +34299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1170" t="n">
         <v>8138</v>
@@ -34415,7 +34415,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1174" t="n">
         <v>18764</v>
@@ -34589,7 +34589,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1180" t="n">
         <v>22131</v>
@@ -34705,7 +34705,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1184" t="n">
         <v>1634</v>
@@ -34734,7 +34734,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1185" t="n">
         <v>1460</v>
@@ -34792,7 +34792,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1187" t="n">
         <v>21143</v>
@@ -34821,7 +34821,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1188" t="n">
         <v>8937</v>
@@ -34850,7 +34850,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1189" t="n">
         <v>9771</v>
@@ -34908,7 +34908,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1191" t="n">
         <v>3139</v>
@@ -34966,7 +34966,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1193" t="n">
         <v>23650</v>
@@ -34995,7 +34995,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1194" t="n">
         <v>30769</v>
@@ -35024,7 +35024,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1195" t="n">
         <v>53170</v>
@@ -35053,7 +35053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1196" t="n">
         <v>8141</v>
@@ -35082,7 +35082,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1197" t="n">
         <v>18888</v>
@@ -35111,7 +35111,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1198" t="n">
         <v>2167</v>
@@ -35140,7 +35140,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1199" t="n">
         <v>21694</v>
@@ -35169,7 +35169,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1200" t="n">
         <v>30561</v>
@@ -35227,7 +35227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1202" t="n">
         <v>13802</v>
@@ -35285,7 +35285,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1204" t="n">
         <v>39802</v>
@@ -35430,7 +35430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1209" t="n">
         <v>13920</v>
@@ -35952,7 +35952,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1227" t="n">
         <v>11126</v>
@@ -36010,7 +36010,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H1229" t="n">
         <v>30135</v>
@@ -36184,7 +36184,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1235" t="n">
         <v>87770</v>
@@ -36242,7 +36242,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1237" t="n">
         <v>86783</v>
@@ -36271,7 +36271,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H1238" t="n">
         <v>10697</v>
@@ -36300,7 +36300,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1239" t="n">
         <v>633742</v>
@@ -36387,7 +36387,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1242" t="n">
         <v>33483</v>
@@ -36416,7 +36416,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297143936157</v>
+        <v>4.22297096252441</v>
       </c>
       <c r="H1243" t="n">
         <v>111404</v>
@@ -36474,7 +36474,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1245" t="n">
         <v>71817</v>
@@ -36503,7 +36503,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1246" t="n">
         <v>15207</v>
@@ -36561,7 +36561,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1248" t="n">
         <v>263769</v>
@@ -36648,7 +36648,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H1251" t="n">
         <v>22609</v>
@@ -36822,7 +36822,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1257" t="n">
         <v>38711</v>
@@ -36909,7 +36909,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1260" t="n">
         <v>48866</v>
@@ -36938,7 +36938,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1261" t="n">
         <v>88377</v>
@@ -37054,7 +37054,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1265" t="n">
         <v>106306</v>
@@ -37547,7 +37547,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1282" t="n">
         <v>41916</v>
@@ -37663,7 +37663,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1286" t="n">
         <v>18275</v>
@@ -37692,7 +37692,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1287" t="n">
         <v>38266</v>
@@ -37721,7 +37721,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1288" t="n">
         <v>44950</v>
@@ -37750,7 +37750,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1289" t="n">
         <v>154179</v>
@@ -37808,7 +37808,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1291" t="n">
         <v>48801</v>
@@ -37895,7 +37895,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1294" t="n">
         <v>76505</v>
@@ -38011,7 +38011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1298" t="n">
         <v>108894</v>
@@ -38040,7 +38040,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1299" t="n">
         <v>13424</v>
@@ -38098,7 +38098,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1301" t="n">
         <v>3761</v>
@@ -38127,7 +38127,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H1302" t="n">
         <v>18383</v>
@@ -38272,7 +38272,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1307" t="n">
         <v>33977</v>
@@ -38330,7 +38330,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1309" t="n">
         <v>8950</v>
@@ -38562,7 +38562,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1317" t="n">
         <v>2395</v>
@@ -38620,7 +38620,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1319" t="n">
         <v>2013</v>
@@ -38649,7 +38649,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1320" t="n">
         <v>19847</v>
@@ -38678,7 +38678,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1321" t="n">
         <v>6721</v>
@@ -38707,7 +38707,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1322" t="n">
         <v>4183885</v>
@@ -38968,7 +38968,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1331" t="n">
         <v>17017</v>
@@ -38997,7 +38997,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1332" t="n">
         <v>17023</v>
@@ -39113,7 +39113,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1336" t="n">
         <v>7875</v>
@@ -39171,7 +39171,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1338" t="n">
         <v>579091</v>
@@ -39200,7 +39200,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1339" t="n">
         <v>13097</v>
@@ -39258,7 +39258,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1341" t="n">
         <v>18512</v>
@@ -39345,7 +39345,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1344" t="n">
         <v>142420</v>
@@ -39374,7 +39374,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1345" t="n">
         <v>32214</v>
@@ -39403,7 +39403,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1346" t="n">
         <v>117615</v>
@@ -39461,7 +39461,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1348" t="n">
         <v>45261</v>
@@ -39490,7 +39490,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1349" t="n">
         <v>53301</v>
@@ -39519,7 +39519,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1350" t="n">
         <v>53244</v>
@@ -39548,7 +39548,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1351" t="n">
         <v>128034</v>
@@ -39751,7 +39751,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1358" t="n">
         <v>28701</v>
@@ -39954,7 +39954,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1365" t="n">
         <v>13059</v>
@@ -40012,7 +40012,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1367" t="n">
         <v>15645</v>
@@ -40041,7 +40041,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1368" t="n">
         <v>36938</v>
@@ -40070,7 +40070,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1369" t="n">
         <v>30397</v>
@@ -40099,7 +40099,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1370" t="n">
         <v>59503</v>
@@ -40128,7 +40128,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1371" t="n">
         <v>7128</v>
@@ -40186,7 +40186,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1373" t="n">
         <v>53763</v>
@@ -40244,7 +40244,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1375" t="n">
         <v>80223</v>
@@ -40360,7 +40360,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1379" t="n">
         <v>35399</v>
@@ -40389,7 +40389,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1380" t="n">
         <v>66631</v>
@@ -40418,7 +40418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1381" t="n">
         <v>36618</v>
@@ -40476,7 +40476,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1383" t="n">
         <v>9917</v>
@@ -40563,7 +40563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1386" t="n">
         <v>14411</v>
@@ -40592,7 +40592,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1387" t="n">
         <v>5736</v>
@@ -40650,7 +40650,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1389" t="n">
         <v>33151</v>
@@ -40708,7 +40708,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1391" t="n">
         <v>172952</v>
@@ -40737,7 +40737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1392" t="n">
         <v>27304</v>
@@ -40766,7 +40766,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1393" t="n">
         <v>10573</v>
@@ -40824,7 +40824,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1395" t="n">
         <v>16020</v>
@@ -40882,7 +40882,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1397" t="n">
         <v>25629</v>
@@ -40911,7 +40911,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1398" t="n">
         <v>21495</v>
@@ -40940,7 +40940,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1399" t="n">
         <v>11491</v>
@@ -40969,7 +40969,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1400" t="n">
         <v>70839</v>
@@ -41027,7 +41027,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1402" t="n">
         <v>25324</v>
@@ -41346,7 +41346,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1413" t="n">
         <v>23278</v>
@@ -41433,7 +41433,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1416" t="n">
         <v>86929</v>
@@ -41578,7 +41578,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1421" t="n">
         <v>84292</v>
@@ -41636,7 +41636,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1423" t="n">
         <v>17733</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1430" t="n">
         <v>17929</v>
@@ -42100,7 +42100,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1439" t="n">
         <v>30849</v>
@@ -42245,7 +42245,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1444" t="n">
         <v>16400</v>
@@ -42448,7 +42448,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1451" t="n">
         <v>10674</v>
@@ -42593,7 +42593,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1456" t="n">
         <v>14950</v>
@@ -42651,7 +42651,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1458" t="n">
         <v>53885</v>
@@ -42680,7 +42680,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1459" t="n">
         <v>43894</v>
@@ -42825,7 +42825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1464" t="n">
         <v>6023</v>
@@ -42854,7 +42854,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1465" t="n">
         <v>13746</v>
@@ -42941,7 +42941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1468" t="n">
         <v>17342</v>
@@ -43318,7 +43318,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1481" t="n">
         <v>4088</v>
@@ -43434,7 +43434,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1485" t="n">
         <v>18559</v>
@@ -43463,7 +43463,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1486" t="n">
         <v>5313</v>
@@ -43695,7 +43695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1494" t="n">
         <v>10058</v>
@@ -43724,7 +43724,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1495" t="n">
         <v>6566</v>
@@ -43898,7 +43898,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1501" t="n">
         <v>24701</v>
@@ -43927,7 +43927,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1502" t="n">
         <v>13712</v>
@@ -43985,7 +43985,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1504" t="n">
         <v>17967</v>
@@ -44014,7 +44014,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1505" t="n">
         <v>12753</v>
@@ -44043,7 +44043,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1506" t="n">
         <v>4017</v>
@@ -44304,7 +44304,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1515" t="n">
         <v>32760</v>
@@ -44420,7 +44420,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1519" t="n">
         <v>13224</v>
@@ -44449,7 +44449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1520" t="n">
         <v>15389</v>
@@ -44536,7 +44536,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1523" t="n">
         <v>23568</v>
@@ -44652,7 +44652,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1527" t="n">
         <v>12057</v>
@@ -44681,7 +44681,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1528" t="n">
         <v>10102</v>
@@ -44710,7 +44710,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1529" t="n">
         <v>11999</v>
@@ -44768,7 +44768,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H1531" t="n">
         <v>23916</v>
@@ -44797,7 +44797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1532" t="n">
         <v>53597</v>
@@ -44826,7 +44826,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1533" t="n">
         <v>35027</v>
@@ -44913,7 +44913,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H1536" t="n">
         <v>27398</v>
@@ -45087,7 +45087,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1542" t="n">
         <v>10776</v>
@@ -45290,7 +45290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1549" t="n">
         <v>17670</v>
@@ -45348,7 +45348,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1551" t="n">
         <v>6270</v>
@@ -45551,7 +45551,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1558" t="n">
         <v>9714</v>
@@ -45580,7 +45580,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1559" t="n">
         <v>9223</v>
@@ -45667,7 +45667,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1562" t="n">
         <v>3769</v>
@@ -45870,7 +45870,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1569" t="n">
         <v>59041</v>
@@ -45928,7 +45928,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1571" t="n">
         <v>19659</v>
@@ -45986,7 +45986,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1573" t="n">
         <v>6033</v>
@@ -46102,7 +46102,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1577" t="n">
         <v>16481</v>
@@ -46131,7 +46131,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1578" t="n">
         <v>16827</v>
@@ -46247,7 +46247,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1582" t="n">
         <v>12336</v>
@@ -46537,7 +46537,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1592" t="n">
         <v>40020</v>
@@ -46566,7 +46566,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1593" t="n">
         <v>20842</v>
@@ -47175,7 +47175,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1614" t="n">
         <v>15568</v>
@@ -47262,7 +47262,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1617" t="n">
         <v>1706</v>
@@ -47320,7 +47320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1619" t="n">
         <v>97926</v>
@@ -47349,7 +47349,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1620" t="n">
         <v>14080</v>
@@ -47378,7 +47378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1621" t="n">
         <v>19839</v>
@@ -47436,7 +47436,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1623" t="n">
         <v>16886</v>
@@ -47552,7 +47552,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605560302734</v>
+        <v>4.99605512619019</v>
       </c>
       <c r="H1627" t="n">
         <v>60722</v>
@@ -47581,7 +47581,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1628" t="n">
         <v>24838</v>
@@ -47610,7 +47610,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1629" t="n">
         <v>21313</v>
@@ -47639,7 +47639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1630" t="n">
         <v>23268</v>
@@ -47668,7 +47668,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1631" t="n">
         <v>2356</v>
@@ -47697,7 +47697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1632" t="n">
         <v>26681</v>
@@ -47755,7 +47755,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1634" t="n">
         <v>18116</v>
@@ -47842,7 +47842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1637" t="n">
         <v>9629</v>
@@ -47900,7 +47900,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1639" t="n">
         <v>10513</v>
@@ -47929,7 +47929,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1640" t="n">
         <v>5633</v>
@@ -47987,7 +47987,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H1642" t="n">
         <v>29183</v>
@@ -58894,9 +58894,38 @@
         <v>5.40000009536743</v>
       </c>
       <c r="H2018" t="n">
-        <v>23235</v>
+        <v>25610</v>
       </c>
       <c r="I2018" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2019" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2019" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="D2019" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="E2019" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G2019" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="H2019" t="n">
+        <v>6067</v>
+      </c>
+      <c r="I2019" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835180282593</v>
+        <v>3.50835204124451</v>
       </c>
       <c r="H5" t="n">
         <v>168607</v>
@@ -572,7 +572,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290790557861</v>
+        <v>3.59290766716003</v>
       </c>
       <c r="H7" t="n">
         <v>115707</v>
@@ -630,7 +630,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555654525757</v>
+        <v>3.54555630683899</v>
       </c>
       <c r="H9" t="n">
         <v>18987</v>
@@ -717,7 +717,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694516181946</v>
+        <v>3.47694540023804</v>
       </c>
       <c r="H12" t="n">
         <v>25574</v>
@@ -775,7 +775,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018074989319</v>
+        <v>3.47018098831177</v>
       </c>
       <c r="H14" t="n">
         <v>14046</v>
@@ -804,7 +804,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887778282166</v>
+        <v>3.47887802124023</v>
       </c>
       <c r="H15" t="n">
         <v>25673</v>
@@ -833,7 +833,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786876678467</v>
+        <v>3.50786852836609</v>
       </c>
       <c r="H16" t="n">
         <v>17829</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887778282166</v>
+        <v>3.47887802124023</v>
       </c>
       <c r="H20" t="n">
         <v>24337</v>
@@ -1007,7 +1007,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786876678467</v>
+        <v>3.50786852836609</v>
       </c>
       <c r="H22" t="n">
         <v>15060</v>
@@ -1065,7 +1065,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710956573486</v>
+        <v>3.58710980415344</v>
       </c>
       <c r="H24" t="n">
         <v>31246</v>
@@ -1297,7 +1297,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299355506897</v>
+        <v>3.53299379348755</v>
       </c>
       <c r="H32" t="n">
         <v>12155</v>
@@ -1326,7 +1326,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5368595123291</v>
+        <v>3.53685927391052</v>
       </c>
       <c r="H33" t="n">
         <v>2992</v>
@@ -1384,7 +1384,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185570716858</v>
+        <v>3.65185546875</v>
       </c>
       <c r="H35" t="n">
         <v>9616</v>
@@ -1500,7 +1500,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H39" t="n">
         <v>33223</v>
@@ -1558,7 +1558,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464335441589</v>
+        <v>3.84464311599731</v>
       </c>
       <c r="H41" t="n">
         <v>67310</v>
@@ -1674,7 +1674,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869839668274</v>
+        <v>3.82869815826416</v>
       </c>
       <c r="H45" t="n">
         <v>15050</v>
@@ -1761,7 +1761,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243504524231</v>
+        <v>3.92243480682373</v>
       </c>
       <c r="H48" t="n">
         <v>7064</v>
@@ -1848,7 +1848,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H51" t="n">
         <v>10244</v>
@@ -2138,7 +2138,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863766670227</v>
+        <v>3.75863742828369</v>
       </c>
       <c r="H61" t="n">
         <v>18963</v>
@@ -2167,7 +2167,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H62" t="n">
         <v>25241</v>
@@ -2254,7 +2254,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H65" t="n">
         <v>14098</v>
@@ -2283,7 +2283,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364123344421</v>
+        <v>3.64364147186279</v>
       </c>
       <c r="H66" t="n">
         <v>24444</v>
@@ -2312,7 +2312,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H67" t="n">
         <v>14328</v>
@@ -2457,7 +2457,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422057151794</v>
+        <v>3.91422080993652</v>
       </c>
       <c r="H72" t="n">
         <v>37886</v>
@@ -2544,7 +2544,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H75" t="n">
         <v>61176</v>
@@ -2573,7 +2573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H76" t="n">
         <v>4871</v>
@@ -2631,7 +2631,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615343093872</v>
+        <v>3.91615319252014</v>
       </c>
       <c r="H78" t="n">
         <v>28408</v>
@@ -2660,7 +2660,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331546783447</v>
+        <v>3.98331522941589</v>
       </c>
       <c r="H79" t="n">
         <v>15491</v>
@@ -2689,7 +2689,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H80" t="n">
         <v>8568</v>
@@ -2718,7 +2718,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.9528751373291</v>
+        <v>3.95287489891052</v>
       </c>
       <c r="H81" t="n">
         <v>11304</v>
@@ -2747,7 +2747,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354773521423</v>
+        <v>3.93354797363281</v>
       </c>
       <c r="H82" t="n">
         <v>1333</v>
@@ -2805,7 +2805,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445355415344</v>
+        <v>3.86445379257202</v>
       </c>
       <c r="H84" t="n">
         <v>14743</v>
@@ -2892,7 +2892,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H87" t="n">
         <v>16436</v>
@@ -2921,7 +2921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H88" t="n">
         <v>70067</v>
@@ -2950,7 +2950,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H89" t="n">
         <v>20248</v>
@@ -2979,7 +2979,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H90" t="n">
         <v>9804</v>
@@ -3008,7 +3008,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H91" t="n">
         <v>8029</v>
@@ -3124,7 +3124,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H95" t="n">
         <v>6789</v>
@@ -3153,7 +3153,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H96" t="n">
         <v>16453</v>
@@ -3182,7 +3182,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H97" t="n">
         <v>13893</v>
@@ -3211,7 +3211,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H98" t="n">
         <v>34445</v>
@@ -3269,7 +3269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H100" t="n">
         <v>5569</v>
@@ -3327,7 +3327,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H102" t="n">
         <v>17175</v>
@@ -3385,7 +3385,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H104" t="n">
         <v>4792</v>
@@ -3443,7 +3443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H106" t="n">
         <v>12618</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H107" t="n">
         <v>7801</v>
@@ -3530,7 +3530,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H109" t="n">
         <v>27377</v>
@@ -3559,7 +3559,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H110" t="n">
         <v>9652</v>
@@ -3588,7 +3588,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H111" t="n">
         <v>22427</v>
@@ -3646,7 +3646,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H113" t="n">
         <v>5635</v>
@@ -3675,7 +3675,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H114" t="n">
         <v>12247</v>
@@ -3704,7 +3704,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H115" t="n">
         <v>46534</v>
@@ -3762,7 +3762,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H117" t="n">
         <v>14370</v>
@@ -3791,7 +3791,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H118" t="n">
         <v>20871</v>
@@ -3849,7 +3849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H120" t="n">
         <v>51861</v>
@@ -3907,7 +3907,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890598297119</v>
+        <v>3.90890622138977</v>
       </c>
       <c r="H122" t="n">
         <v>24632</v>
@@ -3965,7 +3965,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856908798218</v>
+        <v>3.91856932640076</v>
       </c>
       <c r="H124" t="n">
         <v>9251</v>
@@ -4023,7 +4023,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H126" t="n">
         <v>23445</v>
@@ -4052,7 +4052,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H127" t="n">
         <v>13288</v>
@@ -4226,7 +4226,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H133" t="n">
         <v>69275</v>
@@ -4255,7 +4255,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.68664455413818</v>
+        <v>3.6866443157196</v>
       </c>
       <c r="H134" t="n">
         <v>83826</v>
@@ -4284,7 +4284,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H135" t="n">
         <v>38411</v>
@@ -4342,7 +4342,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H137" t="n">
         <v>28361</v>
@@ -4371,7 +4371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H138" t="n">
         <v>16251</v>
@@ -4400,7 +4400,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890598297119</v>
+        <v>3.90890622138977</v>
       </c>
       <c r="H139" t="n">
         <v>24663</v>
@@ -4661,7 +4661,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H148" t="n">
         <v>6408</v>
@@ -4690,7 +4690,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H149" t="n">
         <v>17007</v>
@@ -4748,7 +4748,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H151" t="n">
         <v>51508</v>
@@ -4893,7 +4893,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.04419565200806</v>
+        <v>4.0441951751709</v>
       </c>
       <c r="H156" t="n">
         <v>57059</v>
@@ -4951,7 +4951,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431663513184</v>
+        <v>4.18431711196899</v>
       </c>
       <c r="H158" t="n">
         <v>51199</v>
@@ -5821,7 +5821,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251356124878</v>
+        <v>4.09251308441162</v>
       </c>
       <c r="H188" t="n">
         <v>3584</v>
@@ -5995,7 +5995,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431663513184</v>
+        <v>4.18431711196899</v>
       </c>
       <c r="H194" t="n">
         <v>11423</v>
@@ -6459,7 +6459,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H210" t="n">
         <v>4401</v>
@@ -6546,7 +6546,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H213" t="n">
         <v>14225</v>
@@ -6720,7 +6720,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H219" t="n">
         <v>109205</v>
@@ -6981,7 +6981,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H228" t="n">
         <v>32762</v>
@@ -7358,7 +7358,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501838684082</v>
+        <v>4.59501791000366</v>
       </c>
       <c r="H241" t="n">
         <v>82951</v>
@@ -7416,7 +7416,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H243" t="n">
         <v>10325</v>
@@ -7445,7 +7445,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H244" t="n">
         <v>8300</v>
@@ -7590,7 +7590,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761623382568</v>
+        <v>4.80761575698853</v>
       </c>
       <c r="H249" t="n">
         <v>50047</v>
@@ -7619,7 +7619,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761623382568</v>
+        <v>4.80761575698853</v>
       </c>
       <c r="H250" t="n">
         <v>91315</v>
@@ -7648,7 +7648,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H251" t="n">
         <v>63937</v>
@@ -7677,7 +7677,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929880142212</v>
+        <v>4.75929832458496</v>
       </c>
       <c r="H252" t="n">
         <v>3333</v>
@@ -7793,7 +7793,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H256" t="n">
         <v>24390</v>
@@ -7967,7 +7967,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H262" t="n">
         <v>8895</v>
@@ -8025,7 +8025,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727933883667</v>
+        <v>4.81727981567383</v>
       </c>
       <c r="H264" t="n">
         <v>44506</v>
@@ -8054,7 +8054,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H265" t="n">
         <v>48189</v>
@@ -8083,7 +8083,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H266" t="n">
         <v>41705</v>
@@ -8141,7 +8141,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H268" t="n">
         <v>123324</v>
@@ -8228,7 +8228,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740127563477</v>
+        <v>4.95740079879761</v>
       </c>
       <c r="H271" t="n">
         <v>6925</v>
@@ -8315,7 +8315,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H274" t="n">
         <v>136710</v>
@@ -8344,7 +8344,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H275" t="n">
         <v>260348</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H278" t="n">
         <v>25684</v>
@@ -8547,7 +8547,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H282" t="n">
         <v>57869</v>
@@ -8924,7 +8924,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H295" t="n">
         <v>20573</v>
@@ -9040,7 +9040,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H299" t="n">
         <v>19695</v>
@@ -9243,7 +9243,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H306" t="n">
         <v>19157</v>
@@ -9359,7 +9359,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596162796021</v>
+        <v>5.28596115112305</v>
       </c>
       <c r="H310" t="n">
         <v>19428</v>
@@ -9417,7 +9417,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H312" t="n">
         <v>4283</v>
@@ -9533,7 +9533,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H316" t="n">
         <v>151029</v>
@@ -9620,7 +9620,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H319" t="n">
         <v>12312</v>
@@ -9649,7 +9649,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317630767822</v>
+        <v>5.65317678451538</v>
       </c>
       <c r="H320" t="n">
         <v>162473</v>
@@ -9765,7 +9765,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H324" t="n">
         <v>99309</v>
@@ -9852,7 +9852,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134479522705</v>
+        <v>5.13134527206421</v>
       </c>
       <c r="H327" t="n">
         <v>34058</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H329" t="n">
         <v>26368</v>
@@ -9968,7 +9968,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H331" t="n">
         <v>32218</v>
@@ -9997,7 +9997,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H332" t="n">
         <v>81218</v>
@@ -10026,7 +10026,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H333" t="n">
         <v>14865</v>
@@ -10258,7 +10258,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H341" t="n">
         <v>82529</v>
@@ -10287,7 +10287,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H342" t="n">
         <v>98211</v>
@@ -10461,7 +10461,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.8994197845459</v>
+        <v>4.89942026138306</v>
       </c>
       <c r="H348" t="n">
         <v>32626</v>
@@ -10635,7 +10635,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H354" t="n">
         <v>33125</v>
@@ -10751,7 +10751,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H358" t="n">
         <v>44086</v>
@@ -10867,7 +10867,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H362" t="n">
         <v>11155</v>
@@ -11041,7 +11041,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H368" t="n">
         <v>26463</v>
@@ -11099,7 +11099,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H370" t="n">
         <v>8841</v>
@@ -11186,7 +11186,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263502120972</v>
+        <v>4.23263454437256</v>
       </c>
       <c r="H373" t="n">
         <v>16343</v>
@@ -11302,7 +11302,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489645004272</v>
+        <v>4.45489692687988</v>
       </c>
       <c r="H377" t="n">
         <v>6689</v>
@@ -11418,7 +11418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H381" t="n">
         <v>31236</v>
@@ -11447,7 +11447,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H382" t="n">
         <v>9513</v>
@@ -11505,7 +11505,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H384" t="n">
         <v>12160</v>
@@ -11563,7 +11563,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H386" t="n">
         <v>5668</v>
@@ -11679,7 +11679,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H390" t="n">
         <v>5996</v>
@@ -11737,7 +11737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H392" t="n">
         <v>19706</v>
@@ -11795,7 +11795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H394" t="n">
         <v>18905</v>
@@ -12027,7 +12027,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H402" t="n">
         <v>20308</v>
@@ -12288,7 +12288,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H411" t="n">
         <v>7185</v>
@@ -12317,7 +12317,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H412" t="n">
         <v>7082</v>
@@ -12375,7 +12375,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H414" t="n">
         <v>49474</v>
@@ -12520,7 +12520,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H419" t="n">
         <v>7439</v>
@@ -12549,7 +12549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H420" t="n">
         <v>15236</v>
@@ -12607,7 +12607,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H422" t="n">
         <v>10351</v>
@@ -12636,7 +12636,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H423" t="n">
         <v>17376</v>
@@ -12810,7 +12810,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H429" t="n">
         <v>7532</v>
@@ -12868,7 +12868,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H431" t="n">
         <v>2225</v>
@@ -12984,7 +12984,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H435" t="n">
         <v>6281</v>
@@ -13013,7 +13013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H436" t="n">
         <v>7095</v>
@@ -13332,7 +13332,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H447" t="n">
         <v>1474</v>
@@ -13361,7 +13361,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422409057617</v>
+        <v>4.47422361373901</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H452" t="n">
         <v>5271</v>
@@ -13564,7 +13564,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H455" t="n">
         <v>7161</v>
@@ -13622,7 +13622,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H457" t="n">
         <v>13780</v>
@@ -13825,7 +13825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H464" t="n">
         <v>16567</v>
@@ -13883,7 +13883,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H466" t="n">
         <v>4338</v>
@@ -13912,7 +13912,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H467" t="n">
         <v>6710</v>
@@ -14028,7 +14028,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H471" t="n">
         <v>8536</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H487" t="n">
         <v>22603</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H491" t="n">
         <v>18592</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H493" t="n">
         <v>6171</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H494" t="n">
         <v>7707</v>
@@ -14927,7 +14927,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H502" t="n">
         <v>22877</v>
@@ -15130,7 +15130,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H509" t="n">
         <v>4568</v>
@@ -15304,7 +15304,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H515" t="n">
         <v>32842</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H517" t="n">
         <v>11854</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H518" t="n">
         <v>8330</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H522" t="n">
         <v>3006</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H524" t="n">
         <v>29907</v>
@@ -15623,7 +15623,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H526" t="n">
         <v>1616</v>
@@ -15855,7 +15855,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H534" t="n">
         <v>33564</v>
@@ -15884,7 +15884,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H535" t="n">
         <v>17947</v>
@@ -16116,7 +16116,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H543" t="n">
         <v>7536</v>
@@ -16145,7 +16145,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H544" t="n">
         <v>20916</v>
@@ -16203,7 +16203,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H546" t="n">
         <v>18431</v>
@@ -16232,7 +16232,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H547" t="n">
         <v>18024</v>
@@ -16261,7 +16261,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H548" t="n">
         <v>5276</v>
@@ -16290,7 +16290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H549" t="n">
         <v>11659</v>
@@ -16319,7 +16319,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H550" t="n">
         <v>9307</v>
@@ -16464,7 +16464,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H555" t="n">
         <v>211195</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H558" t="n">
         <v>68260</v>
@@ -16725,7 +16725,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H564" t="n">
         <v>44216</v>
@@ -16928,7 +16928,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H571" t="n">
         <v>137820</v>
@@ -16957,7 +16957,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H572" t="n">
         <v>46726</v>
@@ -17102,7 +17102,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H577" t="n">
         <v>232133</v>
@@ -17218,7 +17218,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H581" t="n">
         <v>183006</v>
@@ -17276,7 +17276,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H583" t="n">
         <v>110634</v>
@@ -17334,7 +17334,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H585" t="n">
         <v>83401</v>
@@ -17450,7 +17450,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H589" t="n">
         <v>48955</v>
@@ -17479,7 +17479,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H590" t="n">
         <v>54246</v>
@@ -17595,7 +17595,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H594" t="n">
         <v>141610</v>
@@ -17798,7 +17798,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H601" t="n">
         <v>21002</v>
@@ -17885,7 +17885,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H604" t="n">
         <v>23320</v>
@@ -17972,7 +17972,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H607" t="n">
         <v>46484</v>
@@ -18320,7 +18320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H619" t="n">
         <v>4323</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H623" t="n">
         <v>16947</v>
@@ -18465,7 +18465,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H624" t="n">
         <v>5894</v>
@@ -18523,7 +18523,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H626" t="n">
         <v>25679</v>
@@ -18639,7 +18639,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H630" t="n">
         <v>33871</v>
@@ -18697,7 +18697,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H632" t="n">
         <v>24188</v>
@@ -18784,7 +18784,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H635" t="n">
         <v>57265</v>
@@ -19074,7 +19074,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H645" t="n">
         <v>121832</v>
@@ -19103,7 +19103,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H646" t="n">
         <v>46978</v>
@@ -19480,7 +19480,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H659" t="n">
         <v>58410</v>
@@ -19509,7 +19509,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H660" t="n">
         <v>94430</v>
@@ -19538,7 +19538,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H661" t="n">
         <v>16435</v>
@@ -19625,7 +19625,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H664" t="n">
         <v>36840</v>
@@ -19770,7 +19770,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H669" t="n">
         <v>26798</v>
@@ -20002,7 +20002,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H677" t="n">
         <v>3700</v>
@@ -20031,7 +20031,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H678" t="n">
         <v>31808</v>
@@ -20060,7 +20060,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H679" t="n">
         <v>28368</v>
@@ -20118,7 +20118,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H681" t="n">
         <v>19635</v>
@@ -20321,7 +20321,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H688" t="n">
         <v>116323</v>
@@ -20350,7 +20350,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H689" t="n">
         <v>33063</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H690" t="n">
         <v>12669</v>
@@ -20582,7 +20582,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H697" t="n">
         <v>29126</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H698" t="n">
         <v>31677</v>
@@ -20669,7 +20669,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H700" t="n">
         <v>1753</v>
@@ -20698,7 +20698,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H701" t="n">
         <v>9847</v>
@@ -20727,7 +20727,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H702" t="n">
         <v>15481</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H703" t="n">
         <v>4841</v>
@@ -20785,7 +20785,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H704" t="n">
         <v>20397</v>
@@ -20814,7 +20814,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H705" t="n">
         <v>22265</v>
@@ -20872,7 +20872,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H707" t="n">
         <v>56099</v>
@@ -20901,7 +20901,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H708" t="n">
         <v>72110</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H710" t="n">
         <v>41126</v>
@@ -20988,7 +20988,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H711" t="n">
         <v>41372</v>
@@ -21075,7 +21075,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H714" t="n">
         <v>27761</v>
@@ -21249,7 +21249,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H720" t="n">
         <v>30084</v>
@@ -21365,7 +21365,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H724" t="n">
         <v>22097</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H725" t="n">
         <v>21424</v>
@@ -21481,7 +21481,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H728" t="n">
         <v>28785</v>
@@ -21539,7 +21539,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H730" t="n">
         <v>63831</v>
@@ -21568,7 +21568,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H731" t="n">
         <v>14790</v>
@@ -21626,7 +21626,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H733" t="n">
         <v>54638</v>
@@ -21655,7 +21655,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H734" t="n">
         <v>25806</v>
@@ -21771,7 +21771,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H738" t="n">
         <v>9042</v>
@@ -21858,7 +21858,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H741" t="n">
         <v>25001</v>
@@ -21945,7 +21945,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H744" t="n">
         <v>36541</v>
@@ -22119,7 +22119,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H750" t="n">
         <v>24595</v>
@@ -22148,7 +22148,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H751" t="n">
         <v>7605</v>
@@ -22177,7 +22177,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H752" t="n">
         <v>31505</v>
@@ -22235,7 +22235,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H754" t="n">
         <v>15983</v>
@@ -22293,7 +22293,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H756" t="n">
         <v>24115</v>
@@ -22322,7 +22322,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H757" t="n">
         <v>23156</v>
@@ -22351,7 +22351,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H758" t="n">
         <v>22826</v>
@@ -22380,7 +22380,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H759" t="n">
         <v>27789</v>
@@ -22554,7 +22554,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947570800781</v>
+        <v>5.75947618484497</v>
       </c>
       <c r="H765" t="n">
         <v>90704</v>
@@ -22641,7 +22641,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H768" t="n">
         <v>25948</v>
@@ -22699,7 +22699,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082185745239</v>
+        <v>5.72082138061523</v>
       </c>
       <c r="H770" t="n">
         <v>21002</v>
@@ -22728,7 +22728,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745719909668</v>
+        <v>5.81745672225952</v>
       </c>
       <c r="H771" t="n">
         <v>45095</v>
@@ -22757,7 +22757,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745719909668</v>
+        <v>5.81745672225952</v>
       </c>
       <c r="H772" t="n">
         <v>32302</v>
@@ -22786,7 +22786,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H773" t="n">
         <v>48385</v>
@@ -22873,7 +22873,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H776" t="n">
         <v>33170</v>
@@ -22902,7 +22902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H777" t="n">
         <v>140269</v>
@@ -22931,7 +22931,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H778" t="n">
         <v>51904</v>
@@ -22989,7 +22989,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H780" t="n">
         <v>26033</v>
@@ -23018,7 +23018,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H781" t="n">
         <v>69932</v>
@@ -23134,7 +23134,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H785" t="n">
         <v>21254</v>
@@ -23424,7 +23424,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H795" t="n">
         <v>129207</v>
@@ -23453,7 +23453,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H796" t="n">
         <v>74996</v>
@@ -23656,7 +23656,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H803" t="n">
         <v>95136</v>
@@ -23830,7 +23830,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H809" t="n">
         <v>42616</v>
@@ -23975,7 +23975,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H814" t="n">
         <v>147606</v>
@@ -24004,7 +24004,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H815" t="n">
         <v>20160</v>
@@ -24062,7 +24062,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H817" t="n">
         <v>48978</v>
@@ -24091,7 +24091,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H818" t="n">
         <v>17601</v>
@@ -24178,7 +24178,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H821" t="n">
         <v>17172</v>
@@ -24207,7 +24207,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H822" t="n">
         <v>21711</v>
@@ -24236,7 +24236,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H823" t="n">
         <v>13038</v>
@@ -24381,7 +24381,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H828" t="n">
         <v>13399</v>
@@ -24700,7 +24700,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H839" t="n">
         <v>10091</v>
@@ -24729,7 +24729,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H840" t="n">
         <v>20843</v>
@@ -24990,7 +24990,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725185394287</v>
+        <v>4.38725137710571</v>
       </c>
       <c r="H849" t="n">
         <v>88040</v>
@@ -25048,7 +25048,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H851" t="n">
         <v>61678</v>
@@ -25077,7 +25077,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H852" t="n">
         <v>25922</v>
@@ -25222,7 +25222,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H857" t="n">
         <v>26131</v>
@@ -25309,7 +25309,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H860" t="n">
         <v>25865</v>
@@ -25483,7 +25483,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H866" t="n">
         <v>10855</v>
@@ -25541,7 +25541,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H868" t="n">
         <v>4022</v>
@@ -25570,7 +25570,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.6240086555481</v>
+        <v>4.62400817871094</v>
       </c>
       <c r="H869" t="n">
         <v>9713</v>
@@ -25628,7 +25628,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602716445923</v>
+        <v>4.56602764129639</v>
       </c>
       <c r="H871" t="n">
         <v>3876</v>
@@ -25802,7 +25802,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602716445923</v>
+        <v>4.56602764129639</v>
       </c>
       <c r="H877" t="n">
         <v>1609</v>
@@ -26179,7 +26179,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H890" t="n">
         <v>21852</v>
@@ -26208,7 +26208,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309242248535</v>
+        <v>4.36309289932251</v>
       </c>
       <c r="H891" t="n">
         <v>19273</v>
@@ -26237,7 +26237,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H892" t="n">
         <v>9208</v>
@@ -26295,7 +26295,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H894" t="n">
         <v>13445</v>
@@ -26324,7 +26324,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645708084106</v>
+        <v>4.26645755767822</v>
       </c>
       <c r="H895" t="n">
         <v>43685</v>
@@ -26440,7 +26440,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H899" t="n">
         <v>27960</v>
@@ -26498,7 +26498,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095245361328</v>
+        <v>4.28095197677612</v>
       </c>
       <c r="H901" t="n">
         <v>33825</v>
@@ -26672,7 +26672,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.04419565200806</v>
+        <v>4.0441951751709</v>
       </c>
       <c r="H907" t="n">
         <v>15181</v>
@@ -26730,7 +26730,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621416091919</v>
+        <v>3.98621439933777</v>
       </c>
       <c r="H909" t="n">
         <v>14992</v>
@@ -26904,7 +26904,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H915" t="n">
         <v>53863</v>
@@ -27049,7 +27049,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H920" t="n">
         <v>5004</v>
@@ -27078,7 +27078,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H921" t="n">
         <v>4290</v>
@@ -27136,7 +27136,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991499900818</v>
+        <v>3.87991523742676</v>
       </c>
       <c r="H923" t="n">
         <v>8482</v>
@@ -27165,7 +27165,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453207015991</v>
+        <v>4.03453254699707</v>
       </c>
       <c r="H924" t="n">
         <v>16764</v>
@@ -27513,7 +27513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H936" t="n">
         <v>1516</v>
@@ -27629,7 +27629,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352233886719</v>
+        <v>4.06352281570435</v>
       </c>
       <c r="H940" t="n">
         <v>4899</v>
@@ -27658,7 +27658,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.8557562828064</v>
+        <v>3.85575652122498</v>
       </c>
       <c r="H941" t="n">
         <v>56027</v>
@@ -27716,7 +27716,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H943" t="n">
         <v>7945</v>
@@ -27861,7 +27861,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H948" t="n">
         <v>9054</v>
@@ -27890,7 +27890,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H949" t="n">
         <v>974</v>
@@ -28006,7 +28006,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H953" t="n">
         <v>15215</v>
@@ -28122,7 +28122,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193398475647</v>
+        <v>3.82193374633789</v>
       </c>
       <c r="H957" t="n">
         <v>1040</v>
@@ -28151,7 +28151,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327965736389</v>
+        <v>3.78327989578247</v>
       </c>
       <c r="H958" t="n">
         <v>5878</v>
@@ -28296,7 +28296,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327965736389</v>
+        <v>3.78327989578247</v>
       </c>
       <c r="H963" t="n">
         <v>1069</v>
@@ -28325,7 +28325,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H964" t="n">
         <v>4985</v>
@@ -28354,7 +28354,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H965" t="n">
         <v>1586</v>
@@ -28412,7 +28412,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H967" t="n">
         <v>22825</v>
@@ -28499,7 +28499,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945759773254</v>
+        <v>3.74945735931396</v>
       </c>
       <c r="H970" t="n">
         <v>1519</v>
@@ -28615,7 +28615,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H974" t="n">
         <v>61487</v>
@@ -28702,7 +28702,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.8557562828064</v>
+        <v>3.85575652122498</v>
       </c>
       <c r="H977" t="n">
         <v>13657</v>
@@ -28731,7 +28731,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H978" t="n">
         <v>26282</v>
@@ -28818,7 +28818,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H981" t="n">
         <v>4451</v>
@@ -28876,7 +28876,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H983" t="n">
         <v>36877</v>
@@ -28905,7 +28905,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H984" t="n">
         <v>1838</v>
@@ -28963,7 +28963,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H986" t="n">
         <v>12068</v>
@@ -28992,7 +28992,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H987" t="n">
         <v>26097</v>
@@ -29021,7 +29021,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945759773254</v>
+        <v>3.74945735931396</v>
       </c>
       <c r="H988" t="n">
         <v>6234</v>
@@ -29224,7 +29224,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H995" t="n">
         <v>11228</v>
@@ -29253,7 +29253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H996" t="n">
         <v>4330</v>
@@ -29282,7 +29282,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H997" t="n">
         <v>8092</v>
@@ -29398,7 +29398,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.96688747406006</v>
+        <v>3.9668869972229</v>
       </c>
       <c r="H1001" t="n">
         <v>517</v>
@@ -29514,7 +29514,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856908798218</v>
+        <v>3.91856932640076</v>
       </c>
       <c r="H1005" t="n">
         <v>15349</v>
@@ -29804,7 +29804,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1015" t="n">
         <v>20471</v>
@@ -29891,7 +29891,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1018" t="n">
         <v>24364</v>
@@ -29920,7 +29920,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1019" t="n">
         <v>19551</v>
@@ -30007,7 +30007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1022" t="n">
         <v>3870</v>
@@ -30616,7 +30616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1043" t="n">
         <v>7439</v>
@@ -30703,7 +30703,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1046" t="n">
         <v>15720</v>
@@ -30732,7 +30732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1047" t="n">
         <v>13320</v>
@@ -30790,7 +30790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1049" t="n">
         <v>1434</v>
@@ -30848,7 +30848,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820470809937</v>
+        <v>3.49820494651794</v>
       </c>
       <c r="H1051" t="n">
         <v>22296</v>
@@ -30906,7 +30906,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1053" t="n">
         <v>16504</v>
@@ -30935,7 +30935,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1054" t="n">
         <v>12412</v>
@@ -30993,7 +30993,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1056" t="n">
         <v>12576</v>
@@ -31051,7 +31051,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.7301299571991</v>
+        <v>3.73013019561768</v>
       </c>
       <c r="H1058" t="n">
         <v>9513</v>
@@ -31225,7 +31225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1064" t="n">
         <v>11552</v>
@@ -31254,7 +31254,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563482284546</v>
+        <v>3.71563506126404</v>
       </c>
       <c r="H1065" t="n">
         <v>34413</v>
@@ -31283,7 +31283,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135464668274</v>
+        <v>3.55135440826416</v>
       </c>
       <c r="H1066" t="n">
         <v>64042</v>
@@ -31341,7 +31341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1068" t="n">
         <v>24424</v>
@@ -31399,7 +31399,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1070" t="n">
         <v>18126</v>
@@ -31457,7 +31457,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.5368595123291</v>
+        <v>3.53685927391052</v>
       </c>
       <c r="H1072" t="n">
         <v>26947</v>
@@ -31515,7 +31515,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1074" t="n">
         <v>76053</v>
@@ -31689,7 +31689,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1080" t="n">
         <v>11888</v>
@@ -31718,7 +31718,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.59967231750488</v>
+        <v>3.5996720790863</v>
       </c>
       <c r="H1081" t="n">
         <v>87040</v>
@@ -31776,7 +31776,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1083" t="n">
         <v>27634</v>
@@ -31805,7 +31805,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135464668274</v>
+        <v>3.55135440826416</v>
       </c>
       <c r="H1084" t="n">
         <v>183394</v>
@@ -31863,7 +31863,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1086" t="n">
         <v>39968</v>
@@ -31892,7 +31892,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1087" t="n">
         <v>19044</v>
@@ -31950,7 +31950,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.59967231750488</v>
+        <v>3.5996720790863</v>
       </c>
       <c r="H1089" t="n">
         <v>21496</v>
@@ -32037,7 +32037,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1092" t="n">
         <v>4199</v>
@@ -32095,7 +32095,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1094" t="n">
         <v>2930</v>
@@ -32124,7 +32124,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1095" t="n">
         <v>17824</v>
@@ -32414,7 +32414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1105" t="n">
         <v>8012</v>
@@ -32501,7 +32501,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1108" t="n">
         <v>20364</v>
@@ -32617,7 +32617,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1112" t="n">
         <v>8014</v>
@@ -32646,7 +32646,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214894294739</v>
+        <v>3.67214870452881</v>
       </c>
       <c r="H1113" t="n">
         <v>5992</v>
@@ -32791,7 +32791,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1118" t="n">
         <v>7468</v>
@@ -32878,7 +32878,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1121" t="n">
         <v>7108</v>
@@ -32907,7 +32907,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383127212524</v>
+        <v>3.62383103370667</v>
       </c>
       <c r="H1122" t="n">
         <v>3566</v>
@@ -32965,7 +32965,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1124" t="n">
         <v>6159</v>
@@ -32994,7 +32994,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1125" t="n">
         <v>36559</v>
@@ -33023,7 +33023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1126" t="n">
         <v>5854</v>
@@ -33081,7 +33081,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1128" t="n">
         <v>85216</v>
@@ -33110,7 +33110,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56584978103638</v>
+        <v>3.56585001945496</v>
       </c>
       <c r="H1129" t="n">
         <v>44308</v>
@@ -33168,7 +33168,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484052658081</v>
+        <v>3.59484076499939</v>
       </c>
       <c r="H1131" t="n">
         <v>2341</v>
@@ -33197,7 +33197,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.5755136013031</v>
+        <v>3.57551336288452</v>
       </c>
       <c r="H1132" t="n">
         <v>13385</v>
@@ -33371,7 +33371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.6914758682251</v>
+        <v>3.69147610664368</v>
       </c>
       <c r="H1138" t="n">
         <v>23416</v>
@@ -33516,7 +33516,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642911911011</v>
+        <v>3.83642935752869</v>
       </c>
       <c r="H1143" t="n">
         <v>14293</v>
@@ -33574,7 +33574,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1145" t="n">
         <v>44949</v>
@@ -33719,7 +33719,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171878814697</v>
+        <v>3.97171926498413</v>
       </c>
       <c r="H1150" t="n">
         <v>7061</v>
@@ -33748,7 +33748,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H1151" t="n">
         <v>5770</v>
@@ -33777,7 +33777,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1152" t="n">
         <v>12871</v>
@@ -33806,7 +33806,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1153" t="n">
         <v>21159</v>
@@ -33835,7 +33835,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1154" t="n">
         <v>63339</v>
@@ -33864,7 +33864,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1155" t="n">
         <v>13966</v>
@@ -34125,7 +34125,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1164" t="n">
         <v>8374</v>
@@ -34154,7 +34154,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1165" t="n">
         <v>8257</v>
@@ -34241,7 +34241,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1168" t="n">
         <v>51543</v>
@@ -34299,7 +34299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1170" t="n">
         <v>8138</v>
@@ -34415,7 +34415,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1174" t="n">
         <v>18764</v>
@@ -34589,7 +34589,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508392333984</v>
+        <v>3.87508368492126</v>
       </c>
       <c r="H1180" t="n">
         <v>22131</v>
@@ -34705,7 +34705,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407395362854</v>
+        <v>3.90407419204712</v>
       </c>
       <c r="H1184" t="n">
         <v>1634</v>
@@ -34734,7 +34734,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1185" t="n">
         <v>1460</v>
@@ -34792,7 +34792,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1187" t="n">
         <v>21143</v>
@@ -34821,7 +34821,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1188" t="n">
         <v>8937</v>
@@ -34850,7 +34850,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1189" t="n">
         <v>9771</v>
@@ -34908,7 +34908,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1191" t="n">
         <v>3139</v>
@@ -34966,7 +34966,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1193" t="n">
         <v>23650</v>
@@ -34995,7 +34995,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1194" t="n">
         <v>30769</v>
@@ -35024,7 +35024,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373801231384</v>
+        <v>3.91373777389526</v>
       </c>
       <c r="H1195" t="n">
         <v>53170</v>
@@ -35053,7 +35053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1196" t="n">
         <v>8141</v>
@@ -35082,7 +35082,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306469917297</v>
+        <v>3.93306493759155</v>
       </c>
       <c r="H1197" t="n">
         <v>18888</v>
@@ -35111,7 +35111,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239210128784</v>
+        <v>3.95239233970642</v>
       </c>
       <c r="H1198" t="n">
         <v>2167</v>
@@ -35140,7 +35140,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1199" t="n">
         <v>21694</v>
@@ -35169,7 +35169,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1200" t="n">
         <v>30561</v>
@@ -35227,7 +35227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205544471741</v>
+        <v>3.96205520629883</v>
       </c>
       <c r="H1202" t="n">
         <v>13802</v>
@@ -35285,7 +35285,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.02003622055054</v>
+        <v>4.0200366973877</v>
       </c>
       <c r="H1204" t="n">
         <v>39802</v>
@@ -35430,7 +35430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.0780177116394</v>
+        <v>4.07801818847656</v>
       </c>
       <c r="H1209" t="n">
         <v>13920</v>
@@ -35952,7 +35952,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037359237671</v>
+        <v>4.01037311553955</v>
       </c>
       <c r="H1227" t="n">
         <v>11126</v>
@@ -36010,7 +36010,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263502120972</v>
+        <v>4.23263454437256</v>
       </c>
       <c r="H1229" t="n">
         <v>30135</v>
@@ -36184,7 +36184,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1235" t="n">
         <v>87770</v>
@@ -36242,7 +36242,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1237" t="n">
         <v>86783</v>
@@ -36271,7 +36271,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095245361328</v>
+        <v>4.28095197677612</v>
       </c>
       <c r="H1238" t="n">
         <v>10697</v>
@@ -36300,7 +36300,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1239" t="n">
         <v>633742</v>
@@ -36387,7 +36387,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1242" t="n">
         <v>33483</v>
@@ -36416,7 +36416,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297096252441</v>
+        <v>4.22297143936157</v>
       </c>
       <c r="H1243" t="n">
         <v>111404</v>
@@ -36474,7 +36474,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1245" t="n">
         <v>71817</v>
@@ -36503,7 +36503,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1246" t="n">
         <v>15207</v>
@@ -36561,7 +36561,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1248" t="n">
         <v>263769</v>
@@ -36648,7 +36648,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220510482788</v>
+        <v>4.53220462799072</v>
       </c>
       <c r="H1251" t="n">
         <v>22609</v>
@@ -36822,7 +36822,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128887176514</v>
+        <v>4.27128934860229</v>
       </c>
       <c r="H1257" t="n">
         <v>38711</v>
@@ -36909,7 +36909,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1260" t="n">
         <v>48866</v>
@@ -36938,7 +36938,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1261" t="n">
         <v>88377</v>
@@ -37054,7 +37054,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1265" t="n">
         <v>106306</v>
@@ -37547,7 +37547,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1282" t="n">
         <v>41916</v>
@@ -37663,7 +37663,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1286" t="n">
         <v>18275</v>
@@ -37692,7 +37692,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1287" t="n">
         <v>38266</v>
@@ -37721,7 +37721,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1288" t="n">
         <v>44950</v>
@@ -37750,7 +37750,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1289" t="n">
         <v>154179</v>
@@ -37808,7 +37808,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1291" t="n">
         <v>48801</v>
@@ -37895,7 +37895,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1294" t="n">
         <v>76505</v>
@@ -38011,7 +38011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1298" t="n">
         <v>108894</v>
@@ -38040,7 +38040,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1299" t="n">
         <v>13424</v>
@@ -38098,7 +38098,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1301" t="n">
         <v>3761</v>
@@ -38127,7 +38127,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725185394287</v>
+        <v>4.38725137710571</v>
       </c>
       <c r="H1302" t="n">
         <v>18383</v>
@@ -38272,7 +38272,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1307" t="n">
         <v>33977</v>
@@ -38330,7 +38330,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1309" t="n">
         <v>8950</v>
@@ -38562,7 +38562,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859704971313</v>
+        <v>4.34859752655029</v>
       </c>
       <c r="H1317" t="n">
         <v>2395</v>
@@ -38620,7 +38620,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162576675415</v>
+        <v>4.26162528991699</v>
       </c>
       <c r="H1319" t="n">
         <v>2013</v>
@@ -38649,7 +38649,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.3196063041687</v>
+        <v>4.31960678100586</v>
       </c>
       <c r="H1320" t="n">
         <v>19847</v>
@@ -38678,7 +38678,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893394470215</v>
+        <v>4.33893346786499</v>
       </c>
       <c r="H1321" t="n">
         <v>6721</v>
@@ -38707,7 +38707,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1322" t="n">
         <v>4183885</v>
@@ -38968,7 +38968,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1331" t="n">
         <v>17017</v>
@@ -38997,7 +38997,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1332" t="n">
         <v>17023</v>
@@ -39113,7 +39113,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1336" t="n">
         <v>7875</v>
@@ -39171,7 +39171,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1338" t="n">
         <v>579091</v>
@@ -39200,7 +39200,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1339" t="n">
         <v>13097</v>
@@ -39258,7 +39258,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1341" t="n">
         <v>18512</v>
@@ -39345,7 +39345,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1344" t="n">
         <v>142420</v>
@@ -39374,7 +39374,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1345" t="n">
         <v>32214</v>
@@ -39403,7 +39403,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1346" t="n">
         <v>117615</v>
@@ -39461,7 +39461,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1348" t="n">
         <v>45261</v>
@@ -39490,7 +39490,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1349" t="n">
         <v>53301</v>
@@ -39519,7 +39519,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1350" t="n">
         <v>53244</v>
@@ -39548,7 +39548,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1351" t="n">
         <v>128034</v>
@@ -39751,7 +39751,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1358" t="n">
         <v>28701</v>
@@ -39954,7 +39954,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1365" t="n">
         <v>13059</v>
@@ -40012,7 +40012,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1367" t="n">
         <v>15645</v>
@@ -40041,7 +40041,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1368" t="n">
         <v>36938</v>
@@ -40070,7 +40070,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1369" t="n">
         <v>30397</v>
@@ -40099,7 +40099,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614862442017</v>
+        <v>4.70614910125732</v>
       </c>
       <c r="H1370" t="n">
         <v>59503</v>
@@ -40128,7 +40128,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581268310547</v>
+        <v>4.71581220626831</v>
       </c>
       <c r="H1371" t="n">
         <v>7128</v>
@@ -40186,7 +40186,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1373" t="n">
         <v>53763</v>
@@ -40244,7 +40244,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1375" t="n">
         <v>80223</v>
@@ -40360,7 +40360,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76413011550903</v>
+        <v>4.76412963867188</v>
       </c>
       <c r="H1379" t="n">
         <v>35399</v>
@@ -40389,7 +40389,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1380" t="n">
         <v>66631</v>
@@ -40418,7 +40418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1381" t="n">
         <v>36618</v>
@@ -40476,7 +40476,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1383" t="n">
         <v>9917</v>
@@ -40563,7 +40563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1386" t="n">
         <v>14411</v>
@@ -40592,7 +40592,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1387" t="n">
         <v>5736</v>
@@ -40650,7 +40650,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.561194896698</v>
+        <v>4.56119537353516</v>
       </c>
       <c r="H1389" t="n">
         <v>33151</v>
@@ -40708,7 +40708,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.6481671333313</v>
+        <v>4.64816761016846</v>
       </c>
       <c r="H1391" t="n">
         <v>172952</v>
@@ -40737,7 +40737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1392" t="n">
         <v>27304</v>
@@ -40766,7 +40766,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1393" t="n">
         <v>10573</v>
@@ -40824,7 +40824,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1395" t="n">
         <v>16020</v>
@@ -40882,7 +40882,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850450515747</v>
+        <v>4.63850402832031</v>
       </c>
       <c r="H1397" t="n">
         <v>25629</v>
@@ -40911,7 +40911,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648504257202</v>
+        <v>4.69648551940918</v>
       </c>
       <c r="H1398" t="n">
         <v>21495</v>
@@ -40940,7 +40940,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749477386475</v>
+        <v>4.66749429702759</v>
       </c>
       <c r="H1399" t="n">
         <v>11491</v>
@@ -40969,7 +40969,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1400" t="n">
         <v>70839</v>
@@ -41027,7 +41027,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1402" t="n">
         <v>25324</v>
@@ -41346,7 +41346,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1413" t="n">
         <v>23278</v>
@@ -41433,7 +41433,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1416" t="n">
         <v>86929</v>
@@ -41578,7 +41578,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1421" t="n">
         <v>84292</v>
@@ -41636,7 +41636,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1423" t="n">
         <v>17733</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1430" t="n">
         <v>17929</v>
@@ -42100,7 +42100,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1439" t="n">
         <v>30849</v>
@@ -42245,7 +42245,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1444" t="n">
         <v>16400</v>
@@ -42448,7 +42448,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1451" t="n">
         <v>10674</v>
@@ -42593,7 +42593,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1456" t="n">
         <v>14950</v>
@@ -42651,7 +42651,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1458" t="n">
         <v>53885</v>
@@ -42680,7 +42680,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1459" t="n">
         <v>43894</v>
@@ -42825,7 +42825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1464" t="n">
         <v>6023</v>
@@ -42854,7 +42854,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1465" t="n">
         <v>13746</v>
@@ -42941,7 +42941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1468" t="n">
         <v>17342</v>
@@ -43318,7 +43318,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1481" t="n">
         <v>4088</v>
@@ -43434,7 +43434,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1485" t="n">
         <v>18559</v>
@@ -43463,7 +43463,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1486" t="n">
         <v>5313</v>
@@ -43695,7 +43695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1494" t="n">
         <v>10058</v>
@@ -43724,7 +43724,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1495" t="n">
         <v>6566</v>
@@ -43898,7 +43898,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1501" t="n">
         <v>24701</v>
@@ -43927,7 +43927,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1502" t="n">
         <v>13712</v>
@@ -43985,7 +43985,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1504" t="n">
         <v>17967</v>
@@ -44014,7 +44014,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1505" t="n">
         <v>12753</v>
@@ -44043,7 +44043,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1506" t="n">
         <v>4017</v>
@@ -44304,7 +44304,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1515" t="n">
         <v>32760</v>
@@ -44420,7 +44420,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1519" t="n">
         <v>13224</v>
@@ -44449,7 +44449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1520" t="n">
         <v>15389</v>
@@ -44536,7 +44536,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H1523" t="n">
         <v>23568</v>
@@ -44652,7 +44652,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1527" t="n">
         <v>12057</v>
@@ -44681,7 +44681,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1528" t="n">
         <v>10102</v>
@@ -44710,7 +44710,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H1529" t="n">
         <v>11999</v>
@@ -44768,7 +44768,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293338775635</v>
+        <v>5.37293386459351</v>
       </c>
       <c r="H1531" t="n">
         <v>23916</v>
@@ -44797,7 +44797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553218841553</v>
+        <v>5.58553171157837</v>
       </c>
       <c r="H1532" t="n">
         <v>53597</v>
@@ -44826,7 +44826,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1533" t="n">
         <v>35027</v>
@@ -44913,7 +44913,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.70149421691895</v>
+        <v>5.7014946937561</v>
       </c>
       <c r="H1536" t="n">
         <v>27398</v>
@@ -45087,7 +45087,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822305679321</v>
+        <v>5.50822353363037</v>
       </c>
       <c r="H1542" t="n">
         <v>10776</v>
@@ -45290,7 +45290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226102828979</v>
+        <v>5.39226055145264</v>
       </c>
       <c r="H1549" t="n">
         <v>17670</v>
@@ -45348,7 +45348,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427953720093</v>
+        <v>5.33427906036377</v>
       </c>
       <c r="H1551" t="n">
         <v>6270</v>
@@ -45551,7 +45551,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.3149528503418</v>
+        <v>5.31495237350464</v>
       </c>
       <c r="H1558" t="n">
         <v>9714</v>
@@ -45580,7 +45580,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1559" t="n">
         <v>9223</v>
@@ -45667,7 +45667,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629804611206</v>
+        <v>5.27629852294922</v>
       </c>
       <c r="H1562" t="n">
         <v>3769</v>
@@ -45870,7 +45870,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446653366089</v>
+        <v>4.75446701049805</v>
       </c>
       <c r="H1569" t="n">
         <v>59041</v>
@@ -45928,7 +45928,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1571" t="n">
         <v>19659</v>
@@ -45986,7 +45986,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1573" t="n">
         <v>6033</v>
@@ -46102,7 +46102,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1577" t="n">
         <v>16481</v>
@@ -46131,7 +46131,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1578" t="n">
         <v>16827</v>
@@ -46247,7 +46247,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1582" t="n">
         <v>12336</v>
@@ -46537,7 +46537,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1592" t="n">
         <v>40020</v>
@@ -46566,7 +46566,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1593" t="n">
         <v>20842</v>
@@ -47175,7 +47175,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1614" t="n">
         <v>15568</v>
@@ -47262,7 +47262,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177471160889</v>
+        <v>4.83177518844604</v>
       </c>
       <c r="H1617" t="n">
         <v>1706</v>
@@ -47320,7 +47320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1619" t="n">
         <v>97926</v>
@@ -47349,7 +47349,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1620" t="n">
         <v>14080</v>
@@ -47378,7 +47378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908336639404</v>
+        <v>4.90908288955688</v>
       </c>
       <c r="H1621" t="n">
         <v>19839</v>
@@ -47436,7 +47436,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1623" t="n">
         <v>16886</v>
@@ -47552,7 +47552,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605512619019</v>
+        <v>4.99605560302734</v>
       </c>
       <c r="H1627" t="n">
         <v>60722</v>
@@ -47581,7 +47581,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1628" t="n">
         <v>24838</v>
@@ -47610,7 +47610,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1629" t="n">
         <v>21313</v>
@@ -47639,7 +47639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1630" t="n">
         <v>23268</v>
@@ -47668,7 +47668,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1631" t="n">
         <v>2356</v>
@@ -47697,7 +47697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773721694946</v>
+        <v>4.94773769378662</v>
       </c>
       <c r="H1632" t="n">
         <v>26681</v>
@@ -47755,7 +47755,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H1634" t="n">
         <v>18116</v>
@@ -47842,7 +47842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504539489746</v>
+        <v>5.02504587173462</v>
       </c>
       <c r="H1637" t="n">
         <v>9629</v>
@@ -47900,7 +47900,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538276672363</v>
+        <v>5.01538228988647</v>
       </c>
       <c r="H1639" t="n">
         <v>10513</v>
@@ -47929,7 +47929,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.14100885391235</v>
+        <v>5.1410083770752</v>
       </c>
       <c r="H1640" t="n">
         <v>5633</v>
@@ -47987,7 +47987,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865345001221</v>
+        <v>5.20865297317505</v>
       </c>
       <c r="H1642" t="n">
         <v>29183</v>
@@ -58923,9 +58923,38 @@
         <v>5.3600001335144</v>
       </c>
       <c r="H2019" t="n">
-        <v>6067</v>
+        <v>7364</v>
       </c>
       <c r="I2019" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2020" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2020" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>5.38000011444092</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G2020" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="H2020" t="n">
+        <v>11185</v>
+      </c>
+      <c r="I2020" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -58958,6 +58958,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2021">
+      <c r="A2021" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2021" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2021" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E2021" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="G2021" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="H2021" t="n">
+        <v>8810</v>
+      </c>
+      <c r="I2021" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.63050007820129</v>
       </c>
       <c r="G5" t="n">
-        <v>3.50835204124451</v>
+        <v>3.50835180282593</v>
       </c>
       <c r="H5" t="n">
         <v>168607</v>
@@ -572,7 +572,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G7" t="n">
-        <v>3.59290766716003</v>
+        <v>3.59290790557861</v>
       </c>
       <c r="H7" t="n">
         <v>115707</v>
@@ -630,7 +630,7 @@
         <v>3.66899991035461</v>
       </c>
       <c r="G9" t="n">
-        <v>3.54555630683899</v>
+        <v>3.54555654525757</v>
       </c>
       <c r="H9" t="n">
         <v>18987</v>
@@ -717,7 +717,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G12" t="n">
-        <v>3.47694540023804</v>
+        <v>3.47694516181946</v>
       </c>
       <c r="H12" t="n">
         <v>25574</v>
@@ -775,7 +775,7 @@
         <v>3.59100008010864</v>
       </c>
       <c r="G14" t="n">
-        <v>3.47018098831177</v>
+        <v>3.47018074989319</v>
       </c>
       <c r="H14" t="n">
         <v>14046</v>
@@ -804,7 +804,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H15" t="n">
         <v>25673</v>
@@ -833,7 +833,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G16" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H16" t="n">
         <v>17829</v>
@@ -949,7 +949,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G20" t="n">
-        <v>3.47887802124023</v>
+        <v>3.47887778282166</v>
       </c>
       <c r="H20" t="n">
         <v>24337</v>
@@ -1007,7 +1007,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G22" t="n">
-        <v>3.50786852836609</v>
+        <v>3.50786876678467</v>
       </c>
       <c r="H22" t="n">
         <v>15060</v>
@@ -1065,7 +1065,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G24" t="n">
-        <v>3.58710980415344</v>
+        <v>3.58710956573486</v>
       </c>
       <c r="H24" t="n">
         <v>31246</v>
@@ -1297,7 +1297,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G32" t="n">
-        <v>3.53299379348755</v>
+        <v>3.53299355506897</v>
       </c>
       <c r="H32" t="n">
         <v>12155</v>
@@ -1326,7 +1326,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H33" t="n">
         <v>2992</v>
@@ -1384,7 +1384,7 @@
         <v>3.77900004386902</v>
       </c>
       <c r="G35" t="n">
-        <v>3.65185546875</v>
+        <v>3.65185570716858</v>
       </c>
       <c r="H35" t="n">
         <v>9616</v>
@@ -1500,7 +1500,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G39" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H39" t="n">
         <v>33223</v>
@@ -1558,7 +1558,7 @@
         <v>3.97849988937378</v>
       </c>
       <c r="G41" t="n">
-        <v>3.84464311599731</v>
+        <v>3.84464335441589</v>
       </c>
       <c r="H41" t="n">
         <v>67310</v>
@@ -1674,7 +1674,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G45" t="n">
-        <v>3.82869815826416</v>
+        <v>3.82869839668274</v>
       </c>
       <c r="H45" t="n">
         <v>15050</v>
@@ -1761,7 +1761,7 @@
         <v>4.05900001525879</v>
       </c>
       <c r="G48" t="n">
-        <v>3.92243480682373</v>
+        <v>3.92243504524231</v>
       </c>
       <c r="H48" t="n">
         <v>7064</v>
@@ -1848,7 +1848,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H51" t="n">
         <v>10244</v>
@@ -2138,7 +2138,7 @@
         <v>3.88949990272522</v>
       </c>
       <c r="G61" t="n">
-        <v>3.75863742828369</v>
+        <v>3.75863766670227</v>
       </c>
       <c r="H61" t="n">
         <v>18963</v>
@@ -2167,7 +2167,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H62" t="n">
         <v>25241</v>
@@ -2254,7 +2254,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H65" t="n">
         <v>14098</v>
@@ -2283,7 +2283,7 @@
         <v>3.77049994468689</v>
       </c>
       <c r="G66" t="n">
-        <v>3.64364147186279</v>
+        <v>3.64364123344421</v>
       </c>
       <c r="H66" t="n">
         <v>24444</v>
@@ -2312,7 +2312,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G67" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H67" t="n">
         <v>14328</v>
@@ -2457,7 +2457,7 @@
         <v>4.05049991607666</v>
       </c>
       <c r="G72" t="n">
-        <v>3.91422080993652</v>
+        <v>3.91422057151794</v>
       </c>
       <c r="H72" t="n">
         <v>37886</v>
@@ -2544,7 +2544,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G75" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H75" t="n">
         <v>61176</v>
@@ -2573,7 +2573,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G76" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H76" t="n">
         <v>4871</v>
@@ -2631,7 +2631,7 @@
         <v>4.05249977111816</v>
       </c>
       <c r="G78" t="n">
-        <v>3.91615319252014</v>
+        <v>3.91615343093872</v>
       </c>
       <c r="H78" t="n">
         <v>28408</v>
@@ -2660,7 +2660,7 @@
         <v>4.12200021743774</v>
       </c>
       <c r="G79" t="n">
-        <v>3.98331522941589</v>
+        <v>3.98331546783447</v>
       </c>
       <c r="H79" t="n">
         <v>15491</v>
@@ -2689,7 +2689,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H80" t="n">
         <v>8568</v>
@@ -2718,7 +2718,7 @@
         <v>4.09049987792969</v>
       </c>
       <c r="G81" t="n">
-        <v>3.95287489891052</v>
+        <v>3.9528751373291</v>
       </c>
       <c r="H81" t="n">
         <v>11304</v>
@@ -2747,7 +2747,7 @@
         <v>4.07049989700317</v>
       </c>
       <c r="G82" t="n">
-        <v>3.93354797363281</v>
+        <v>3.93354773521423</v>
       </c>
       <c r="H82" t="n">
         <v>1333</v>
@@ -2805,7 +2805,7 @@
         <v>3.99900007247925</v>
       </c>
       <c r="G84" t="n">
-        <v>3.86445379257202</v>
+        <v>3.86445355415344</v>
       </c>
       <c r="H84" t="n">
         <v>14743</v>
@@ -2892,7 +2892,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G87" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H87" t="n">
         <v>16436</v>
@@ -2921,7 +2921,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G88" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H88" t="n">
         <v>70067</v>
@@ -2950,7 +2950,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G89" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H89" t="n">
         <v>20248</v>
@@ -2979,7 +2979,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G90" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H90" t="n">
         <v>9804</v>
@@ -3008,7 +3008,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H91" t="n">
         <v>8029</v>
@@ -3124,7 +3124,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G95" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H95" t="n">
         <v>6789</v>
@@ -3153,7 +3153,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H96" t="n">
         <v>16453</v>
@@ -3182,7 +3182,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H97" t="n">
         <v>13893</v>
@@ -3211,7 +3211,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G98" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H98" t="n">
         <v>34445</v>
@@ -3269,7 +3269,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G100" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H100" t="n">
         <v>5569</v>
@@ -3327,7 +3327,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H102" t="n">
         <v>17175</v>
@@ -3385,7 +3385,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H104" t="n">
         <v>4792</v>
@@ -3443,7 +3443,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H106" t="n">
         <v>12618</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H107" t="n">
         <v>7801</v>
@@ -3530,7 +3530,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G109" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H109" t="n">
         <v>27377</v>
@@ -3559,7 +3559,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H110" t="n">
         <v>9652</v>
@@ -3588,7 +3588,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G111" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H111" t="n">
         <v>22427</v>
@@ -3646,7 +3646,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H113" t="n">
         <v>5635</v>
@@ -3675,7 +3675,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G114" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H114" t="n">
         <v>12247</v>
@@ -3704,7 +3704,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G115" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H115" t="n">
         <v>46534</v>
@@ -3762,7 +3762,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G117" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H117" t="n">
         <v>14370</v>
@@ -3791,7 +3791,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G118" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H118" t="n">
         <v>20871</v>
@@ -3849,7 +3849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G120" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H120" t="n">
         <v>51861</v>
@@ -3907,7 +3907,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H122" t="n">
         <v>24632</v>
@@ -3965,7 +3965,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G124" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H124" t="n">
         <v>9251</v>
@@ -4023,7 +4023,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H126" t="n">
         <v>23445</v>
@@ -4052,7 +4052,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H127" t="n">
         <v>13288</v>
@@ -4226,7 +4226,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G133" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H133" t="n">
         <v>69275</v>
@@ -4255,7 +4255,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G134" t="n">
-        <v>3.6866443157196</v>
+        <v>3.68664455413818</v>
       </c>
       <c r="H134" t="n">
         <v>83826</v>
@@ -4284,7 +4284,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G135" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H135" t="n">
         <v>38411</v>
@@ -4342,7 +4342,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G137" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H137" t="n">
         <v>28361</v>
@@ -4371,7 +4371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H138" t="n">
         <v>16251</v>
@@ -4400,7 +4400,7 @@
         <v>4.04500007629395</v>
       </c>
       <c r="G139" t="n">
-        <v>3.90890622138977</v>
+        <v>3.90890598297119</v>
       </c>
       <c r="H139" t="n">
         <v>24663</v>
@@ -4661,7 +4661,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G148" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H148" t="n">
         <v>6408</v>
@@ -4690,7 +4690,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G149" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H149" t="n">
         <v>17007</v>
@@ -4748,7 +4748,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H151" t="n">
         <v>51508</v>
@@ -4893,7 +4893,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H156" t="n">
         <v>57059</v>
@@ -4951,7 +4951,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G158" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H158" t="n">
         <v>51199</v>
@@ -5821,7 +5821,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G188" t="n">
-        <v>4.09251308441162</v>
+        <v>4.09251356124878</v>
       </c>
       <c r="H188" t="n">
         <v>3584</v>
@@ -5995,7 +5995,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G194" t="n">
-        <v>4.18431711196899</v>
+        <v>4.18431663513184</v>
       </c>
       <c r="H194" t="n">
         <v>11423</v>
@@ -6459,7 +6459,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G210" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H210" t="n">
         <v>4401</v>
@@ -6546,7 +6546,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G213" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H213" t="n">
         <v>14225</v>
@@ -6720,7 +6720,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H219" t="n">
         <v>109205</v>
@@ -6981,7 +6981,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G228" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H228" t="n">
         <v>32762</v>
@@ -7358,7 +7358,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>4.59501791000366</v>
+        <v>4.59501838684082</v>
       </c>
       <c r="H241" t="n">
         <v>82951</v>
@@ -7416,7 +7416,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G243" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H243" t="n">
         <v>10325</v>
@@ -7445,7 +7445,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G244" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H244" t="n">
         <v>8300</v>
@@ -7590,7 +7590,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G249" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H249" t="n">
         <v>50047</v>
@@ -7619,7 +7619,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>4.80761575698853</v>
+        <v>4.80761623382568</v>
       </c>
       <c r="H250" t="n">
         <v>91315</v>
@@ -7648,7 +7648,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G251" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H251" t="n">
         <v>63937</v>
@@ -7677,7 +7677,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>4.75929832458496</v>
+        <v>4.75929880142212</v>
       </c>
       <c r="H252" t="n">
         <v>3333</v>
@@ -7793,7 +7793,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H256" t="n">
         <v>24390</v>
@@ -7967,7 +7967,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H262" t="n">
         <v>8895</v>
@@ -8025,7 +8025,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G264" t="n">
-        <v>4.81727981567383</v>
+        <v>4.81727933883667</v>
       </c>
       <c r="H264" t="n">
         <v>44506</v>
@@ -8054,7 +8054,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G265" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H265" t="n">
         <v>48189</v>
@@ -8083,7 +8083,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G266" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H266" t="n">
         <v>41705</v>
@@ -8141,7 +8141,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G268" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H268" t="n">
         <v>123324</v>
@@ -8228,7 +8228,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>4.95740079879761</v>
+        <v>4.95740127563477</v>
       </c>
       <c r="H271" t="n">
         <v>6925</v>
@@ -8315,7 +8315,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G274" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H274" t="n">
         <v>136710</v>
@@ -8344,7 +8344,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G275" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H275" t="n">
         <v>260348</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H278" t="n">
         <v>25684</v>
@@ -8547,7 +8547,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G282" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H282" t="n">
         <v>57869</v>
@@ -8924,7 +8924,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H295" t="n">
         <v>20573</v>
@@ -9040,7 +9040,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H299" t="n">
         <v>19695</v>
@@ -9243,7 +9243,7 @@
         <v>5.5</v>
       </c>
       <c r="G306" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H306" t="n">
         <v>19157</v>
@@ -9359,7 +9359,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>5.28596115112305</v>
+        <v>5.28596162796021</v>
       </c>
       <c r="H310" t="n">
         <v>19428</v>
@@ -9417,7 +9417,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G312" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H312" t="n">
         <v>4283</v>
@@ -9533,7 +9533,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G316" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H316" t="n">
         <v>151029</v>
@@ -9620,7 +9620,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H319" t="n">
         <v>12312</v>
@@ -9649,7 +9649,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G320" t="n">
-        <v>5.65317678451538</v>
+        <v>5.65317630767822</v>
       </c>
       <c r="H320" t="n">
         <v>162473</v>
@@ -9765,7 +9765,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G324" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H324" t="n">
         <v>99309</v>
@@ -9852,7 +9852,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>5.13134527206421</v>
+        <v>5.13134479522705</v>
       </c>
       <c r="H327" t="n">
         <v>34058</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H329" t="n">
         <v>26368</v>
@@ -9968,7 +9968,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G331" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H331" t="n">
         <v>32218</v>
@@ -9997,7 +9997,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G332" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H332" t="n">
         <v>81218</v>
@@ -10026,7 +10026,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H333" t="n">
         <v>14865</v>
@@ -10258,7 +10258,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H341" t="n">
         <v>82529</v>
@@ -10287,7 +10287,7 @@
         <v>5</v>
       </c>
       <c r="G342" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H342" t="n">
         <v>98211</v>
@@ -10461,7 +10461,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>4.89942026138306</v>
+        <v>4.8994197845459</v>
       </c>
       <c r="H348" t="n">
         <v>32626</v>
@@ -10635,7 +10635,7 @@
         <v>5</v>
       </c>
       <c r="G354" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H354" t="n">
         <v>33125</v>
@@ -10751,7 +10751,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G358" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H358" t="n">
         <v>44086</v>
@@ -10867,7 +10867,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H362" t="n">
         <v>11155</v>
@@ -11041,7 +11041,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G368" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H368" t="n">
         <v>26463</v>
@@ -11099,7 +11099,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G370" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H370" t="n">
         <v>8841</v>
@@ -11186,7 +11186,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G373" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H373" t="n">
         <v>16343</v>
@@ -11302,7 +11302,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G377" t="n">
-        <v>4.45489692687988</v>
+        <v>4.45489645004272</v>
       </c>
       <c r="H377" t="n">
         <v>6689</v>
@@ -11418,7 +11418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H381" t="n">
         <v>31236</v>
@@ -11447,7 +11447,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G382" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H382" t="n">
         <v>9513</v>
@@ -11505,7 +11505,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H384" t="n">
         <v>12160</v>
@@ -11563,7 +11563,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G386" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H386" t="n">
         <v>5668</v>
@@ -11679,7 +11679,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H390" t="n">
         <v>5996</v>
@@ -11737,7 +11737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H392" t="n">
         <v>19706</v>
@@ -11795,7 +11795,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G394" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H394" t="n">
         <v>18905</v>
@@ -12027,7 +12027,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G402" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H402" t="n">
         <v>20308</v>
@@ -12288,7 +12288,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H411" t="n">
         <v>7185</v>
@@ -12317,7 +12317,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G412" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H412" t="n">
         <v>7082</v>
@@ -12375,7 +12375,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G414" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H414" t="n">
         <v>49474</v>
@@ -12520,7 +12520,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H419" t="n">
         <v>7439</v>
@@ -12549,7 +12549,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G420" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H420" t="n">
         <v>15236</v>
@@ -12607,7 +12607,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G422" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H422" t="n">
         <v>10351</v>
@@ -12636,7 +12636,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G423" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H423" t="n">
         <v>17376</v>
@@ -12810,7 +12810,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G429" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H429" t="n">
         <v>7532</v>
@@ -12868,7 +12868,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G431" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H431" t="n">
         <v>2225</v>
@@ -12984,7 +12984,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G435" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H435" t="n">
         <v>6281</v>
@@ -13013,7 +13013,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G436" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H436" t="n">
         <v>7095</v>
@@ -13332,7 +13332,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H447" t="n">
         <v>1474</v>
@@ -13361,7 +13361,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G448" t="n">
-        <v>4.47422361373901</v>
+        <v>4.47422409057617</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G452" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H452" t="n">
         <v>5271</v>
@@ -13564,7 +13564,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G455" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H455" t="n">
         <v>7161</v>
@@ -13622,7 +13622,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H457" t="n">
         <v>13780</v>
@@ -13825,7 +13825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H464" t="n">
         <v>16567</v>
@@ -13883,7 +13883,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G466" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H466" t="n">
         <v>4338</v>
@@ -13912,7 +13912,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G467" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H467" t="n">
         <v>6710</v>
@@ -14028,7 +14028,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H471" t="n">
         <v>8536</v>
@@ -14492,7 +14492,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H487" t="n">
         <v>22603</v>
@@ -14608,7 +14608,7 @@
         <v>5</v>
       </c>
       <c r="G491" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H491" t="n">
         <v>18592</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H493" t="n">
         <v>6171</v>
@@ -14695,7 +14695,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H494" t="n">
         <v>7707</v>
@@ -14927,7 +14927,7 @@
         <v>4.5</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H502" t="n">
         <v>22877</v>
@@ -15130,7 +15130,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G509" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H509" t="n">
         <v>4568</v>
@@ -15304,7 +15304,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G515" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H515" t="n">
         <v>32842</v>
@@ -15362,7 +15362,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G517" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H517" t="n">
         <v>11854</v>
@@ -15391,7 +15391,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H518" t="n">
         <v>8330</v>
@@ -15507,7 +15507,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H522" t="n">
         <v>3006</v>
@@ -15565,7 +15565,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H524" t="n">
         <v>29907</v>
@@ -15623,7 +15623,7 @@
         <v>5</v>
       </c>
       <c r="G526" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H526" t="n">
         <v>1616</v>
@@ -15855,7 +15855,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H534" t="n">
         <v>33564</v>
@@ -15884,7 +15884,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H535" t="n">
         <v>17947</v>
@@ -16116,7 +16116,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G543" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H543" t="n">
         <v>7536</v>
@@ -16145,7 +16145,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H544" t="n">
         <v>20916</v>
@@ -16203,7 +16203,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G546" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H546" t="n">
         <v>18431</v>
@@ -16232,7 +16232,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H547" t="n">
         <v>18024</v>
@@ -16261,7 +16261,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H548" t="n">
         <v>5276</v>
@@ -16290,7 +16290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H549" t="n">
         <v>11659</v>
@@ -16319,7 +16319,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G550" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H550" t="n">
         <v>9307</v>
@@ -16464,7 +16464,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G555" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H555" t="n">
         <v>211195</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H558" t="n">
         <v>68260</v>
@@ -16725,7 +16725,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G564" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H564" t="n">
         <v>44216</v>
@@ -16928,7 +16928,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H571" t="n">
         <v>137820</v>
@@ -16957,7 +16957,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G572" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H572" t="n">
         <v>46726</v>
@@ -17102,7 +17102,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G577" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H577" t="n">
         <v>232133</v>
@@ -17218,7 +17218,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H581" t="n">
         <v>183006</v>
@@ -17276,7 +17276,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G583" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H583" t="n">
         <v>110634</v>
@@ -17334,7 +17334,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G585" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H585" t="n">
         <v>83401</v>
@@ -17450,7 +17450,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H589" t="n">
         <v>48955</v>
@@ -17479,7 +17479,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H590" t="n">
         <v>54246</v>
@@ -17595,7 +17595,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G594" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H594" t="n">
         <v>141610</v>
@@ -17798,7 +17798,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H601" t="n">
         <v>21002</v>
@@ -17885,7 +17885,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G604" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H604" t="n">
         <v>23320</v>
@@ -17972,7 +17972,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G607" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H607" t="n">
         <v>46484</v>
@@ -18320,7 +18320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H619" t="n">
         <v>4323</v>
@@ -18436,7 +18436,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G623" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H623" t="n">
         <v>16947</v>
@@ -18465,7 +18465,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H624" t="n">
         <v>5894</v>
@@ -18523,7 +18523,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H626" t="n">
         <v>25679</v>
@@ -18639,7 +18639,7 @@
         <v>5</v>
       </c>
       <c r="G630" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H630" t="n">
         <v>33871</v>
@@ -18697,7 +18697,7 @@
         <v>5</v>
       </c>
       <c r="G632" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H632" t="n">
         <v>24188</v>
@@ -18784,7 +18784,7 @@
         <v>5</v>
       </c>
       <c r="G635" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H635" t="n">
         <v>57265</v>
@@ -19074,7 +19074,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G645" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H645" t="n">
         <v>121832</v>
@@ -19103,7 +19103,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G646" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H646" t="n">
         <v>46978</v>
@@ -19480,7 +19480,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G659" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H659" t="n">
         <v>58410</v>
@@ -19509,7 +19509,7 @@
         <v>5.5</v>
       </c>
       <c r="G660" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H660" t="n">
         <v>94430</v>
@@ -19538,7 +19538,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G661" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H661" t="n">
         <v>16435</v>
@@ -19625,7 +19625,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G664" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H664" t="n">
         <v>36840</v>
@@ -19770,7 +19770,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G669" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H669" t="n">
         <v>26798</v>
@@ -20002,7 +20002,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H677" t="n">
         <v>3700</v>
@@ -20031,7 +20031,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H678" t="n">
         <v>31808</v>
@@ -20060,7 +20060,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G679" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H679" t="n">
         <v>28368</v>
@@ -20118,7 +20118,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G681" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H681" t="n">
         <v>19635</v>
@@ -20321,7 +20321,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H688" t="n">
         <v>116323</v>
@@ -20350,7 +20350,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H689" t="n">
         <v>33063</v>
@@ -20379,7 +20379,7 @@
         <v>5.5</v>
       </c>
       <c r="G690" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H690" t="n">
         <v>12669</v>
@@ -20582,7 +20582,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G697" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H697" t="n">
         <v>29126</v>
@@ -20611,7 +20611,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G698" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H698" t="n">
         <v>31677</v>
@@ -20669,7 +20669,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G700" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H700" t="n">
         <v>1753</v>
@@ -20698,7 +20698,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H701" t="n">
         <v>9847</v>
@@ -20727,7 +20727,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H702" t="n">
         <v>15481</v>
@@ -20756,7 +20756,7 @@
         <v>5.5</v>
       </c>
       <c r="G703" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H703" t="n">
         <v>4841</v>
@@ -20785,7 +20785,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G704" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H704" t="n">
         <v>20397</v>
@@ -20814,7 +20814,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G705" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H705" t="n">
         <v>22265</v>
@@ -20872,7 +20872,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G707" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H707" t="n">
         <v>56099</v>
@@ -20901,7 +20901,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G708" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H708" t="n">
         <v>72110</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H710" t="n">
         <v>41126</v>
@@ -20988,7 +20988,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H711" t="n">
         <v>41372</v>
@@ -21075,7 +21075,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G714" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H714" t="n">
         <v>27761</v>
@@ -21249,7 +21249,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H720" t="n">
         <v>30084</v>
@@ -21365,7 +21365,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G724" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H724" t="n">
         <v>22097</v>
@@ -21394,7 +21394,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G725" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H725" t="n">
         <v>21424</v>
@@ -21481,7 +21481,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G728" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H728" t="n">
         <v>28785</v>
@@ -21539,7 +21539,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G730" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H730" t="n">
         <v>63831</v>
@@ -21568,7 +21568,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G731" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H731" t="n">
         <v>14790</v>
@@ -21626,7 +21626,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G733" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H733" t="n">
         <v>54638</v>
@@ -21655,7 +21655,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H734" t="n">
         <v>25806</v>
@@ -21771,7 +21771,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H738" t="n">
         <v>9042</v>
@@ -21858,7 +21858,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G741" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H741" t="n">
         <v>25001</v>
@@ -21945,7 +21945,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G744" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H744" t="n">
         <v>36541</v>
@@ -22119,7 +22119,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G750" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H750" t="n">
         <v>24595</v>
@@ -22148,7 +22148,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G751" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H751" t="n">
         <v>7605</v>
@@ -22177,7 +22177,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G752" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H752" t="n">
         <v>31505</v>
@@ -22235,7 +22235,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G754" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H754" t="n">
         <v>15983</v>
@@ -22293,7 +22293,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H756" t="n">
         <v>24115</v>
@@ -22322,7 +22322,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H757" t="n">
         <v>23156</v>
@@ -22351,7 +22351,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G758" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H758" t="n">
         <v>22826</v>
@@ -22380,7 +22380,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G759" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H759" t="n">
         <v>27789</v>
@@ -22554,7 +22554,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>5.75947618484497</v>
+        <v>5.75947570800781</v>
       </c>
       <c r="H765" t="n">
         <v>90704</v>
@@ -22641,7 +22641,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G768" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H768" t="n">
         <v>25948</v>
@@ -22699,7 +22699,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>5.72082138061523</v>
+        <v>5.72082185745239</v>
       </c>
       <c r="H770" t="n">
         <v>21002</v>
@@ -22728,7 +22728,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G771" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H771" t="n">
         <v>45095</v>
@@ -22757,7 +22757,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>5.81745672225952</v>
+        <v>5.81745719909668</v>
       </c>
       <c r="H772" t="n">
         <v>32302</v>
@@ -22786,7 +22786,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G773" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H773" t="n">
         <v>48385</v>
@@ -22873,7 +22873,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G776" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H776" t="n">
         <v>33170</v>
@@ -22902,7 +22902,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G777" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H777" t="n">
         <v>140269</v>
@@ -22931,7 +22931,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G778" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H778" t="n">
         <v>51904</v>
@@ -22989,7 +22989,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H780" t="n">
         <v>26033</v>
@@ -23018,7 +23018,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G781" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H781" t="n">
         <v>69932</v>
@@ -23134,7 +23134,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G785" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H785" t="n">
         <v>21254</v>
@@ -23424,7 +23424,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H795" t="n">
         <v>129207</v>
@@ -23453,7 +23453,7 @@
         <v>5.5</v>
       </c>
       <c r="G796" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H796" t="n">
         <v>74996</v>
@@ -23656,7 +23656,7 @@
         <v>5</v>
       </c>
       <c r="G803" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H803" t="n">
         <v>95136</v>
@@ -23830,7 +23830,7 @@
         <v>5</v>
       </c>
       <c r="G809" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H809" t="n">
         <v>42616</v>
@@ -23975,7 +23975,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G814" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H814" t="n">
         <v>147606</v>
@@ -24004,7 +24004,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G815" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H815" t="n">
         <v>20160</v>
@@ -24062,7 +24062,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G817" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H817" t="n">
         <v>48978</v>
@@ -24091,7 +24091,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G818" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H818" t="n">
         <v>17601</v>
@@ -24178,7 +24178,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H821" t="n">
         <v>17172</v>
@@ -24207,7 +24207,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G822" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H822" t="n">
         <v>21711</v>
@@ -24236,7 +24236,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G823" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H823" t="n">
         <v>13038</v>
@@ -24381,7 +24381,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G828" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H828" t="n">
         <v>13399</v>
@@ -24700,7 +24700,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G839" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H839" t="n">
         <v>10091</v>
@@ -24729,7 +24729,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G840" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H840" t="n">
         <v>20843</v>
@@ -24990,7 +24990,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H849" t="n">
         <v>88040</v>
@@ -25048,7 +25048,7 @@
         <v>4.5</v>
       </c>
       <c r="G851" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H851" t="n">
         <v>61678</v>
@@ -25077,7 +25077,7 @@
         <v>4.5</v>
       </c>
       <c r="G852" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H852" t="n">
         <v>25922</v>
@@ -25222,7 +25222,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G857" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H857" t="n">
         <v>26131</v>
@@ -25309,7 +25309,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H860" t="n">
         <v>25865</v>
@@ -25483,7 +25483,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G866" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H866" t="n">
         <v>10855</v>
@@ -25541,7 +25541,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G868" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H868" t="n">
         <v>4022</v>
@@ -25570,7 +25570,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G869" t="n">
-        <v>4.62400817871094</v>
+        <v>4.6240086555481</v>
       </c>
       <c r="H869" t="n">
         <v>9713</v>
@@ -25628,7 +25628,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G871" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H871" t="n">
         <v>3876</v>
@@ -25802,7 +25802,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G877" t="n">
-        <v>4.56602764129639</v>
+        <v>4.56602716445923</v>
       </c>
       <c r="H877" t="n">
         <v>1609</v>
@@ -26179,7 +26179,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G890" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H890" t="n">
         <v>21852</v>
@@ -26208,7 +26208,7 @@
         <v>4.5149998664856</v>
       </c>
       <c r="G891" t="n">
-        <v>4.36309289932251</v>
+        <v>4.36309242248535</v>
       </c>
       <c r="H891" t="n">
         <v>19273</v>
@@ -26237,7 +26237,7 @@
         <v>4.5</v>
       </c>
       <c r="G892" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H892" t="n">
         <v>9208</v>
@@ -26295,7 +26295,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G894" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H894" t="n">
         <v>13445</v>
@@ -26324,7 +26324,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>4.26645755767822</v>
+        <v>4.26645708084106</v>
       </c>
       <c r="H895" t="n">
         <v>43685</v>
@@ -26440,7 +26440,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G899" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H899" t="n">
         <v>27960</v>
@@ -26498,7 +26498,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G901" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H901" t="n">
         <v>33825</v>
@@ -26672,7 +26672,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G907" t="n">
-        <v>4.0441951751709</v>
+        <v>4.04419565200806</v>
       </c>
       <c r="H907" t="n">
         <v>15181</v>
@@ -26730,7 +26730,7 @@
         <v>4.125</v>
       </c>
       <c r="G909" t="n">
-        <v>3.98621439933777</v>
+        <v>3.98621416091919</v>
       </c>
       <c r="H909" t="n">
         <v>14992</v>
@@ -26904,7 +26904,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G915" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H915" t="n">
         <v>53863</v>
@@ -27049,7 +27049,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G920" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H920" t="n">
         <v>5004</v>
@@ -27078,7 +27078,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G921" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H921" t="n">
         <v>4290</v>
@@ -27136,7 +27136,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G923" t="n">
-        <v>3.87991523742676</v>
+        <v>3.87991499900818</v>
       </c>
       <c r="H923" t="n">
         <v>8482</v>
@@ -27165,7 +27165,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G924" t="n">
-        <v>4.03453254699707</v>
+        <v>4.03453207015991</v>
       </c>
       <c r="H924" t="n">
         <v>16764</v>
@@ -27513,7 +27513,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H936" t="n">
         <v>1516</v>
@@ -27629,7 +27629,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>4.06352281570435</v>
+        <v>4.06352233886719</v>
       </c>
       <c r="H940" t="n">
         <v>4899</v>
@@ -27658,7 +27658,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G941" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H941" t="n">
         <v>56027</v>
@@ -27716,7 +27716,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G943" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H943" t="n">
         <v>7945</v>
@@ -27861,7 +27861,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G948" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H948" t="n">
         <v>9054</v>
@@ -27890,7 +27890,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G949" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H949" t="n">
         <v>974</v>
@@ -28006,7 +28006,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G953" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H953" t="n">
         <v>15215</v>
@@ -28122,7 +28122,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G957" t="n">
-        <v>3.82193374633789</v>
+        <v>3.82193398475647</v>
       </c>
       <c r="H957" t="n">
         <v>1040</v>
@@ -28151,7 +28151,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H958" t="n">
         <v>5878</v>
@@ -28296,7 +28296,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G963" t="n">
-        <v>3.78327989578247</v>
+        <v>3.78327965736389</v>
       </c>
       <c r="H963" t="n">
         <v>1069</v>
@@ -28325,7 +28325,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G964" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H964" t="n">
         <v>4985</v>
@@ -28354,7 +28354,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G965" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H965" t="n">
         <v>1586</v>
@@ -28412,7 +28412,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G967" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H967" t="n">
         <v>22825</v>
@@ -28499,7 +28499,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G970" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H970" t="n">
         <v>1519</v>
@@ -28615,7 +28615,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G974" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H974" t="n">
         <v>61487</v>
@@ -28702,7 +28702,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G977" t="n">
-        <v>3.85575652122498</v>
+        <v>3.8557562828064</v>
       </c>
       <c r="H977" t="n">
         <v>13657</v>
@@ -28731,7 +28731,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G978" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H978" t="n">
         <v>26282</v>
@@ -28818,7 +28818,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H981" t="n">
         <v>4451</v>
@@ -28876,7 +28876,7 @@
         <v>3.75</v>
       </c>
       <c r="G983" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H983" t="n">
         <v>36877</v>
@@ -28905,7 +28905,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G984" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H984" t="n">
         <v>1838</v>
@@ -28963,7 +28963,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G986" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H986" t="n">
         <v>12068</v>
@@ -28992,7 +28992,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H987" t="n">
         <v>26097</v>
@@ -29021,7 +29021,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G988" t="n">
-        <v>3.74945735931396</v>
+        <v>3.74945759773254</v>
       </c>
       <c r="H988" t="n">
         <v>6234</v>
@@ -29224,7 +29224,7 @@
         <v>3.75</v>
       </c>
       <c r="G995" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H995" t="n">
         <v>11228</v>
@@ -29253,7 +29253,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G996" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H996" t="n">
         <v>4330</v>
@@ -29282,7 +29282,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H997" t="n">
         <v>8092</v>
@@ -29398,7 +29398,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.9668869972229</v>
+        <v>3.96688747406006</v>
       </c>
       <c r="H1001" t="n">
         <v>517</v>
@@ -29514,7 +29514,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.91856932640076</v>
+        <v>3.91856908798218</v>
       </c>
       <c r="H1005" t="n">
         <v>15349</v>
@@ -29804,7 +29804,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1015" t="n">
         <v>20471</v>
@@ -29891,7 +29891,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1018" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1018" t="n">
         <v>24364</v>
@@ -29920,7 +29920,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1019" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1019" t="n">
         <v>19551</v>
@@ -30007,7 +30007,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1022" t="n">
         <v>3870</v>
@@ -30616,7 +30616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1043" t="n">
         <v>7439</v>
@@ -30703,7 +30703,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1046" t="n">
         <v>15720</v>
@@ -30732,7 +30732,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1047" t="n">
         <v>13320</v>
@@ -30790,7 +30790,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1049" t="n">
         <v>1434</v>
@@ -30848,7 +30848,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.49820494651794</v>
+        <v>3.49820470809937</v>
       </c>
       <c r="H1051" t="n">
         <v>22296</v>
@@ -30906,7 +30906,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1053" t="n">
         <v>16504</v>
@@ -30935,7 +30935,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1054" t="n">
         <v>12412</v>
@@ -30993,7 +30993,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1056" t="n">
         <v>12576</v>
@@ -31051,7 +31051,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.73013019561768</v>
+        <v>3.7301299571991</v>
       </c>
       <c r="H1058" t="n">
         <v>9513</v>
@@ -31225,7 +31225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1064" t="n">
         <v>11552</v>
@@ -31254,7 +31254,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.71563506126404</v>
+        <v>3.71563482284546</v>
       </c>
       <c r="H1065" t="n">
         <v>34413</v>
@@ -31283,7 +31283,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1066" t="n">
         <v>64042</v>
@@ -31341,7 +31341,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1068" t="n">
         <v>24424</v>
@@ -31399,7 +31399,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1070" t="n">
         <v>18126</v>
@@ -31457,7 +31457,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.53685927391052</v>
+        <v>3.5368595123291</v>
       </c>
       <c r="H1072" t="n">
         <v>26947</v>
@@ -31515,7 +31515,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1074" t="n">
         <v>76053</v>
@@ -31689,7 +31689,7 @@
         <v>3.75</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1080" t="n">
         <v>11888</v>
@@ -31718,7 +31718,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1081" t="n">
         <v>87040</v>
@@ -31776,7 +31776,7 @@
         <v>3.75</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1083" t="n">
         <v>27634</v>
@@ -31805,7 +31805,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.55135440826416</v>
+        <v>3.55135464668274</v>
       </c>
       <c r="H1084" t="n">
         <v>183394</v>
@@ -31863,7 +31863,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1086" t="n">
         <v>39968</v>
@@ -31892,7 +31892,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1087" t="n">
         <v>19044</v>
@@ -31950,7 +31950,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.5996720790863</v>
+        <v>3.59967231750488</v>
       </c>
       <c r="H1089" t="n">
         <v>21496</v>
@@ -32037,7 +32037,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1092" t="n">
         <v>4199</v>
@@ -32095,7 +32095,7 @@
         <v>3.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1094" t="n">
         <v>2930</v>
@@ -32124,7 +32124,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1095" t="n">
         <v>17824</v>
@@ -32414,7 +32414,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1105" t="n">
         <v>8012</v>
@@ -32501,7 +32501,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1108" t="n">
         <v>20364</v>
@@ -32617,7 +32617,7 @@
         <v>3.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1112" t="n">
         <v>8014</v>
@@ -32646,7 +32646,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1113" t="n">
-        <v>3.67214870452881</v>
+        <v>3.67214894294739</v>
       </c>
       <c r="H1113" t="n">
         <v>5992</v>
@@ -32791,7 +32791,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1118" t="n">
         <v>7468</v>
@@ -32878,7 +32878,7 @@
         <v>3.75</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1121" t="n">
         <v>7108</v>
@@ -32907,7 +32907,7 @@
         <v>3.75</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.62383103370667</v>
+        <v>3.62383127212524</v>
       </c>
       <c r="H1122" t="n">
         <v>3566</v>
@@ -32965,7 +32965,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1124" t="n">
         <v>6159</v>
@@ -32994,7 +32994,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1125" t="n">
         <v>36559</v>
@@ -33023,7 +33023,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1126" t="n">
         <v>5854</v>
@@ -33081,7 +33081,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1128" t="n">
         <v>85216</v>
@@ -33110,7 +33110,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1129" t="n">
-        <v>3.56585001945496</v>
+        <v>3.56584978103638</v>
       </c>
       <c r="H1129" t="n">
         <v>44308</v>
@@ -33168,7 +33168,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1131" t="n">
-        <v>3.59484076499939</v>
+        <v>3.59484052658081</v>
       </c>
       <c r="H1131" t="n">
         <v>2341</v>
@@ -33197,7 +33197,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1132" t="n">
-        <v>3.57551336288452</v>
+        <v>3.5755136013031</v>
       </c>
       <c r="H1132" t="n">
         <v>13385</v>
@@ -33371,7 +33371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1138" t="n">
-        <v>3.69147610664368</v>
+        <v>3.6914758682251</v>
       </c>
       <c r="H1138" t="n">
         <v>23416</v>
@@ -33516,7 +33516,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1143" t="n">
-        <v>3.83642935752869</v>
+        <v>3.83642911911011</v>
       </c>
       <c r="H1143" t="n">
         <v>14293</v>
@@ -33574,7 +33574,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1145" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1145" t="n">
         <v>44949</v>
@@ -33719,7 +33719,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1150" t="n">
-        <v>3.97171926498413</v>
+        <v>3.97171878814697</v>
       </c>
       <c r="H1150" t="n">
         <v>7061</v>
@@ -33748,7 +33748,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1151" t="n">
         <v>5770</v>
@@ -33777,7 +33777,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1152" t="n">
         <v>12871</v>
@@ -33806,7 +33806,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1153" t="n">
         <v>21159</v>
@@ -33835,7 +33835,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1154" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1154" t="n">
         <v>63339</v>
@@ -33864,7 +33864,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1155" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1155" t="n">
         <v>13966</v>
@@ -34125,7 +34125,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1164" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1164" t="n">
         <v>8374</v>
@@ -34154,7 +34154,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1165" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1165" t="n">
         <v>8257</v>
@@ -34241,7 +34241,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1168" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1168" t="n">
         <v>51543</v>
@@ -34299,7 +34299,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1170" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1170" t="n">
         <v>8138</v>
@@ -34415,7 +34415,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1174" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1174" t="n">
         <v>18764</v>
@@ -34589,7 +34589,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1180" t="n">
-        <v>3.87508368492126</v>
+        <v>3.87508392333984</v>
       </c>
       <c r="H1180" t="n">
         <v>22131</v>
@@ -34705,7 +34705,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>3.90407419204712</v>
+        <v>3.90407395362854</v>
       </c>
       <c r="H1184" t="n">
         <v>1634</v>
@@ -34734,7 +34734,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1185" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1185" t="n">
         <v>1460</v>
@@ -34792,7 +34792,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1187" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1187" t="n">
         <v>21143</v>
@@ -34821,7 +34821,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1188" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1188" t="n">
         <v>8937</v>
@@ -34850,7 +34850,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1189" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1189" t="n">
         <v>9771</v>
@@ -34908,7 +34908,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1191" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1191" t="n">
         <v>3139</v>
@@ -34966,7 +34966,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1193" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1193" t="n">
         <v>23650</v>
@@ -34995,7 +34995,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1194" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1194" t="n">
         <v>30769</v>
@@ -35024,7 +35024,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1195" t="n">
-        <v>3.91373777389526</v>
+        <v>3.91373801231384</v>
       </c>
       <c r="H1195" t="n">
         <v>53170</v>
@@ -35053,7 +35053,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1196" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1196" t="n">
         <v>8141</v>
@@ -35082,7 +35082,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1197" t="n">
-        <v>3.93306493759155</v>
+        <v>3.93306469917297</v>
       </c>
       <c r="H1197" t="n">
         <v>18888</v>
@@ -35111,7 +35111,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1198" t="n">
-        <v>3.95239233970642</v>
+        <v>3.95239210128784</v>
       </c>
       <c r="H1198" t="n">
         <v>2167</v>
@@ -35140,7 +35140,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1199" t="n">
         <v>21694</v>
@@ -35169,7 +35169,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1200" t="n">
         <v>30561</v>
@@ -35227,7 +35227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1202" t="n">
-        <v>3.96205520629883</v>
+        <v>3.96205544471741</v>
       </c>
       <c r="H1202" t="n">
         <v>13802</v>
@@ -35285,7 +35285,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.0200366973877</v>
+        <v>4.02003622055054</v>
       </c>
       <c r="H1204" t="n">
         <v>39802</v>
@@ -35430,7 +35430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.07801818847656</v>
+        <v>4.0780177116394</v>
       </c>
       <c r="H1209" t="n">
         <v>13920</v>
@@ -35952,7 +35952,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.01037311553955</v>
+        <v>4.01037359237671</v>
       </c>
       <c r="H1227" t="n">
         <v>11126</v>
@@ -36010,7 +36010,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.23263454437256</v>
+        <v>4.23263502120972</v>
       </c>
       <c r="H1229" t="n">
         <v>30135</v>
@@ -36184,7 +36184,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1235" t="n">
         <v>87770</v>
@@ -36242,7 +36242,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1237" t="n">
         <v>86783</v>
@@ -36271,7 +36271,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1238" t="n">
-        <v>4.28095197677612</v>
+        <v>4.28095245361328</v>
       </c>
       <c r="H1238" t="n">
         <v>10697</v>
@@ -36300,7 +36300,7 @@
         <v>4.5</v>
       </c>
       <c r="G1239" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1239" t="n">
         <v>633742</v>
@@ -36387,7 +36387,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1242" t="n">
         <v>33483</v>
@@ -36416,7 +36416,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1243" t="n">
-        <v>4.22297143936157</v>
+        <v>4.22297096252441</v>
       </c>
       <c r="H1243" t="n">
         <v>111404</v>
@@ -36474,7 +36474,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1245" t="n">
         <v>71817</v>
@@ -36503,7 +36503,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1246" t="n">
         <v>15207</v>
@@ -36561,7 +36561,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1248" t="n">
         <v>263769</v>
@@ -36648,7 +36648,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.53220462799072</v>
+        <v>4.53220510482788</v>
       </c>
       <c r="H1251" t="n">
         <v>22609</v>
@@ -36822,7 +36822,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.27128934860229</v>
+        <v>4.27128887176514</v>
       </c>
       <c r="H1257" t="n">
         <v>38711</v>
@@ -36909,7 +36909,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1260" t="n">
         <v>48866</v>
@@ -36938,7 +36938,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1261" t="n">
         <v>88377</v>
@@ -37054,7 +37054,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1265" t="n">
         <v>106306</v>
@@ -37547,7 +37547,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1282" t="n">
         <v>41916</v>
@@ -37663,7 +37663,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1286" t="n">
         <v>18275</v>
@@ -37692,7 +37692,7 @@
         <v>4.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1287" t="n">
         <v>38266</v>
@@ -37721,7 +37721,7 @@
         <v>4.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1288" t="n">
         <v>44950</v>
@@ -37750,7 +37750,7 @@
         <v>4.5</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1289" t="n">
         <v>154179</v>
@@ -37808,7 +37808,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1291" t="n">
         <v>48801</v>
@@ -37895,7 +37895,7 @@
         <v>4.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1294" t="n">
         <v>76505</v>
@@ -38011,7 +38011,7 @@
         <v>4.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1298" t="n">
         <v>108894</v>
@@ -38040,7 +38040,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1299" t="n">
         <v>13424</v>
@@ -38098,7 +38098,7 @@
         <v>4.5</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1301" t="n">
         <v>3761</v>
@@ -38127,7 +38127,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.38725137710571</v>
+        <v>4.38725185394287</v>
       </c>
       <c r="H1302" t="n">
         <v>18383</v>
@@ -38272,7 +38272,7 @@
         <v>4.5</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1307" t="n">
         <v>33977</v>
@@ -38330,7 +38330,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1309" t="n">
         <v>8950</v>
@@ -38562,7 +38562,7 @@
         <v>4.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.34859752655029</v>
+        <v>4.34859704971313</v>
       </c>
       <c r="H1317" t="n">
         <v>2395</v>
@@ -38620,7 +38620,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.26162528991699</v>
+        <v>4.26162576675415</v>
       </c>
       <c r="H1319" t="n">
         <v>2013</v>
@@ -38649,7 +38649,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.31960678100586</v>
+        <v>4.3196063041687</v>
       </c>
       <c r="H1320" t="n">
         <v>19847</v>
@@ -38678,7 +38678,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.33893346786499</v>
+        <v>4.33893394470215</v>
       </c>
       <c r="H1321" t="n">
         <v>6721</v>
@@ -38707,7 +38707,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1322" t="n">
         <v>4183885</v>
@@ -38968,7 +38968,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1331" t="n">
         <v>17017</v>
@@ -38997,7 +38997,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1332" t="n">
         <v>17023</v>
@@ -39113,7 +39113,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1336" t="n">
         <v>7875</v>
@@ -39171,7 +39171,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1338" t="n">
         <v>579091</v>
@@ -39200,7 +39200,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1339" t="n">
         <v>13097</v>
@@ -39258,7 +39258,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1341" t="n">
         <v>18512</v>
@@ -39345,7 +39345,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1344" t="n">
         <v>142420</v>
@@ -39374,7 +39374,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1345" t="n">
         <v>32214</v>
@@ -39403,7 +39403,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1346" t="n">
         <v>117615</v>
@@ -39461,7 +39461,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1348" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1348" t="n">
         <v>45261</v>
@@ -39490,7 +39490,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1349" t="n">
         <v>53301</v>
@@ -39519,7 +39519,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1350" t="n">
         <v>53244</v>
@@ -39548,7 +39548,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1351" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1351" t="n">
         <v>128034</v>
@@ -39751,7 +39751,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1358" t="n">
         <v>28701</v>
@@ -39954,7 +39954,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1365" t="n">
         <v>13059</v>
@@ -40012,7 +40012,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1367" t="n">
         <v>15645</v>
@@ -40041,7 +40041,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1368" t="n">
         <v>36938</v>
@@ -40070,7 +40070,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1369" t="n">
         <v>30397</v>
@@ -40099,7 +40099,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.70614910125732</v>
+        <v>4.70614862442017</v>
       </c>
       <c r="H1370" t="n">
         <v>59503</v>
@@ -40128,7 +40128,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.71581220626831</v>
+        <v>4.71581268310547</v>
       </c>
       <c r="H1371" t="n">
         <v>7128</v>
@@ -40186,7 +40186,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1373" t="n">
         <v>53763</v>
@@ -40244,7 +40244,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1375" t="n">
         <v>80223</v>
@@ -40360,7 +40360,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.76412963867188</v>
+        <v>4.76413011550903</v>
       </c>
       <c r="H1379" t="n">
         <v>35399</v>
@@ -40389,7 +40389,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1380" t="n">
         <v>66631</v>
@@ -40418,7 +40418,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1381" t="n">
         <v>36618</v>
@@ -40476,7 +40476,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1383" t="n">
         <v>9917</v>
@@ -40563,7 +40563,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1386" t="n">
         <v>14411</v>
@@ -40592,7 +40592,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1387" t="n">
         <v>5736</v>
@@ -40650,7 +40650,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.56119537353516</v>
+        <v>4.561194896698</v>
       </c>
       <c r="H1389" t="n">
         <v>33151</v>
@@ -40708,7 +40708,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.64816761016846</v>
+        <v>4.6481671333313</v>
       </c>
       <c r="H1391" t="n">
         <v>172952</v>
@@ -40737,7 +40737,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1392" t="n">
         <v>27304</v>
@@ -40766,7 +40766,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1393" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1393" t="n">
         <v>10573</v>
@@ -40824,7 +40824,7 @@
         <v>5</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1395" t="n">
         <v>16020</v>
@@ -40882,7 +40882,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.63850402832031</v>
+        <v>4.63850450515747</v>
       </c>
       <c r="H1397" t="n">
         <v>25629</v>
@@ -40911,7 +40911,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.69648551940918</v>
+        <v>4.69648504257202</v>
       </c>
       <c r="H1398" t="n">
         <v>21495</v>
@@ -40940,7 +40940,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.66749429702759</v>
+        <v>4.66749477386475</v>
       </c>
       <c r="H1399" t="n">
         <v>11491</v>
@@ -40969,7 +40969,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1400" t="n">
         <v>70839</v>
@@ -41027,7 +41027,7 @@
         <v>5</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1402" t="n">
         <v>25324</v>
@@ -41346,7 +41346,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1413" t="n">
         <v>23278</v>
@@ -41433,7 +41433,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1416" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1416" t="n">
         <v>86929</v>
@@ -41578,7 +41578,7 @@
         <v>5.5</v>
       </c>
       <c r="G1421" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1421" t="n">
         <v>84292</v>
@@ -41636,7 +41636,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1423" t="n">
         <v>17733</v>
@@ -41839,7 +41839,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1430" t="n">
         <v>17929</v>
@@ -42100,7 +42100,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1439" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1439" t="n">
         <v>30849</v>
@@ -42245,7 +42245,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1444" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1444" t="n">
         <v>16400</v>
@@ -42448,7 +42448,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1451" t="n">
         <v>10674</v>
@@ -42593,7 +42593,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1456" t="n">
         <v>14950</v>
@@ -42651,7 +42651,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1458" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1458" t="n">
         <v>53885</v>
@@ -42680,7 +42680,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1459" t="n">
         <v>43894</v>
@@ -42825,7 +42825,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1464" t="n">
         <v>6023</v>
@@ -42854,7 +42854,7 @@
         <v>5</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1465" t="n">
         <v>13746</v>
@@ -42941,7 +42941,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1468" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1468" t="n">
         <v>17342</v>
@@ -43318,7 +43318,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1481" t="n">
         <v>4088</v>
@@ -43434,7 +43434,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1485" t="n">
         <v>18559</v>
@@ -43463,7 +43463,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1486" t="n">
         <v>5313</v>
@@ -43695,7 +43695,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1494" t="n">
         <v>10058</v>
@@ -43724,7 +43724,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1495" t="n">
         <v>6566</v>
@@ -43898,7 +43898,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1501" t="n">
         <v>24701</v>
@@ -43927,7 +43927,7 @@
         <v>5.5</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1502" t="n">
         <v>13712</v>
@@ -43985,7 +43985,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1504" t="n">
         <v>17967</v>
@@ -44014,7 +44014,7 @@
         <v>5.5</v>
       </c>
       <c r="G1505" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1505" t="n">
         <v>12753</v>
@@ -44043,7 +44043,7 @@
         <v>5.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1506" t="n">
         <v>4017</v>
@@ -44304,7 +44304,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1515" t="n">
         <v>32760</v>
@@ -44420,7 +44420,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1519" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1519" t="n">
         <v>13224</v>
@@ -44449,7 +44449,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1520" t="n">
         <v>15389</v>
@@ -44536,7 +44536,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1523" t="n">
         <v>23568</v>
@@ -44652,7 +44652,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1527" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1527" t="n">
         <v>12057</v>
@@ -44681,7 +44681,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1528" t="n">
         <v>10102</v>
@@ -44710,7 +44710,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1529" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1529" t="n">
         <v>11999</v>
@@ -44768,7 +44768,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.37293386459351</v>
+        <v>5.37293338775635</v>
       </c>
       <c r="H1531" t="n">
         <v>23916</v>
@@ -44797,7 +44797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1532" t="n">
-        <v>5.58553171157837</v>
+        <v>5.58553218841553</v>
       </c>
       <c r="H1532" t="n">
         <v>53597</v>
@@ -44826,7 +44826,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1533" t="n">
         <v>35027</v>
@@ -44913,7 +44913,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1536" t="n">
-        <v>5.7014946937561</v>
+        <v>5.70149421691895</v>
       </c>
       <c r="H1536" t="n">
         <v>27398</v>
@@ -45087,7 +45087,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1542" t="n">
-        <v>5.50822353363037</v>
+        <v>5.50822305679321</v>
       </c>
       <c r="H1542" t="n">
         <v>10776</v>
@@ -45290,7 +45290,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1549" t="n">
-        <v>5.39226055145264</v>
+        <v>5.39226102828979</v>
       </c>
       <c r="H1549" t="n">
         <v>17670</v>
@@ -45348,7 +45348,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.33427906036377</v>
+        <v>5.33427953720093</v>
       </c>
       <c r="H1551" t="n">
         <v>6270</v>
@@ -45551,7 +45551,7 @@
         <v>5.5</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.31495237350464</v>
+        <v>5.3149528503418</v>
       </c>
       <c r="H1558" t="n">
         <v>9714</v>
@@ -45580,7 +45580,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1559" t="n">
         <v>9223</v>
@@ -45667,7 +45667,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.27629852294922</v>
+        <v>5.27629804611206</v>
       </c>
       <c r="H1562" t="n">
         <v>3769</v>
@@ -45870,7 +45870,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.75446701049805</v>
+        <v>4.75446653366089</v>
       </c>
       <c r="H1569" t="n">
         <v>59041</v>
@@ -45928,7 +45928,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1571" t="n">
         <v>19659</v>
@@ -45986,7 +45986,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1573" t="n">
         <v>6033</v>
@@ -46102,7 +46102,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1577" t="n">
         <v>16481</v>
@@ -46131,7 +46131,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1578" t="n">
         <v>16827</v>
@@ -46247,7 +46247,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1582" t="n">
         <v>12336</v>
@@ -46537,7 +46537,7 @@
         <v>5</v>
       </c>
       <c r="G1592" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1592" t="n">
         <v>40020</v>
@@ -46566,7 +46566,7 @@
         <v>5</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1593" t="n">
         <v>20842</v>
@@ -47175,7 +47175,7 @@
         <v>5</v>
       </c>
       <c r="G1614" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1614" t="n">
         <v>15568</v>
@@ -47262,7 +47262,7 @@
         <v>5</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.83177518844604</v>
+        <v>4.83177471160889</v>
       </c>
       <c r="H1617" t="n">
         <v>1706</v>
@@ -47320,7 +47320,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1619" t="n">
         <v>97926</v>
@@ -47349,7 +47349,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1620" t="n">
         <v>14080</v>
@@ -47378,7 +47378,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.90908288955688</v>
+        <v>4.90908336639404</v>
       </c>
       <c r="H1621" t="n">
         <v>19839</v>
@@ -47436,7 +47436,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1623" t="n">
         <v>16886</v>
@@ -47552,7 +47552,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.99605560302734</v>
+        <v>4.99605512619019</v>
       </c>
       <c r="H1627" t="n">
         <v>60722</v>
@@ -47581,7 +47581,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1628" t="n">
         <v>24838</v>
@@ -47610,7 +47610,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1629" t="n">
         <v>21313</v>
@@ -47639,7 +47639,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1630" t="n">
         <v>23268</v>
@@ -47668,7 +47668,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1631" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1631" t="n">
         <v>2356</v>
@@ -47697,7 +47697,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.94773769378662</v>
+        <v>4.94773721694946</v>
       </c>
       <c r="H1632" t="n">
         <v>26681</v>
@@ -47755,7 +47755,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1634" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1634" t="n">
         <v>18116</v>
@@ -47842,7 +47842,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1637" t="n">
-        <v>5.02504587173462</v>
+        <v>5.02504539489746</v>
       </c>
       <c r="H1637" t="n">
         <v>9629</v>
@@ -47900,7 +47900,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.01538228988647</v>
+        <v>5.01538276672363</v>
       </c>
       <c r="H1639" t="n">
         <v>10513</v>
@@ -47929,7 +47929,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.1410083770752</v>
+        <v>5.14100885391235</v>
       </c>
       <c r="H1640" t="n">
         <v>5633</v>
@@ -47987,7 +47987,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.20865297317505</v>
+        <v>5.20865345001221</v>
       </c>
       <c r="H1642" t="n">
         <v>29183</v>
@@ -58984,6 +58984,35 @@
         <v>8810</v>
       </c>
       <c r="I2021" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2022" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2022" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="D2022" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E2022" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F2022" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G2022" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="H2022" t="n">
+        <v>6379</v>
+      </c>
+      <c r="I2022" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -59016,6 +59016,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2023">
+      <c r="A2023" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2023" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2023" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="D2023" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E2023" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="G2023" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="H2023" t="n">
+        <v>7356</v>
+      </c>
+      <c r="I2023" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GHC.MI.xlsx
+++ b/data/GHC.MI.xlsx
@@ -59045,6 +59045,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2024">
+      <c r="A2024" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2024" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2024" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="D2024" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E2024" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="F2024" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="G2024" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="H2024" t="n">
+        <v>3579</v>
+      </c>
+      <c r="I2024" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
